--- a/020_アプリケーション開発標準/020_テスト標準/単体テスト標準.xlsx
+++ b/020_アプリケーション開発標準/020_テスト標準/単体テスト標準.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD594ABF-9C60-45F3-A03F-1E1E3836C12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0235CBC0-FE63-4301-8D9A-A5F83BBC5F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="1860" windowWidth="25800" windowHeight="13710" tabRatio="641" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="641" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="33" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="368">
   <si>
     <t>更新</t>
     <rPh sb="0" eb="2">
@@ -4186,6 +4186,13 @@
       <t>ハン</t>
     </rPh>
     <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1.2. 参照ドキュメント</t>
+    <rPh sb="5" eb="7">
+      <t>サンショウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
@@ -8433,7 +8440,7 @@
       <c r="H25" s="10"/>
       <c r="I25" s="94">
         <f ca="1">IF(INDIRECT("変更履歴!D8")="","",MAX(INDIRECT("変更履歴!D8"):INDIRECT("変更履歴!F33")))</f>
-        <v>43336</v>
+        <v>45061</v>
       </c>
       <c r="J25" s="94"/>
       <c r="K25" s="94"/>
@@ -9110,7 +9117,7 @@
       <c r="AF1" s="148"/>
       <c r="AG1" s="149">
         <f>IF(D8="","",D8)</f>
-        <v>43336</v>
+        <v>45061</v>
       </c>
       <c r="AH1" s="150"/>
       <c r="AI1" s="151"/>
@@ -9406,7 +9413,7 @@
       </c>
       <c r="C8" s="132"/>
       <c r="D8" s="133">
-        <v>43336</v>
+        <v>45061</v>
       </c>
       <c r="E8" s="134"/>
       <c r="F8" s="135"/>
@@ -10573,7 +10580,7 @@
   <sheetPr codeName="Sheet44">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AW109"/>
+  <dimension ref="A1:AW110"/>
   <sheetFormatPr defaultColWidth="4.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="16" width="4.83203125" style="3" customWidth="1"/>
@@ -10633,7 +10640,7 @@
       <c r="AF1" s="148"/>
       <c r="AG1" s="149">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>43336</v>
+        <v>45061</v>
       </c>
       <c r="AH1" s="150"/>
       <c r="AI1" s="151"/>
@@ -11040,8 +11047,9 @@
     </row>
     <row r="9" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="A9" s="1"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="1"/>
+      <c r="C9" s="58" t="s">
+        <v>367</v>
+      </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -11093,9 +11101,7 @@
     </row>
     <row r="10" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="A10" s="1"/>
-      <c r="B10" s="24" t="s">
-        <v>238</v>
-      </c>
+      <c r="B10" s="18"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -11148,9 +11154,10 @@
     </row>
     <row r="11" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="A11" s="1"/>
-      <c r="C11" s="58" t="s">
-        <v>341</v>
-      </c>
+      <c r="B11" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -11203,7 +11210,7 @@
     <row r="12" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="A12" s="1"/>
       <c r="C12" s="58" t="s">
-        <v>240</v>
+        <v>341</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -11254,7 +11261,7 @@
     <row r="13" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="A13" s="1"/>
       <c r="C13" s="58" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -11306,7 +11313,7 @@
     <row r="14" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="A14" s="1"/>
       <c r="C14" s="58" t="s">
-        <v>340</v>
+        <v>241</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -11357,8 +11364,9 @@
     </row>
     <row r="15" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="A15" s="1"/>
-      <c r="B15" s="41"/>
-      <c r="C15" s="1"/>
+      <c r="C15" s="58" t="s">
+        <v>340</v>
+      </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -11406,18 +11414,17 @@
       <c r="AW15" s="41"/>
     </row>
     <row r="16" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="A16" s="41"/>
-      <c r="B16" s="24" t="s">
-        <v>342</v>
-      </c>
+      <c r="A16" s="1"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="41"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
       <c r="L16" s="41"/>
       <c r="M16" s="41"/>
       <c r="N16" s="41"/>
@@ -11457,18 +11464,18 @@
       <c r="AW16" s="41"/>
     </row>
     <row r="17" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="A17" s="1"/>
-      <c r="C17" s="58" t="s">
-        <v>242</v>
-      </c>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
+      <c r="A17" s="41"/>
+      <c r="B17" s="24" t="s">
+        <v>342</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="41"/>
@@ -11510,16 +11517,16 @@
     <row r="18" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="A18" s="1"/>
       <c r="C18" s="58" t="s">
-        <v>243</v>
-      </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
+        <v>242</v>
+      </c>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
-      <c r="K18" s="41"/>
+      <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -11559,18 +11566,17 @@
       <c r="AW18" s="41"/>
     </row>
     <row r="19" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="A19" s="41"/>
-      <c r="B19" s="1"/>
+      <c r="A19" s="1"/>
       <c r="C19" s="58" t="s">
-        <v>244</v>
-      </c>
-      <c r="D19" s="24"/>
+        <v>243</v>
+      </c>
+      <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="41"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
       <c r="K19" s="41"/>
       <c r="L19" s="41"/>
       <c r="M19" s="41"/>
@@ -11611,6 +11617,18 @@
     </row>
     <row r="20" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="A20" s="41"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="58" t="s">
+        <v>244</v>
+      </c>
+      <c r="D20" s="24"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="41"/>
       <c r="O20" s="41"/>
       <c r="P20" s="41"/>
       <c r="Q20" s="57"/>
@@ -11765,15 +11783,6 @@
     </row>
     <row r="25" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="A25" s="41"/>
-      <c r="B25" s="41"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="41"/>
-      <c r="J25" s="41"/>
-      <c r="K25" s="41"/>
       <c r="L25" s="41"/>
       <c r="M25" s="41"/>
       <c r="N25" s="41"/>
@@ -11916,6 +11925,7 @@
     <row r="28" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="A28" s="41"/>
       <c r="B28" s="41"/>
+      <c r="D28" s="59"/>
       <c r="E28" s="41"/>
       <c r="F28" s="41"/>
       <c r="G28" s="41"/>
@@ -11965,6 +11975,13 @@
     <row r="29" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="A29" s="41"/>
       <c r="B29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="41"/>
       <c r="N29" s="41"/>
       <c r="O29" s="41"/>
       <c r="P29" s="41"/>
@@ -12004,13 +12021,6 @@
     <row r="30" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="A30" s="41"/>
       <c r="B30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="41"/>
-      <c r="J30" s="41"/>
-      <c r="K30" s="41"/>
       <c r="L30" s="41"/>
       <c r="M30" s="41"/>
       <c r="N30" s="41"/>
@@ -12053,7 +12063,6 @@
       <c r="A31" s="41"/>
       <c r="B31" s="41"/>
       <c r="D31" s="41"/>
-      <c r="E31" s="59"/>
       <c r="F31" s="41"/>
       <c r="G31" s="41"/>
       <c r="H31" s="41"/>
@@ -12149,9 +12158,9 @@
     </row>
     <row r="33" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="A33" s="41"/>
-      <c r="B33" s="18"/>
+      <c r="B33" s="41"/>
       <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
+      <c r="E33" s="59"/>
       <c r="F33" s="41"/>
       <c r="G33" s="41"/>
       <c r="H33" s="41"/>
@@ -12198,8 +12207,14 @@
     </row>
     <row r="34" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="A34" s="41"/>
-      <c r="B34" s="41"/>
-      <c r="C34" s="41"/>
+      <c r="B34" s="18"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="41"/>
       <c r="K34" s="41"/>
       <c r="L34" s="41"/>
       <c r="M34" s="41"/>
@@ -12286,13 +12301,7 @@
       <c r="A36" s="41"/>
       <c r="B36" s="41"/>
       <c r="C36" s="41"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="40"/>
+      <c r="K36" s="41"/>
       <c r="L36" s="41"/>
       <c r="M36" s="41"/>
       <c r="N36" s="41"/>
@@ -12315,8 +12324,8 @@
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
-      <c r="H37" s="41"/>
-      <c r="I37" s="41"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
       <c r="J37" s="15"/>
       <c r="K37" s="40"/>
       <c r="L37" s="41"/>
@@ -12338,7 +12347,6 @@
       <c r="A38" s="41"/>
       <c r="B38" s="41"/>
       <c r="C38" s="41"/>
-      <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -12364,15 +12372,15 @@
     <row r="39" spans="1:49" ht="11.25" x14ac:dyDescent="0.15">
       <c r="A39" s="41"/>
       <c r="B39" s="41"/>
-      <c r="C39" s="1"/>
+      <c r="C39" s="41"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
       <c r="H39" s="41"/>
       <c r="I39" s="41"/>
       <c r="J39" s="15"/>
-      <c r="K39" s="15"/>
+      <c r="K39" s="40"/>
       <c r="L39" s="41"/>
       <c r="M39" s="41"/>
       <c r="N39" s="41"/>
@@ -12392,15 +12400,15 @@
     <row r="40" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="41"/>
       <c r="B40" s="41"/>
-      <c r="C40" s="41"/>
-      <c r="D40" s="41"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
       <c r="E40" s="41"/>
       <c r="F40" s="41"/>
       <c r="G40" s="41"/>
       <c r="H40" s="41"/>
       <c r="I40" s="41"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="41"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
       <c r="L40" s="41"/>
       <c r="M40" s="41"/>
       <c r="N40" s="41"/>
@@ -12449,6 +12457,7 @@
       <c r="A42" s="41"/>
       <c r="B42" s="41"/>
       <c r="C42" s="41"/>
+      <c r="D42" s="41"/>
       <c r="E42" s="41"/>
       <c r="F42" s="41"/>
       <c r="G42" s="41"/>
@@ -12481,7 +12490,7 @@
       <c r="G43" s="41"/>
       <c r="H43" s="41"/>
       <c r="I43" s="41"/>
-      <c r="J43" s="1"/>
+      <c r="J43" s="2"/>
       <c r="K43" s="41"/>
       <c r="L43" s="41"/>
       <c r="M43" s="41"/>
@@ -12665,6 +12674,11 @@
       <c r="A50" s="41"/>
       <c r="B50" s="41"/>
       <c r="C50" s="41"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="41"/>
+      <c r="G50" s="41"/>
+      <c r="H50" s="41"/>
+      <c r="I50" s="41"/>
       <c r="J50" s="1"/>
       <c r="K50" s="41"/>
       <c r="L50" s="41"/>
@@ -12687,6 +12701,12 @@
       <c r="A51" s="41"/>
       <c r="B51" s="41"/>
       <c r="C51" s="41"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
       <c r="J51" s="1"/>
       <c r="K51" s="41"/>
       <c r="L51" s="36"/>
@@ -12708,6 +12728,12 @@
       <c r="A52" s="41"/>
       <c r="B52" s="41"/>
       <c r="C52" s="41"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="22"/>
+      <c r="I52" s="22"/>
       <c r="J52" s="1"/>
       <c r="K52" s="41"/>
       <c r="L52" s="41"/>
@@ -12731,7 +12757,7 @@
       <c r="B53" s="41"/>
       <c r="C53" s="41"/>
       <c r="J53" s="1"/>
-      <c r="K53" s="36"/>
+      <c r="K53" s="41"/>
       <c r="L53" s="41"/>
       <c r="M53" s="41"/>
       <c r="N53" s="41"/>
@@ -12753,7 +12779,7 @@
       <c r="B54" s="41"/>
       <c r="C54" s="41"/>
       <c r="J54" s="1"/>
-      <c r="K54" s="41"/>
+      <c r="K54" s="36"/>
       <c r="L54" s="41"/>
       <c r="M54" s="41"/>
       <c r="N54" s="41"/>
@@ -12818,7 +12844,6 @@
       <c r="A57" s="41"/>
       <c r="B57" s="41"/>
       <c r="C57" s="41"/>
-      <c r="D57" s="41"/>
       <c r="J57" s="1"/>
       <c r="K57" s="41"/>
       <c r="L57" s="41"/>
@@ -12840,6 +12865,8 @@
     <row r="58" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="41"/>
       <c r="B58" s="41"/>
+      <c r="C58" s="41"/>
+      <c r="D58" s="41"/>
       <c r="J58" s="1"/>
       <c r="K58" s="41"/>
       <c r="L58" s="41"/>
@@ -12861,7 +12888,6 @@
     <row r="59" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="41"/>
       <c r="B59" s="41"/>
-      <c r="D59" s="41"/>
       <c r="J59" s="1"/>
       <c r="K59" s="41"/>
       <c r="L59" s="41"/>
@@ -13016,11 +13042,6 @@
       <c r="A66" s="41"/>
       <c r="B66" s="41"/>
       <c r="D66" s="41"/>
-      <c r="E66" s="41"/>
-      <c r="F66" s="41"/>
-      <c r="G66" s="41"/>
-      <c r="H66" s="41"/>
-      <c r="I66" s="41"/>
       <c r="J66" s="1"/>
       <c r="K66" s="41"/>
       <c r="L66" s="41"/>
@@ -13101,7 +13122,7 @@
       <c r="F69" s="41"/>
       <c r="G69" s="41"/>
       <c r="H69" s="41"/>
-      <c r="I69" s="15"/>
+      <c r="I69" s="41"/>
       <c r="J69" s="1"/>
       <c r="K69" s="41"/>
       <c r="L69" s="41"/>
@@ -13182,8 +13203,8 @@
       <c r="F72" s="41"/>
       <c r="G72" s="41"/>
       <c r="H72" s="41"/>
-      <c r="I72" s="41"/>
-      <c r="J72" s="2"/>
+      <c r="I72" s="15"/>
+      <c r="J72" s="1"/>
       <c r="K72" s="41"/>
       <c r="L72" s="41"/>
       <c r="M72" s="41"/>
@@ -13202,16 +13223,15 @@
       <c r="AH72" s="3"/>
     </row>
     <row r="73" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A73" s="15"/>
-      <c r="B73" s="1"/>
-      <c r="C73" s="41"/>
+      <c r="A73" s="41"/>
+      <c r="B73" s="41"/>
       <c r="D73" s="41"/>
       <c r="E73" s="41"/>
       <c r="F73" s="41"/>
       <c r="G73" s="41"/>
       <c r="H73" s="41"/>
       <c r="I73" s="41"/>
-      <c r="J73" s="41"/>
+      <c r="J73" s="2"/>
       <c r="K73" s="41"/>
       <c r="L73" s="41"/>
       <c r="M73" s="41"/>
@@ -13222,8 +13242,8 @@
       <c r="AH73" s="3"/>
     </row>
     <row r="74" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A74" s="41"/>
-      <c r="B74" s="2"/>
+      <c r="A74" s="15"/>
+      <c r="B74" s="1"/>
       <c r="C74" s="41"/>
       <c r="D74" s="41"/>
       <c r="E74" s="41"/>
@@ -13302,8 +13322,8 @@
       <c r="AH77" s="3"/>
     </row>
     <row r="78" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A78" s="15"/>
-      <c r="B78" s="15"/>
+      <c r="A78" s="41"/>
+      <c r="B78" s="2"/>
       <c r="C78" s="41"/>
       <c r="D78" s="41"/>
       <c r="E78" s="41"/>
@@ -13463,16 +13483,16 @@
     </row>
     <row r="86" spans="1:34" s="22" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="15"/>
-      <c r="B86" s="1"/>
+      <c r="B86" s="15"/>
       <c r="C86" s="41"/>
-      <c r="D86" s="36"/>
-      <c r="E86" s="36"/>
-      <c r="F86" s="36"/>
-      <c r="G86" s="36"/>
-      <c r="H86" s="36"/>
-      <c r="I86" s="36"/>
-      <c r="J86" s="36"/>
-      <c r="K86" s="36"/>
+      <c r="D86" s="41"/>
+      <c r="E86" s="41"/>
+      <c r="F86" s="41"/>
+      <c r="G86" s="41"/>
+      <c r="H86" s="41"/>
+      <c r="I86" s="41"/>
+      <c r="J86" s="41"/>
+      <c r="K86" s="41"/>
       <c r="L86" s="36"/>
       <c r="M86" s="36"/>
       <c r="N86" s="36"/>
@@ -13484,14 +13504,14 @@
       <c r="A87" s="15"/>
       <c r="B87" s="1"/>
       <c r="C87" s="41"/>
-      <c r="D87" s="41"/>
-      <c r="E87" s="41"/>
-      <c r="F87" s="41"/>
-      <c r="G87" s="41"/>
-      <c r="H87" s="41"/>
-      <c r="I87" s="41"/>
-      <c r="J87" s="41"/>
-      <c r="K87" s="41"/>
+      <c r="D87" s="36"/>
+      <c r="E87" s="36"/>
+      <c r="F87" s="36"/>
+      <c r="G87" s="36"/>
+      <c r="H87" s="36"/>
+      <c r="I87" s="36"/>
+      <c r="J87" s="36"/>
+      <c r="K87" s="36"/>
       <c r="L87" s="41"/>
       <c r="M87" s="41"/>
       <c r="N87" s="41"/>
@@ -13503,7 +13523,7 @@
     <row r="88" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="15"/>
       <c r="B88" s="1"/>
-      <c r="C88" s="36"/>
+      <c r="C88" s="41"/>
       <c r="D88" s="41"/>
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
@@ -13523,7 +13543,7 @@
     <row r="89" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="15"/>
       <c r="B89" s="1"/>
-      <c r="C89" s="41"/>
+      <c r="C89" s="36"/>
       <c r="D89" s="41"/>
       <c r="E89" s="41"/>
       <c r="F89" s="41"/>
@@ -13641,8 +13661,8 @@
       <c r="AH94" s="3"/>
     </row>
     <row r="95" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A95" s="41"/>
-      <c r="B95" s="2"/>
+      <c r="A95" s="15"/>
+      <c r="B95" s="1"/>
       <c r="C95" s="41"/>
       <c r="D95" s="41"/>
       <c r="E95" s="41"/>
@@ -13721,8 +13741,8 @@
       <c r="AH98" s="3"/>
     </row>
     <row r="99" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A99" s="15"/>
-      <c r="B99" s="1"/>
+      <c r="A99" s="41"/>
+      <c r="B99" s="2"/>
       <c r="C99" s="41"/>
       <c r="D99" s="41"/>
       <c r="E99" s="41"/>
@@ -13841,8 +13861,8 @@
       <c r="AH104" s="3"/>
     </row>
     <row r="105" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A105" s="41"/>
-      <c r="B105" s="2"/>
+      <c r="A105" s="15"/>
+      <c r="B105" s="1"/>
       <c r="C105" s="41"/>
       <c r="D105" s="41"/>
       <c r="E105" s="41"/>
@@ -13922,7 +13942,7 @@
     </row>
     <row r="109" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="41"/>
-      <c r="B109" s="41"/>
+      <c r="B109" s="2"/>
       <c r="C109" s="41"/>
       <c r="D109" s="41"/>
       <c r="E109" s="41"/>
@@ -13969,6 +13989,19 @@
       <c r="AV109" s="41"/>
       <c r="AW109" s="41"/>
     </row>
+    <row r="110" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A110" s="41"/>
+      <c r="B110" s="41"/>
+      <c r="C110" s="41"/>
+      <c r="D110" s="41"/>
+      <c r="E110" s="41"/>
+      <c r="F110" s="41"/>
+      <c r="G110" s="41"/>
+      <c r="H110" s="41"/>
+      <c r="I110" s="41"/>
+      <c r="J110" s="41"/>
+      <c r="K110" s="41"/>
+    </row>
   </sheetData>
   <mergeCells count="17">
     <mergeCell ref="AC3:AF3"/>
@@ -14061,7 +14094,7 @@
       <c r="AF1" s="148"/>
       <c r="AG1" s="149">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>43336</v>
+        <v>45061</v>
       </c>
       <c r="AH1" s="150"/>
       <c r="AI1" s="151"/>
@@ -15055,7 +15088,7 @@
       <c r="AF1" s="148"/>
       <c r="AG1" s="149">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>43336</v>
+        <v>45061</v>
       </c>
       <c r="AH1" s="150"/>
       <c r="AI1" s="151"/>
@@ -16240,7 +16273,7 @@
       <c r="AF1" s="148"/>
       <c r="AG1" s="149">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>43336</v>
+        <v>45061</v>
       </c>
       <c r="AH1" s="150"/>
       <c r="AI1" s="151"/>
@@ -19474,7 +19507,7 @@
       <c r="AF1" s="148"/>
       <c r="AG1" s="149">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>43336</v>
+        <v>45061</v>
       </c>
       <c r="AH1" s="150"/>
       <c r="AI1" s="151"/>

--- a/020_アプリケーション開発標準/020_テスト標準/単体テスト標準.xlsx
+++ b/020_アプリケーション開発標準/020_テスト標準/単体テスト標準.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0235CBC0-FE63-4301-8D9A-A5F83BBC5F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D0F957-52F8-4FD8-AC8F-6190719590AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" tabRatio="641" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="754" yWindow="754" windowWidth="24686" windowHeight="13260" tabRatio="641" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="33" r:id="rId1"/>
@@ -5710,8 +5710,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7753350" y="390525"/>
-          <a:ext cx="1390650" cy="581025"/>
+          <a:off x="8100332" y="387804"/>
+          <a:ext cx="1460047" cy="570139"/>
           <a:chOff x="809" y="41"/>
           <a:chExt cx="143" cy="61"/>
         </a:xfrm>
@@ -8382,39 +8382,39 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:S512"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="13.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="8.83203125" style="7"/>
+    <col min="1" max="16384" width="8.81640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B1" s="8"/>
       <c r="C1" s="9"/>
     </row>
-    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
     </row>
-    <row r="3" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="4" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="6" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="7" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="8" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="9" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="10" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="11" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="12" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="13" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="14" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="15" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="16" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="17" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="18" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="19" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="20" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="21" spans="6:12" ht="9" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="22" spans="6:12" ht="9" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="23" spans="6:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="6:12" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="6:12" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="6:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
@@ -8425,7 +8425,7 @@
       <c r="K23" s="33"/>
       <c r="L23" s="33"/>
     </row>
-    <row r="24" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
@@ -8434,19 +8434,19 @@
       <c r="K24" s="33"/>
       <c r="L24" s="33"/>
     </row>
-    <row r="25" spans="6:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="6:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
       <c r="I25" s="94">
         <f ca="1">IF(INDIRECT("変更履歴!D8")="","",MAX(INDIRECT("変更履歴!D8"):INDIRECT("変更履歴!F33")))</f>
-        <v>45061</v>
+        <v>45565</v>
       </c>
       <c r="J25" s="94"/>
       <c r="K25" s="94"/>
       <c r="L25" s="33"/>
     </row>
-    <row r="26" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
       <c r="H26" s="10"/>
@@ -8455,7 +8455,7 @@
       <c r="K26" s="33"/>
       <c r="L26" s="33"/>
     </row>
-    <row r="27" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
@@ -8464,7 +8464,7 @@
       <c r="K27" s="33"/>
       <c r="L27" s="33"/>
     </row>
-    <row r="28" spans="6:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="6:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F28" s="10"/>
       <c r="H28" s="10"/>
       <c r="I28" s="33"/>
@@ -8472,7 +8472,7 @@
       <c r="K28" s="33"/>
       <c r="L28" s="33"/>
     </row>
-    <row r="29" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F29" s="10"/>
       <c r="G29" s="11"/>
       <c r="H29" s="10"/>
@@ -8481,7 +8481,7 @@
       <c r="K29" s="33"/>
       <c r="L29" s="33"/>
     </row>
-    <row r="30" spans="6:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="6:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F30" s="10"/>
       <c r="G30" s="11"/>
       <c r="H30" s="10"/>
@@ -8490,7 +8490,7 @@
       <c r="K30" s="33"/>
       <c r="L30" s="33"/>
     </row>
-    <row r="31" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F31" s="10"/>
       <c r="G31" s="11"/>
       <c r="H31" s="10"/>
@@ -8499,7 +8499,7 @@
       <c r="K31" s="33"/>
       <c r="L31" s="33"/>
     </row>
-    <row r="32" spans="6:12" ht="18.75" x14ac:dyDescent="0.2">
+    <row r="32" spans="6:12" ht="18.45" x14ac:dyDescent="0.3">
       <c r="F32" s="10"/>
       <c r="G32" s="11"/>
       <c r="H32" s="10"/>
@@ -8510,7 +8510,7 @@
       <c r="K32" s="33"/>
       <c r="L32" s="33"/>
     </row>
-    <row r="33" spans="6:19" ht="18.75" x14ac:dyDescent="0.2">
+    <row r="33" spans="6:19" ht="18.45" x14ac:dyDescent="0.3">
       <c r="F33" s="10"/>
       <c r="H33" s="10"/>
       <c r="I33" s="33"/>
@@ -8522,7 +8522,7 @@
       <c r="O33" s="12"/>
       <c r="P33" s="12"/>
     </row>
-    <row r="34" spans="6:19" ht="18.75" x14ac:dyDescent="0.2">
+    <row r="34" spans="6:19" ht="18.45" x14ac:dyDescent="0.3">
       <c r="F34" s="10"/>
       <c r="H34" s="10"/>
       <c r="I34" s="33"/>
@@ -8539,504 +8539,504 @@
       <c r="R34" s="92"/>
       <c r="S34" s="92"/>
     </row>
-    <row r="35" spans="6:19" x14ac:dyDescent="0.15">
+    <row r="35" spans="6:19" x14ac:dyDescent="0.25">
       <c r="Q35" s="92"/>
       <c r="R35" s="92"/>
       <c r="S35" s="92"/>
     </row>
-    <row r="36" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Q36" s="93"/>
       <c r="R36" s="92"/>
       <c r="S36" s="32"/>
     </row>
-    <row r="37" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Q37" s="89"/>
       <c r="R37" s="90"/>
       <c r="S37" s="89"/>
     </row>
-    <row r="38" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Q38" s="90"/>
       <c r="R38" s="90"/>
       <c r="S38" s="90"/>
     </row>
-    <row r="39" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Q39" s="90"/>
       <c r="R39" s="90"/>
       <c r="S39" s="90"/>
     </row>
-    <row r="40" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="41" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="42" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="43" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="44" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="45" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="46" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="47" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="48" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="49" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="50" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="51" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="52" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="53" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="54" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="55" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="56" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="57" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="58" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="59" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="60" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="61" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="62" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="63" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="64" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="65" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="66" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="67" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="68" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="69" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="70" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="71" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="72" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="73" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="74" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="75" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="76" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="77" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="78" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="79" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="80" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="81" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="82" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="83" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="84" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="85" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="86" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="87" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="88" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="89" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="90" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="91" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="92" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="93" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="94" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="95" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="96" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="97" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="98" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="99" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="100" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="101" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="102" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="103" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="104" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="105" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="106" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="107" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="108" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="109" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="110" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="111" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="112" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="113" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="114" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="115" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="116" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="117" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="118" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="119" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="120" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="121" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="122" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="123" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="124" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="125" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="126" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="40" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="Q37:R39"/>
@@ -9060,16 +9060,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AN33"/>
-  <sheetFormatPr defaultColWidth="4.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="4.81640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16" width="4.83203125" style="19" customWidth="1"/>
-    <col min="17" max="17" width="4.83203125" style="21" customWidth="1"/>
-    <col min="18" max="34" width="4.83203125" style="19" customWidth="1"/>
-    <col min="35" max="35" width="4.83203125" style="21" customWidth="1"/>
-    <col min="36" max="16384" width="4.83203125" style="19"/>
+    <col min="1" max="16" width="4.81640625" style="19" customWidth="1"/>
+    <col min="17" max="17" width="4.81640625" style="21" customWidth="1"/>
+    <col min="18" max="34" width="4.81640625" style="19" customWidth="1"/>
+    <col min="35" max="35" width="4.81640625" style="21" customWidth="1"/>
+    <col min="36" max="16384" width="4.81640625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="107" t="s">
         <v>225</v>
       </c>
@@ -9117,7 +9117,7 @@
       <c r="AF1" s="148"/>
       <c r="AG1" s="149">
         <f>IF(D8="","",D8)</f>
-        <v>45061</v>
+        <v>45565</v>
       </c>
       <c r="AH1" s="150"/>
       <c r="AI1" s="151"/>
@@ -9127,7 +9127,7 @@
       <c r="AM1" s="37"/>
       <c r="AN1" s="38"/>
     </row>
-    <row r="2" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="107" t="s">
         <v>228</v>
       </c>
@@ -9181,7 +9181,7 @@
       <c r="AM2" s="37"/>
       <c r="AN2" s="37"/>
     </row>
-    <row r="3" spans="1:40" s="13" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:40" s="13" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A3" s="107" t="s">
         <v>230</v>
       </c>
@@ -9225,7 +9225,7 @@
       <c r="AM3" s="36"/>
       <c r="AN3" s="36"/>
     </row>
-    <row r="4" spans="1:40" s="13" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:40" s="13" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="36"/>
       <c r="B4" s="36"/>
       <c r="C4" s="36"/>
@@ -9267,7 +9267,7 @@
       <c r="AM4" s="36"/>
       <c r="AN4" s="36"/>
     </row>
-    <row r="5" spans="1:40" s="13" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" s="13" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="36"/>
       <c r="B5" s="36"/>
       <c r="C5" s="36"/>
@@ -9311,7 +9311,7 @@
       <c r="AM5" s="36"/>
       <c r="AN5" s="36"/>
     </row>
-    <row r="6" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="36"/>
       <c r="B6" s="36"/>
       <c r="C6" s="36"/>
@@ -9353,7 +9353,7 @@
       <c r="AM6" s="36"/>
       <c r="AN6" s="36"/>
     </row>
-    <row r="7" spans="1:40" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="55" t="s">
         <v>234</v>
       </c>
@@ -9404,7 +9404,7 @@
       <c r="AH7" s="159"/>
       <c r="AI7" s="158"/>
     </row>
-    <row r="8" spans="1:40" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:40" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A8" s="65">
         <v>1</v>
       </c>
@@ -9413,7 +9413,7 @@
       </c>
       <c r="C8" s="132"/>
       <c r="D8" s="133">
-        <v>45061</v>
+        <v>45565</v>
       </c>
       <c r="E8" s="134"/>
       <c r="F8" s="135"/>
@@ -9455,7 +9455,7 @@
       <c r="AH8" s="140"/>
       <c r="AI8" s="141"/>
     </row>
-    <row r="9" spans="1:40" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:40" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A9" s="66"/>
       <c r="B9" s="156"/>
       <c r="C9" s="102"/>
@@ -9492,7 +9492,7 @@
       <c r="AH9" s="96"/>
       <c r="AI9" s="97"/>
     </row>
-    <row r="10" spans="1:40" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:40" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A10" s="56"/>
       <c r="B10" s="156"/>
       <c r="C10" s="102"/>
@@ -9529,7 +9529,7 @@
       <c r="AH10" s="96"/>
       <c r="AI10" s="97"/>
     </row>
-    <row r="11" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="56"/>
       <c r="B11" s="101"/>
       <c r="C11" s="102"/>
@@ -9566,7 +9566,7 @@
       <c r="AH11" s="96"/>
       <c r="AI11" s="97"/>
     </row>
-    <row r="12" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="56"/>
       <c r="B12" s="101"/>
       <c r="C12" s="102"/>
@@ -9603,7 +9603,7 @@
       <c r="AH12" s="96"/>
       <c r="AI12" s="97"/>
     </row>
-    <row r="13" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="56"/>
       <c r="B13" s="101"/>
       <c r="C13" s="102"/>
@@ -9640,7 +9640,7 @@
       <c r="AH13" s="96"/>
       <c r="AI13" s="97"/>
     </row>
-    <row r="14" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="56"/>
       <c r="B14" s="101"/>
       <c r="C14" s="102"/>
@@ -9677,7 +9677,7 @@
       <c r="AH14" s="96"/>
       <c r="AI14" s="97"/>
     </row>
-    <row r="15" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="56"/>
       <c r="B15" s="101"/>
       <c r="C15" s="102"/>
@@ -9714,7 +9714,7 @@
       <c r="AH15" s="96"/>
       <c r="AI15" s="97"/>
     </row>
-    <row r="16" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="56"/>
       <c r="B16" s="101"/>
       <c r="C16" s="102"/>
@@ -9751,7 +9751,7 @@
       <c r="AH16" s="96"/>
       <c r="AI16" s="97"/>
     </row>
-    <row r="17" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="56"/>
       <c r="B17" s="101"/>
       <c r="C17" s="102"/>
@@ -9788,7 +9788,7 @@
       <c r="AH17" s="96"/>
       <c r="AI17" s="97"/>
     </row>
-    <row r="18" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="56"/>
       <c r="B18" s="101"/>
       <c r="C18" s="102"/>
@@ -9825,7 +9825,7 @@
       <c r="AH18" s="96"/>
       <c r="AI18" s="97"/>
     </row>
-    <row r="19" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="56"/>
       <c r="B19" s="101"/>
       <c r="C19" s="102"/>
@@ -9862,7 +9862,7 @@
       <c r="AH19" s="96"/>
       <c r="AI19" s="97"/>
     </row>
-    <row r="20" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="56"/>
       <c r="B20" s="101"/>
       <c r="C20" s="102"/>
@@ -9899,7 +9899,7 @@
       <c r="AH20" s="96"/>
       <c r="AI20" s="97"/>
     </row>
-    <row r="21" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="56"/>
       <c r="B21" s="101"/>
       <c r="C21" s="102"/>
@@ -9936,7 +9936,7 @@
       <c r="AH21" s="96"/>
       <c r="AI21" s="97"/>
     </row>
-    <row r="22" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="56"/>
       <c r="B22" s="101"/>
       <c r="C22" s="102"/>
@@ -9973,7 +9973,7 @@
       <c r="AH22" s="96"/>
       <c r="AI22" s="97"/>
     </row>
-    <row r="23" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="56"/>
       <c r="B23" s="101"/>
       <c r="C23" s="102"/>
@@ -10010,7 +10010,7 @@
       <c r="AH23" s="96"/>
       <c r="AI23" s="97"/>
     </row>
-    <row r="24" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="56"/>
       <c r="B24" s="101"/>
       <c r="C24" s="102"/>
@@ -10047,7 +10047,7 @@
       <c r="AH24" s="96"/>
       <c r="AI24" s="97"/>
     </row>
-    <row r="25" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="56"/>
       <c r="B25" s="101"/>
       <c r="C25" s="102"/>
@@ -10084,7 +10084,7 @@
       <c r="AH25" s="96"/>
       <c r="AI25" s="97"/>
     </row>
-    <row r="26" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="56"/>
       <c r="B26" s="101"/>
       <c r="C26" s="102"/>
@@ -10121,7 +10121,7 @@
       <c r="AH26" s="96"/>
       <c r="AI26" s="97"/>
     </row>
-    <row r="27" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="56"/>
       <c r="B27" s="101"/>
       <c r="C27" s="102"/>
@@ -10158,7 +10158,7 @@
       <c r="AH27" s="96"/>
       <c r="AI27" s="97"/>
     </row>
-    <row r="28" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="56"/>
       <c r="B28" s="101"/>
       <c r="C28" s="102"/>
@@ -10195,7 +10195,7 @@
       <c r="AH28" s="96"/>
       <c r="AI28" s="97"/>
     </row>
-    <row r="29" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="56"/>
       <c r="B29" s="101"/>
       <c r="C29" s="102"/>
@@ -10232,7 +10232,7 @@
       <c r="AH29" s="96"/>
       <c r="AI29" s="97"/>
     </row>
-    <row r="30" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="56"/>
       <c r="B30" s="101"/>
       <c r="C30" s="102"/>
@@ -10269,7 +10269,7 @@
       <c r="AH30" s="96"/>
       <c r="AI30" s="97"/>
     </row>
-    <row r="31" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="56"/>
       <c r="B31" s="101"/>
       <c r="C31" s="102"/>
@@ -10306,7 +10306,7 @@
       <c r="AH31" s="96"/>
       <c r="AI31" s="97"/>
     </row>
-    <row r="32" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="56"/>
       <c r="B32" s="101"/>
       <c r="C32" s="102"/>
@@ -10343,7 +10343,7 @@
       <c r="AH32" s="96"/>
       <c r="AI32" s="97"/>
     </row>
-    <row r="33" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="56"/>
       <c r="B33" s="101"/>
       <c r="C33" s="102"/>
@@ -10581,16 +10581,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AW110"/>
-  <sheetFormatPr defaultColWidth="4.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="4.81640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16" width="4.83203125" style="3" customWidth="1"/>
-    <col min="17" max="17" width="4.83203125" style="2" customWidth="1"/>
-    <col min="18" max="33" width="4.83203125" style="3" customWidth="1"/>
-    <col min="34" max="34" width="4.83203125" style="2" customWidth="1"/>
-    <col min="35" max="16384" width="4.83203125" style="3"/>
+    <col min="1" max="16" width="4.81640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="4.81640625" style="2" customWidth="1"/>
+    <col min="18" max="33" width="4.81640625" style="3" customWidth="1"/>
+    <col min="34" max="34" width="4.81640625" style="2" customWidth="1"/>
+    <col min="35" max="16384" width="4.81640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:49" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="107" t="s">
         <v>225</v>
       </c>
@@ -10640,7 +10640,7 @@
       <c r="AF1" s="148"/>
       <c r="AG1" s="149">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>45061</v>
+        <v>45565</v>
       </c>
       <c r="AH1" s="150"/>
       <c r="AI1" s="151"/>
@@ -10659,7 +10659,7 @@
       <c r="AV1" s="36"/>
       <c r="AW1" s="36"/>
     </row>
-    <row r="2" spans="1:49" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:49" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="107" t="s">
         <v>228</v>
       </c>
@@ -10723,7 +10723,7 @@
       <c r="AV2" s="36"/>
       <c r="AW2" s="36"/>
     </row>
-    <row r="3" spans="1:49" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:49" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="107" t="s">
         <v>230</v>
       </c>
@@ -10785,7 +10785,7 @@
       <c r="AV3" s="36"/>
       <c r="AW3" s="36"/>
     </row>
-    <row r="4" spans="1:49" s="13" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:49" s="13" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A4" s="36"/>
       <c r="B4" s="36"/>
       <c r="C4" s="36"/>
@@ -10836,7 +10836,7 @@
       <c r="AV4" s="36"/>
       <c r="AW4" s="36"/>
     </row>
-    <row r="5" spans="1:49" s="13" customFormat="1" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:49" s="13" customFormat="1" ht="16.75" x14ac:dyDescent="0.3">
       <c r="A5" s="36"/>
       <c r="B5" s="36"/>
       <c r="C5" s="36"/>
@@ -10887,7 +10887,7 @@
       <c r="AV5" s="36"/>
       <c r="AW5" s="36"/>
     </row>
-    <row r="6" spans="1:49" s="13" customFormat="1" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:49" s="13" customFormat="1" ht="16.75" x14ac:dyDescent="0.3">
       <c r="A6" s="36"/>
       <c r="B6" s="36"/>
       <c r="C6" s="36"/>
@@ -10938,7 +10938,7 @@
       <c r="AV6" s="36"/>
       <c r="AW6" s="36"/>
     </row>
-    <row r="7" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="24" t="s">
         <v>237</v>
@@ -10992,7 +10992,7 @@
       <c r="AV7" s="41"/>
       <c r="AW7" s="41"/>
     </row>
-    <row r="8" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="C8" s="58" t="s">
         <v>239</v>
@@ -11045,7 +11045,7 @@
       <c r="AV8" s="41"/>
       <c r="AW8" s="41"/>
     </row>
-    <row r="9" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="C9" s="58" t="s">
         <v>367</v>
@@ -11099,7 +11099,7 @@
       <c r="AV9" s="41"/>
       <c r="AW9" s="41"/>
     </row>
-    <row r="10" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="18"/>
       <c r="C10" s="1"/>
@@ -11152,7 +11152,7 @@
       <c r="AV10" s="41"/>
       <c r="AW10" s="41"/>
     </row>
-    <row r="11" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="24" t="s">
         <v>238</v>
@@ -11207,7 +11207,7 @@
       <c r="AV11" s="41"/>
       <c r="AW11" s="41"/>
     </row>
-    <row r="12" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="C12" s="58" t="s">
         <v>341</v>
@@ -11258,7 +11258,7 @@
       <c r="AV12" s="41"/>
       <c r="AW12" s="41"/>
     </row>
-    <row r="13" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="C13" s="58" t="s">
         <v>240</v>
@@ -11310,7 +11310,7 @@
       <c r="AV13" s="41"/>
       <c r="AW13" s="41"/>
     </row>
-    <row r="14" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="C14" s="58" t="s">
         <v>241</v>
@@ -11362,7 +11362,7 @@
       <c r="AV14" s="41"/>
       <c r="AW14" s="41"/>
     </row>
-    <row r="15" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="C15" s="58" t="s">
         <v>340</v>
@@ -11413,7 +11413,7 @@
       <c r="AV15" s="41"/>
       <c r="AW15" s="41"/>
     </row>
-    <row r="16" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="41"/>
       <c r="C16" s="1"/>
@@ -11463,7 +11463,7 @@
       <c r="AV16" s="41"/>
       <c r="AW16" s="41"/>
     </row>
-    <row r="17" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A17" s="41"/>
       <c r="B17" s="24" t="s">
         <v>342</v>
@@ -11514,7 +11514,7 @@
       <c r="AV17" s="41"/>
       <c r="AW17" s="41"/>
     </row>
-    <row r="18" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="C18" s="58" t="s">
         <v>242</v>
@@ -11565,7 +11565,7 @@
       <c r="AV18" s="41"/>
       <c r="AW18" s="41"/>
     </row>
-    <row r="19" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="C19" s="58" t="s">
         <v>243</v>
@@ -11615,7 +11615,7 @@
       <c r="AV19" s="41"/>
       <c r="AW19" s="41"/>
     </row>
-    <row r="20" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A20" s="41"/>
       <c r="B20" s="1"/>
       <c r="C20" s="58" t="s">
@@ -11664,7 +11664,7 @@
       <c r="AV20" s="41"/>
       <c r="AW20" s="41"/>
     </row>
-    <row r="21" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A21" s="41"/>
       <c r="O21" s="41"/>
       <c r="P21" s="41"/>
@@ -11702,7 +11702,7 @@
       <c r="AV21" s="41"/>
       <c r="AW21" s="41"/>
     </row>
-    <row r="22" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A22" s="41"/>
       <c r="O22" s="41"/>
       <c r="P22" s="41"/>
@@ -11729,7 +11729,7 @@
       <c r="AV22" s="41"/>
       <c r="AW22" s="41"/>
     </row>
-    <row r="23" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A23" s="41"/>
       <c r="O23" s="41"/>
       <c r="P23" s="41"/>
@@ -11756,7 +11756,7 @@
       <c r="AV23" s="41"/>
       <c r="AW23" s="41"/>
     </row>
-    <row r="24" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A24" s="41"/>
       <c r="O24" s="41"/>
       <c r="P24" s="41"/>
@@ -11781,7 +11781,7 @@
       <c r="AV24" s="41"/>
       <c r="AW24" s="41"/>
     </row>
-    <row r="25" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A25" s="41"/>
       <c r="L25" s="41"/>
       <c r="M25" s="41"/>
@@ -11822,7 +11822,7 @@
       <c r="AV25" s="41"/>
       <c r="AW25" s="41"/>
     </row>
-    <row r="26" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A26" s="41"/>
       <c r="B26" s="41"/>
       <c r="D26" s="59"/>
@@ -11872,7 +11872,7 @@
       <c r="AV26" s="41"/>
       <c r="AW26" s="41"/>
     </row>
-    <row r="27" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A27" s="41"/>
       <c r="B27" s="41"/>
       <c r="D27" s="59"/>
@@ -11922,7 +11922,7 @@
       <c r="AV27" s="41"/>
       <c r="AW27" s="41"/>
     </row>
-    <row r="28" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A28" s="41"/>
       <c r="B28" s="41"/>
       <c r="D28" s="59"/>
@@ -11972,7 +11972,7 @@
       <c r="AV28" s="36"/>
       <c r="AW28" s="36"/>
     </row>
-    <row r="29" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A29" s="41"/>
       <c r="B29" s="41"/>
       <c r="E29" s="41"/>
@@ -12018,7 +12018,7 @@
       <c r="AV29" s="36"/>
       <c r="AW29" s="36"/>
     </row>
-    <row r="30" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A30" s="41"/>
       <c r="B30" s="41"/>
       <c r="L30" s="41"/>
@@ -12059,7 +12059,7 @@
       <c r="AV30" s="36"/>
       <c r="AW30" s="36"/>
     </row>
-    <row r="31" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A31" s="41"/>
       <c r="B31" s="41"/>
       <c r="D31" s="41"/>
@@ -12107,7 +12107,7 @@
       <c r="AV31" s="36"/>
       <c r="AW31" s="36"/>
     </row>
-    <row r="32" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A32" s="41"/>
       <c r="B32" s="41"/>
       <c r="D32" s="41"/>
@@ -12156,7 +12156,7 @@
       <c r="AV32" s="36"/>
       <c r="AW32" s="36"/>
     </row>
-    <row r="33" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A33" s="41"/>
       <c r="B33" s="41"/>
       <c r="D33" s="41"/>
@@ -12205,7 +12205,7 @@
       <c r="AV33" s="36"/>
       <c r="AW33" s="36"/>
     </row>
-    <row r="34" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A34" s="41"/>
       <c r="B34" s="18"/>
       <c r="D34" s="41"/>
@@ -12254,7 +12254,7 @@
       <c r="AV34" s="36"/>
       <c r="AW34" s="36"/>
     </row>
-    <row r="35" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A35" s="41"/>
       <c r="B35" s="41"/>
       <c r="C35" s="41"/>
@@ -12297,7 +12297,7 @@
       <c r="AV35" s="36"/>
       <c r="AW35" s="36"/>
     </row>
-    <row r="36" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A36" s="41"/>
       <c r="B36" s="41"/>
       <c r="C36" s="41"/>
@@ -12317,7 +12317,7 @@
       <c r="X36" s="41"/>
       <c r="Y36" s="41"/>
     </row>
-    <row r="37" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A37" s="41"/>
       <c r="B37" s="41"/>
       <c r="C37" s="41"/>
@@ -12343,7 +12343,7 @@
       <c r="X37" s="41"/>
       <c r="Y37" s="41"/>
     </row>
-    <row r="38" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A38" s="41"/>
       <c r="B38" s="41"/>
       <c r="C38" s="41"/>
@@ -12369,7 +12369,7 @@
       <c r="X38" s="41"/>
       <c r="Y38" s="41"/>
     </row>
-    <row r="39" spans="1:49" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:49" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A39" s="41"/>
       <c r="B39" s="41"/>
       <c r="C39" s="41"/>
@@ -12397,7 +12397,7 @@
       <c r="Y39" s="41"/>
       <c r="AH39" s="3"/>
     </row>
-    <row r="40" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="41"/>
       <c r="B40" s="41"/>
       <c r="C40" s="1"/>
@@ -12425,7 +12425,7 @@
       <c r="Y40" s="41"/>
       <c r="AH40" s="3"/>
     </row>
-    <row r="41" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="41"/>
       <c r="B41" s="41"/>
       <c r="C41" s="41"/>
@@ -12453,7 +12453,7 @@
       <c r="Y41" s="41"/>
       <c r="AH41" s="3"/>
     </row>
-    <row r="42" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="41"/>
       <c r="B42" s="41"/>
       <c r="C42" s="41"/>
@@ -12481,7 +12481,7 @@
       <c r="Y42" s="41"/>
       <c r="AH42" s="3"/>
     </row>
-    <row r="43" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="41"/>
       <c r="B43" s="41"/>
       <c r="C43" s="41"/>
@@ -12508,7 +12508,7 @@
       <c r="Y43" s="41"/>
       <c r="AH43" s="3"/>
     </row>
-    <row r="44" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="41"/>
       <c r="B44" s="41"/>
       <c r="C44" s="41"/>
@@ -12535,7 +12535,7 @@
       <c r="Y44" s="41"/>
       <c r="AH44" s="3"/>
     </row>
-    <row r="45" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="41"/>
       <c r="B45" s="41"/>
       <c r="C45" s="41"/>
@@ -12562,7 +12562,7 @@
       <c r="Y45" s="41"/>
       <c r="AH45" s="3"/>
     </row>
-    <row r="46" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="41"/>
       <c r="B46" s="41"/>
       <c r="C46" s="41"/>
@@ -12589,7 +12589,7 @@
       <c r="Y46" s="41"/>
       <c r="AH46" s="3"/>
     </row>
-    <row r="47" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="41"/>
       <c r="B47" s="41"/>
       <c r="C47" s="41"/>
@@ -12616,7 +12616,7 @@
       <c r="Y47" s="41"/>
       <c r="AH47" s="3"/>
     </row>
-    <row r="48" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="41"/>
       <c r="B48" s="41"/>
       <c r="C48" s="41"/>
@@ -12643,7 +12643,7 @@
       <c r="Y48" s="41"/>
       <c r="AH48" s="3"/>
     </row>
-    <row r="49" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="41"/>
       <c r="B49" s="41"/>
       <c r="C49" s="41"/>
@@ -12670,7 +12670,7 @@
       <c r="Y49" s="41"/>
       <c r="AH49" s="3"/>
     </row>
-    <row r="50" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="41"/>
       <c r="B50" s="41"/>
       <c r="C50" s="41"/>
@@ -12697,7 +12697,7 @@
       <c r="Y50" s="41"/>
       <c r="AH50" s="3"/>
     </row>
-    <row r="51" spans="1:34" s="22" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:34" s="22" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="41"/>
       <c r="B51" s="41"/>
       <c r="C51" s="41"/>
@@ -12724,7 +12724,7 @@
       <c r="X51" s="36"/>
       <c r="Y51" s="36"/>
     </row>
-    <row r="52" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="41"/>
       <c r="B52" s="41"/>
       <c r="C52" s="41"/>
@@ -12752,7 +12752,7 @@
       <c r="Y52" s="41"/>
       <c r="AH52" s="3"/>
     </row>
-    <row r="53" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="41"/>
       <c r="B53" s="41"/>
       <c r="C53" s="41"/>
@@ -12774,7 +12774,7 @@
       <c r="Y53" s="41"/>
       <c r="AH53" s="3"/>
     </row>
-    <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="41"/>
       <c r="B54" s="41"/>
       <c r="C54" s="41"/>
@@ -12796,7 +12796,7 @@
       <c r="Y54" s="41"/>
       <c r="AH54" s="3"/>
     </row>
-    <row r="55" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="41"/>
       <c r="B55" s="41"/>
       <c r="C55" s="41"/>
@@ -12818,7 +12818,7 @@
       <c r="Y55" s="41"/>
       <c r="AH55" s="3"/>
     </row>
-    <row r="56" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="41"/>
       <c r="B56" s="41"/>
       <c r="C56" s="41"/>
@@ -12840,7 +12840,7 @@
       <c r="Y56" s="41"/>
       <c r="AH56" s="3"/>
     </row>
-    <row r="57" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="41"/>
       <c r="B57" s="41"/>
       <c r="C57" s="41"/>
@@ -12862,7 +12862,7 @@
       <c r="Y57" s="41"/>
       <c r="AH57" s="3"/>
     </row>
-    <row r="58" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="41"/>
       <c r="B58" s="41"/>
       <c r="C58" s="41"/>
@@ -12885,7 +12885,7 @@
       <c r="Y58" s="41"/>
       <c r="AH58" s="3"/>
     </row>
-    <row r="59" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="41"/>
       <c r="B59" s="41"/>
       <c r="J59" s="1"/>
@@ -12906,7 +12906,7 @@
       <c r="Y59" s="41"/>
       <c r="AH59" s="3"/>
     </row>
-    <row r="60" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="41"/>
       <c r="B60" s="41"/>
       <c r="D60" s="41"/>
@@ -12928,7 +12928,7 @@
       <c r="Y60" s="41"/>
       <c r="AH60" s="3"/>
     </row>
-    <row r="61" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="41"/>
       <c r="B61" s="41"/>
       <c r="D61" s="41"/>
@@ -12950,7 +12950,7 @@
       <c r="Y61" s="41"/>
       <c r="AH61" s="3"/>
     </row>
-    <row r="62" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="41"/>
       <c r="B62" s="41"/>
       <c r="D62" s="41"/>
@@ -12972,7 +12972,7 @@
       <c r="Y62" s="41"/>
       <c r="AH62" s="3"/>
     </row>
-    <row r="63" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="41"/>
       <c r="B63" s="41"/>
       <c r="D63" s="41"/>
@@ -12994,7 +12994,7 @@
       <c r="Y63" s="41"/>
       <c r="AH63" s="3"/>
     </row>
-    <row r="64" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="41"/>
       <c r="B64" s="41"/>
       <c r="D64" s="41"/>
@@ -13016,7 +13016,7 @@
       <c r="Y64" s="41"/>
       <c r="AH64" s="3"/>
     </row>
-    <row r="65" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="41"/>
       <c r="B65" s="41"/>
       <c r="D65" s="41"/>
@@ -13038,7 +13038,7 @@
       <c r="Y65" s="41"/>
       <c r="AH65" s="3"/>
     </row>
-    <row r="66" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="41"/>
       <c r="B66" s="41"/>
       <c r="D66" s="41"/>
@@ -13060,7 +13060,7 @@
       <c r="Y66" s="41"/>
       <c r="AH66" s="3"/>
     </row>
-    <row r="67" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="41"/>
       <c r="B67" s="41"/>
       <c r="D67" s="41"/>
@@ -13087,7 +13087,7 @@
       <c r="Y67" s="41"/>
       <c r="AH67" s="3"/>
     </row>
-    <row r="68" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="41"/>
       <c r="B68" s="41"/>
       <c r="D68" s="41"/>
@@ -13114,7 +13114,7 @@
       <c r="Y68" s="41"/>
       <c r="AH68" s="3"/>
     </row>
-    <row r="69" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="41"/>
       <c r="B69" s="41"/>
       <c r="D69" s="41"/>
@@ -13141,7 +13141,7 @@
       <c r="Y69" s="41"/>
       <c r="AH69" s="3"/>
     </row>
-    <row r="70" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="41"/>
       <c r="B70" s="41"/>
       <c r="D70" s="41"/>
@@ -13168,7 +13168,7 @@
       <c r="Y70" s="41"/>
       <c r="AH70" s="3"/>
     </row>
-    <row r="71" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="41"/>
       <c r="B71" s="41"/>
       <c r="D71" s="41"/>
@@ -13195,7 +13195,7 @@
       <c r="Y71" s="41"/>
       <c r="AH71" s="3"/>
     </row>
-    <row r="72" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="41"/>
       <c r="B72" s="41"/>
       <c r="D72" s="41"/>
@@ -13222,7 +13222,7 @@
       <c r="Y72" s="41"/>
       <c r="AH72" s="3"/>
     </row>
-    <row r="73" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="41"/>
       <c r="B73" s="41"/>
       <c r="D73" s="41"/>
@@ -13241,7 +13241,7 @@
       <c r="Q73" s="41"/>
       <c r="AH73" s="3"/>
     </row>
-    <row r="74" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="15"/>
       <c r="B74" s="1"/>
       <c r="C74" s="41"/>
@@ -13261,7 +13261,7 @@
       <c r="Q74" s="41"/>
       <c r="AH74" s="3"/>
     </row>
-    <row r="75" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="41"/>
       <c r="B75" s="2"/>
       <c r="C75" s="41"/>
@@ -13281,7 +13281,7 @@
       <c r="Q75" s="41"/>
       <c r="AH75" s="3"/>
     </row>
-    <row r="76" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="41"/>
       <c r="B76" s="2"/>
       <c r="C76" s="41"/>
@@ -13301,7 +13301,7 @@
       <c r="Q76" s="41"/>
       <c r="AH76" s="3"/>
     </row>
-    <row r="77" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="41"/>
       <c r="B77" s="2"/>
       <c r="C77" s="41"/>
@@ -13321,7 +13321,7 @@
       <c r="Q77" s="41"/>
       <c r="AH77" s="3"/>
     </row>
-    <row r="78" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="41"/>
       <c r="B78" s="2"/>
       <c r="C78" s="41"/>
@@ -13341,7 +13341,7 @@
       <c r="Q78" s="41"/>
       <c r="AH78" s="3"/>
     </row>
-    <row r="79" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="15"/>
       <c r="B79" s="15"/>
       <c r="C79" s="41"/>
@@ -13361,7 +13361,7 @@
       <c r="Q79" s="41"/>
       <c r="AH79" s="3"/>
     </row>
-    <row r="80" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="15"/>
       <c r="B80" s="15"/>
       <c r="C80" s="41"/>
@@ -13381,7 +13381,7 @@
       <c r="Q80" s="41"/>
       <c r="AH80" s="3"/>
     </row>
-    <row r="81" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="15"/>
       <c r="B81" s="15"/>
       <c r="C81" s="41"/>
@@ -13401,7 +13401,7 @@
       <c r="Q81" s="41"/>
       <c r="AH81" s="3"/>
     </row>
-    <row r="82" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="15"/>
       <c r="B82" s="15"/>
       <c r="C82" s="41"/>
@@ -13421,7 +13421,7 @@
       <c r="Q82" s="41"/>
       <c r="AH82" s="3"/>
     </row>
-    <row r="83" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="15"/>
       <c r="B83" s="15"/>
       <c r="C83" s="41"/>
@@ -13441,7 +13441,7 @@
       <c r="Q83" s="41"/>
       <c r="AH83" s="3"/>
     </row>
-    <row r="84" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="15"/>
       <c r="B84" s="15"/>
       <c r="C84" s="41"/>
@@ -13461,7 +13461,7 @@
       <c r="Q84" s="41"/>
       <c r="AH84" s="3"/>
     </row>
-    <row r="85" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="15"/>
       <c r="B85" s="15"/>
       <c r="C85" s="41"/>
@@ -13481,7 +13481,7 @@
       <c r="Q85" s="41"/>
       <c r="AH85" s="3"/>
     </row>
-    <row r="86" spans="1:34" s="22" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:34" s="22" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="15"/>
       <c r="B86" s="15"/>
       <c r="C86" s="41"/>
@@ -13500,7 +13500,7 @@
       <c r="P86" s="36"/>
       <c r="Q86" s="36"/>
     </row>
-    <row r="87" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="15"/>
       <c r="B87" s="1"/>
       <c r="C87" s="41"/>
@@ -13520,7 +13520,7 @@
       <c r="Q87" s="41"/>
       <c r="AH87" s="3"/>
     </row>
-    <row r="88" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="15"/>
       <c r="B88" s="1"/>
       <c r="C88" s="41"/>
@@ -13540,7 +13540,7 @@
       <c r="Q88" s="41"/>
       <c r="AH88" s="3"/>
     </row>
-    <row r="89" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="15"/>
       <c r="B89" s="1"/>
       <c r="C89" s="36"/>
@@ -13560,7 +13560,7 @@
       <c r="Q89" s="41"/>
       <c r="AH89" s="3"/>
     </row>
-    <row r="90" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="15"/>
       <c r="B90" s="1"/>
       <c r="C90" s="41"/>
@@ -13580,7 +13580,7 @@
       <c r="Q90" s="41"/>
       <c r="AH90" s="3"/>
     </row>
-    <row r="91" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="15"/>
       <c r="B91" s="1"/>
       <c r="C91" s="41"/>
@@ -13600,7 +13600,7 @@
       <c r="Q91" s="41"/>
       <c r="AH91" s="3"/>
     </row>
-    <row r="92" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="15"/>
       <c r="B92" s="1"/>
       <c r="C92" s="41"/>
@@ -13620,7 +13620,7 @@
       <c r="Q92" s="41"/>
       <c r="AH92" s="3"/>
     </row>
-    <row r="93" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="15"/>
       <c r="B93" s="1"/>
       <c r="C93" s="41"/>
@@ -13640,7 +13640,7 @@
       <c r="Q93" s="41"/>
       <c r="AH93" s="3"/>
     </row>
-    <row r="94" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="15"/>
       <c r="B94" s="1"/>
       <c r="C94" s="41"/>
@@ -13660,7 +13660,7 @@
       <c r="Q94" s="41"/>
       <c r="AH94" s="3"/>
     </row>
-    <row r="95" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="15"/>
       <c r="B95" s="1"/>
       <c r="C95" s="41"/>
@@ -13680,7 +13680,7 @@
       <c r="Q95" s="41"/>
       <c r="AH95" s="3"/>
     </row>
-    <row r="96" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="41"/>
       <c r="B96" s="2"/>
       <c r="C96" s="41"/>
@@ -13700,7 +13700,7 @@
       <c r="Q96" s="41"/>
       <c r="AH96" s="3"/>
     </row>
-    <row r="97" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="41"/>
       <c r="B97" s="2"/>
       <c r="C97" s="41"/>
@@ -13720,7 +13720,7 @@
       <c r="Q97" s="41"/>
       <c r="AH97" s="3"/>
     </row>
-    <row r="98" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="41"/>
       <c r="B98" s="2"/>
       <c r="C98" s="41"/>
@@ -13740,7 +13740,7 @@
       <c r="Q98" s="41"/>
       <c r="AH98" s="3"/>
     </row>
-    <row r="99" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="41"/>
       <c r="B99" s="2"/>
       <c r="C99" s="41"/>
@@ -13760,7 +13760,7 @@
       <c r="Q99" s="41"/>
       <c r="AH99" s="3"/>
     </row>
-    <row r="100" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="15"/>
       <c r="B100" s="1"/>
       <c r="C100" s="41"/>
@@ -13780,7 +13780,7 @@
       <c r="Q100" s="41"/>
       <c r="AH100" s="3"/>
     </row>
-    <row r="101" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="15"/>
       <c r="B101" s="1"/>
       <c r="C101" s="41"/>
@@ -13800,7 +13800,7 @@
       <c r="Q101" s="41"/>
       <c r="AH101" s="3"/>
     </row>
-    <row r="102" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="15"/>
       <c r="B102" s="1"/>
       <c r="C102" s="41"/>
@@ -13820,7 +13820,7 @@
       <c r="Q102" s="41"/>
       <c r="AH102" s="3"/>
     </row>
-    <row r="103" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="15"/>
       <c r="B103" s="1"/>
       <c r="C103" s="41"/>
@@ -13840,7 +13840,7 @@
       <c r="Q103" s="41"/>
       <c r="AH103" s="3"/>
     </row>
-    <row r="104" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="15"/>
       <c r="B104" s="1"/>
       <c r="C104" s="41"/>
@@ -13860,7 +13860,7 @@
       <c r="Q104" s="41"/>
       <c r="AH104" s="3"/>
     </row>
-    <row r="105" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="15"/>
       <c r="B105" s="1"/>
       <c r="C105" s="41"/>
@@ -13880,7 +13880,7 @@
       <c r="Q105" s="41"/>
       <c r="AH105" s="3"/>
     </row>
-    <row r="106" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="41"/>
       <c r="B106" s="2"/>
       <c r="C106" s="41"/>
@@ -13900,7 +13900,7 @@
       <c r="Q106" s="41"/>
       <c r="AH106" s="3"/>
     </row>
-    <row r="107" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="41"/>
       <c r="B107" s="2"/>
       <c r="C107" s="41"/>
@@ -13920,7 +13920,7 @@
       <c r="Q107" s="41"/>
       <c r="AH107" s="3"/>
     </row>
-    <row r="108" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="41"/>
       <c r="B108" s="2"/>
       <c r="C108" s="41"/>
@@ -13940,7 +13940,7 @@
       <c r="Q108" s="41"/>
       <c r="AH108" s="3"/>
     </row>
-    <row r="109" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="41"/>
       <c r="B109" s="2"/>
       <c r="C109" s="41"/>
@@ -13989,7 +13989,7 @@
       <c r="AV109" s="41"/>
       <c r="AW109" s="41"/>
     </row>
-    <row r="110" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="41"/>
       <c r="B110" s="41"/>
       <c r="C110" s="41"/>
@@ -14039,12 +14039,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AI25"/>
-  <sheetFormatPr defaultColWidth="4.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="4.81640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="4.83203125" style="14"/>
+    <col min="1" max="16384" width="4.81640625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:35" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="107" t="s">
         <v>225</v>
       </c>
@@ -14094,12 +14094,12 @@
       <c r="AF1" s="148"/>
       <c r="AG1" s="149">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>45061</v>
+        <v>45565</v>
       </c>
       <c r="AH1" s="150"/>
       <c r="AI1" s="151"/>
     </row>
-    <row r="2" spans="1:35" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:35" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="107" t="s">
         <v>228</v>
       </c>
@@ -14149,7 +14149,7 @@
       <c r="AH2" s="150"/>
       <c r="AI2" s="151"/>
     </row>
-    <row r="3" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A3" s="107" t="s">
         <v>230</v>
       </c>
@@ -14197,7 +14197,7 @@
       <c r="AH3" s="150"/>
       <c r="AI3" s="151"/>
     </row>
-    <row r="4" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -14234,7 +14234,7 @@
       <c r="AH4" s="1"/>
       <c r="AI4" s="1"/>
     </row>
-    <row r="5" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="B5" s="24" t="s">
         <v>245</v>
       </c>
@@ -14272,7 +14272,7 @@
       <c r="AH5" s="1"/>
       <c r="AI5" s="1"/>
     </row>
-    <row r="6" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="C6" s="24" t="s">
         <v>246</v>
@@ -14309,7 +14309,7 @@
       <c r="AH6" s="1"/>
       <c r="AI6" s="1"/>
     </row>
-    <row r="7" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="C7" s="24"/>
       <c r="E7" s="1"/>
@@ -14344,7 +14344,7 @@
       <c r="AH7" s="1"/>
       <c r="AI7" s="1"/>
     </row>
-    <row r="8" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
@@ -14382,7 +14382,7 @@
       <c r="AH8" s="1"/>
       <c r="AI8" s="1"/>
     </row>
-    <row r="9" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
@@ -14420,7 +14420,7 @@
       <c r="AH9" s="1"/>
       <c r="AI9" s="1"/>
     </row>
-    <row r="10" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -14456,7 +14456,7 @@
       <c r="AH10" s="1"/>
       <c r="AI10" s="1"/>
     </row>
-    <row r="11" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
@@ -14494,7 +14494,7 @@
       <c r="AH11" s="1"/>
       <c r="AI11" s="1"/>
     </row>
-    <row r="12" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
@@ -14532,8 +14532,8 @@
       <c r="AH12" s="1"/>
       <c r="AI12" s="1"/>
     </row>
-    <row r="13" spans="1:35" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="14" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:35" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="24" t="s">
@@ -14574,7 +14574,7 @@
       <c r="AH14" s="1"/>
       <c r="AI14" s="1"/>
     </row>
-    <row r="15" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -14611,7 +14611,7 @@
       <c r="AH15" s="1"/>
       <c r="AI15" s="1"/>
     </row>
-    <row r="16" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -14650,7 +14650,7 @@
       <c r="AH16" s="1"/>
       <c r="AI16" s="1"/>
     </row>
-    <row r="17" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -14687,7 +14687,7 @@
       <c r="AH17" s="1"/>
       <c r="AI17" s="1"/>
     </row>
-    <row r="18" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -14726,7 +14726,7 @@
       <c r="AH18" s="1"/>
       <c r="AI18" s="1"/>
     </row>
-    <row r="19" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -14765,7 +14765,7 @@
       <c r="AH19" s="1"/>
       <c r="AI19" s="1"/>
     </row>
-    <row r="20" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -14802,7 +14802,7 @@
       <c r="AH20" s="1"/>
       <c r="AI20" s="1"/>
     </row>
-    <row r="21" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -14841,7 +14841,7 @@
       <c r="AH21" s="1"/>
       <c r="AI21" s="1"/>
     </row>
-    <row r="22" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -14880,7 +14880,7 @@
       <c r="AH22" s="1"/>
       <c r="AI22" s="1"/>
     </row>
-    <row r="23" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -14917,7 +14917,7 @@
       <c r="AH23" s="1"/>
       <c r="AI23" s="1"/>
     </row>
-    <row r="24" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -14954,7 +14954,7 @@
       <c r="AH24" s="1"/>
       <c r="AI24" s="1"/>
     </row>
-    <row r="25" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -15033,12 +15033,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AK73"/>
-  <sheetFormatPr defaultColWidth="4.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="4.81640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="4.83203125" style="1"/>
+    <col min="1" max="16384" width="4.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:37" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="107" t="s">
         <v>225</v>
       </c>
@@ -15088,12 +15088,12 @@
       <c r="AF1" s="148"/>
       <c r="AG1" s="149">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>45061</v>
+        <v>45565</v>
       </c>
       <c r="AH1" s="150"/>
       <c r="AI1" s="151"/>
     </row>
-    <row r="2" spans="1:37" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:37" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="107" t="s">
         <v>228</v>
       </c>
@@ -15143,7 +15143,7 @@
       <c r="AH2" s="150"/>
       <c r="AI2" s="151"/>
     </row>
-    <row r="3" spans="1:37" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:37" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A3" s="107" t="s">
         <v>230</v>
       </c>
@@ -15191,16 +15191,16 @@
       <c r="AH3" s="150"/>
       <c r="AI3" s="151"/>
     </row>
-    <row r="4" spans="1:37" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:37" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:37" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:37" ht="10.75" x14ac:dyDescent="0.2">
       <c r="B5" s="24" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:37" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:37" ht="10.75" x14ac:dyDescent="0.2">
       <c r="B6" s="24"/>
     </row>
-    <row r="7" spans="1:37" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:37" ht="10.75" x14ac:dyDescent="0.2">
       <c r="C7" s="58" t="s">
         <v>120</v>
       </c>
@@ -15211,35 +15211,35 @@
       <c r="F7" s="37"/>
       <c r="G7" s="37"/>
     </row>
-    <row r="8" spans="1:37" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:37" ht="10.75" x14ac:dyDescent="0.2">
       <c r="C8" s="58"/>
       <c r="D8" s="24"/>
       <c r="E8" s="37"/>
       <c r="F8" s="37"/>
       <c r="G8" s="37"/>
     </row>
-    <row r="9" spans="1:37" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:37" ht="10.75" x14ac:dyDescent="0.2">
       <c r="C9" s="18"/>
       <c r="D9" s="24" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="10" spans="1:37" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:37" ht="10.75" x14ac:dyDescent="0.2">
       <c r="C10" s="18"/>
       <c r="D10" s="24" t="s">
         <v>307</v>
       </c>
       <c r="AK10" s="24"/>
     </row>
-    <row r="11" spans="1:37" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:37" ht="10.75" x14ac:dyDescent="0.2">
       <c r="C11" s="18"/>
       <c r="D11" s="73" t="s">
         <v>297</v>
       </c>
       <c r="AK11" s="24"/>
     </row>
-    <row r="12" spans="1:37" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="13" spans="1:37" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:37" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:37" ht="10.75" x14ac:dyDescent="0.2">
       <c r="C13" s="58" t="s">
         <v>295</v>
       </c>
@@ -15247,35 +15247,35 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:37" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:37" ht="10.75" x14ac:dyDescent="0.2">
       <c r="C14" s="18"/>
     </row>
-    <row r="15" spans="1:37" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:37" ht="10.75" x14ac:dyDescent="0.2">
       <c r="C15" s="18"/>
       <c r="D15" s="24" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="16" spans="1:37" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="17" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="18" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="19" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="20" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="21" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="22" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="23" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="24" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="25" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="26" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="27" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="28" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="29" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:37" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="17" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D29" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="31" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="30" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D31" s="169" t="s">
         <v>60</v>
       </c>
@@ -15312,7 +15312,7 @@
       <c r="AG31" s="170"/>
       <c r="AH31" s="171"/>
     </row>
-    <row r="32" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="32" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D32" s="175" t="s">
         <v>62</v>
       </c>
@@ -15349,7 +15349,7 @@
       <c r="AG32" s="185"/>
       <c r="AH32" s="186"/>
     </row>
-    <row r="33" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="33" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D33" s="178"/>
       <c r="E33" s="179"/>
       <c r="F33" s="179"/>
@@ -15382,7 +15382,7 @@
       <c r="AG33" s="188"/>
       <c r="AH33" s="189"/>
     </row>
-    <row r="34" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="34" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D34" s="178"/>
       <c r="E34" s="179"/>
       <c r="F34" s="179"/>
@@ -15415,7 +15415,7 @@
       <c r="AG34" s="188"/>
       <c r="AH34" s="189"/>
     </row>
-    <row r="35" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="35" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D35" s="181"/>
       <c r="E35" s="182"/>
       <c r="F35" s="182"/>
@@ -15448,7 +15448,7 @@
       <c r="AG35" s="191"/>
       <c r="AH35" s="192"/>
     </row>
-    <row r="36" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="36" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D36" s="175" t="s">
         <v>63</v>
       </c>
@@ -15485,7 +15485,7 @@
       <c r="AG36" s="194"/>
       <c r="AH36" s="195"/>
     </row>
-    <row r="37" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="37" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D37" s="178"/>
       <c r="E37" s="179"/>
       <c r="F37" s="179"/>
@@ -15518,7 +15518,7 @@
       <c r="AG37" s="197"/>
       <c r="AH37" s="198"/>
     </row>
-    <row r="38" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="38" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D38" s="178"/>
       <c r="E38" s="179"/>
       <c r="F38" s="179"/>
@@ -15551,7 +15551,7 @@
       <c r="AG38" s="197"/>
       <c r="AH38" s="198"/>
     </row>
-    <row r="39" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="39" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D39" s="181"/>
       <c r="E39" s="182"/>
       <c r="F39" s="182"/>
@@ -15584,7 +15584,7 @@
       <c r="AG39" s="200"/>
       <c r="AH39" s="201"/>
     </row>
-    <row r="40" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="40" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D40" s="175" t="s">
         <v>64</v>
       </c>
@@ -15621,7 +15621,7 @@
       <c r="AG40" s="194"/>
       <c r="AH40" s="195"/>
     </row>
-    <row r="41" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="41" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D41" s="178"/>
       <c r="E41" s="179"/>
       <c r="F41" s="179"/>
@@ -15654,7 +15654,7 @@
       <c r="AG41" s="197"/>
       <c r="AH41" s="198"/>
     </row>
-    <row r="42" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="42" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D42" s="178"/>
       <c r="E42" s="179"/>
       <c r="F42" s="179"/>
@@ -15687,7 +15687,7 @@
       <c r="AG42" s="197"/>
       <c r="AH42" s="198"/>
     </row>
-    <row r="43" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="43" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D43" s="181"/>
       <c r="E43" s="182"/>
       <c r="F43" s="182"/>
@@ -15720,7 +15720,7 @@
       <c r="AG43" s="200"/>
       <c r="AH43" s="201"/>
     </row>
-    <row r="44" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="44" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D44" s="25" t="s">
         <v>186</v>
       </c>
@@ -15728,19 +15728,19 @@
         <v>95</v>
       </c>
     </row>
-    <row r="45" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="46" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="45" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D46" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="47" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="47" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D47" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="48" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="49" spans="3:35" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="49" spans="3:35" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D49" s="203" t="s">
         <v>248</v>
       </c>
@@ -15788,7 +15788,7 @@
       <c r="AD49" s="173"/>
       <c r="AE49" s="174"/>
     </row>
-    <row r="50" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="50" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D50" s="95" t="s">
         <v>97</v>
       </c>
@@ -15836,7 +15836,7 @@
       <c r="AD50" s="96"/>
       <c r="AE50" s="97"/>
     </row>
-    <row r="51" spans="3:35" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="3:35" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D51" s="145" t="s">
         <v>52</v>
       </c>
@@ -15884,7 +15884,7 @@
       <c r="AD51" s="99"/>
       <c r="AE51" s="100"/>
     </row>
-    <row r="52" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="52" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D52" s="95" t="s">
         <v>98</v>
       </c>
@@ -15932,7 +15932,7 @@
       <c r="AD52" s="96"/>
       <c r="AE52" s="97"/>
     </row>
-    <row r="53" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="53" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D53" s="1" t="s">
         <v>121</v>
       </c>
@@ -15940,7 +15940,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="54" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="54" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D54" s="1" t="s">
         <v>15</v>
       </c>
@@ -15948,7 +15948,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="55" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="55" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D55" s="1" t="s">
         <v>16</v>
       </c>
@@ -15956,12 +15956,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="56" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="56" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="E56" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="57" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="57" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D57" s="1" t="s">
         <v>122</v>
       </c>
@@ -15994,7 +15994,7 @@
       <c r="AH57" s="23"/>
       <c r="AI57" s="23"/>
     </row>
-    <row r="58" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="58" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="J58" s="23"/>
       <c r="K58" s="23"/>
       <c r="L58" s="23"/>
@@ -16021,38 +16021,38 @@
       <c r="AG58" s="23"/>
       <c r="AH58" s="23"/>
     </row>
-    <row r="59" spans="3:35" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="60" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="59" spans="3:35" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="60" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="C60" s="58" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="61" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="61" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="C61" s="58"/>
     </row>
-    <row r="62" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="62" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D62" s="24" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="63" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="63" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D63" s="24"/>
     </row>
-    <row r="64" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="64" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="C64" s="58" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="65" spans="3:23" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="65" spans="3:23" ht="10.75" x14ac:dyDescent="0.2">
       <c r="C65" s="58"/>
     </row>
-    <row r="66" spans="3:23" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="66" spans="3:23" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D66" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="67" spans="3:23" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="68" spans="3:23" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="67" spans="3:23" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="68" spans="3:23" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D68" s="15" t="s">
         <v>11</v>
       </c>
@@ -16060,13 +16060,13 @@
         <v>93</v>
       </c>
     </row>
-    <row r="69" spans="3:23" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="69" spans="3:23" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D69" s="15"/>
       <c r="E69" s="1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="70" spans="3:23" s="17" customFormat="1" ht="12" x14ac:dyDescent="0.15">
+    <row r="70" spans="3:23" s="17" customFormat="1" ht="11.6" x14ac:dyDescent="0.2">
       <c r="E70" s="42" t="s">
         <v>221</v>
       </c>
@@ -16089,7 +16089,7 @@
       <c r="V70" s="16"/>
       <c r="W70" s="16"/>
     </row>
-    <row r="71" spans="3:23" s="17" customFormat="1" ht="12" x14ac:dyDescent="0.15">
+    <row r="71" spans="3:23" s="17" customFormat="1" ht="11.6" x14ac:dyDescent="0.2">
       <c r="E71" s="42" t="s">
         <v>222</v>
       </c>
@@ -16112,7 +16112,7 @@
       <c r="V71" s="16"/>
       <c r="W71" s="16"/>
     </row>
-    <row r="72" spans="3:23" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="72" spans="3:23" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D72" s="15" t="s">
         <v>12</v>
       </c>
@@ -16120,7 +16120,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="73" spans="3:23" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="73" spans="3:23" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D73" s="15" t="s">
         <v>94</v>
       </c>
@@ -16217,13 +16217,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AK194"/>
-  <sheetFormatPr defaultColWidth="4.83203125" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="4.81640625" defaultRowHeight="10.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="9" width="4.83203125" style="37" customWidth="1"/>
-    <col min="10" max="16384" width="4.83203125" style="37"/>
+    <col min="1" max="9" width="4.81640625" style="37" customWidth="1"/>
+    <col min="10" max="16384" width="4.81640625" style="37"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:35" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="107" t="s">
         <v>225</v>
       </c>
@@ -16273,12 +16273,12 @@
       <c r="AF1" s="148"/>
       <c r="AG1" s="149">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>45061</v>
+        <v>45565</v>
       </c>
       <c r="AH1" s="150"/>
       <c r="AI1" s="151"/>
     </row>
-    <row r="2" spans="1:35" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:35" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="107" t="s">
         <v>228</v>
       </c>
@@ -16328,7 +16328,7 @@
       <c r="AH2" s="150"/>
       <c r="AI2" s="151"/>
     </row>
-    <row r="3" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="107" t="s">
         <v>230</v>
       </c>
@@ -16376,14 +16376,14 @@
       <c r="AH3" s="150"/>
       <c r="AI3" s="151"/>
     </row>
-    <row r="4" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="6" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="7" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C7" s="18" t="s">
         <v>124</v>
       </c>
@@ -16391,52 +16391,52 @@
         <v>106</v>
       </c>
     </row>
-    <row r="8" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C8" s="18"/>
     </row>
-    <row r="9" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C9" s="18"/>
       <c r="D9" s="25" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="10" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C10" s="18"/>
       <c r="D10" s="24" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="11" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C11" s="18"/>
       <c r="D11" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="12" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C12" s="18"/>
     </row>
-    <row r="13" spans="1:35" s="25" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:35" s="25" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C13" s="26"/>
       <c r="D13" s="25" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="14" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C14" s="18"/>
       <c r="D14" s="25" t="s">
         <v>204</v>
       </c>
       <c r="E14" s="25"/>
     </row>
-    <row r="15" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C15" s="18"/>
       <c r="D15" s="25"/>
       <c r="E15" s="25"/>
     </row>
-    <row r="16" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C16" s="18"/>
     </row>
-    <row r="17" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C17" s="18" t="s">
         <v>17</v>
       </c>
@@ -16444,137 +16444,137 @@
         <v>162</v>
       </c>
     </row>
-    <row r="18" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C18" s="18"/>
     </row>
-    <row r="19" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C19" s="18"/>
       <c r="D19" s="24" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="20" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C20" s="18"/>
       <c r="D20" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="21" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C21" s="18"/>
     </row>
-    <row r="22" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C22" s="18"/>
     </row>
-    <row r="23" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C23" s="18"/>
     </row>
-    <row r="24" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C24" s="18"/>
     </row>
-    <row r="25" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C25" s="18"/>
     </row>
-    <row r="26" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C26" s="18"/>
     </row>
-    <row r="27" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C27" s="18"/>
       <c r="AK27" s="24"/>
     </row>
-    <row r="28" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C28" s="18"/>
       <c r="AK28" s="24"/>
     </row>
-    <row r="29" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C29" s="18"/>
       <c r="Z29" s="1" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="30" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C30" s="18"/>
     </row>
-    <row r="31" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C31" s="18"/>
     </row>
-    <row r="32" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C32" s="18"/>
     </row>
-    <row r="33" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C33" s="18"/>
     </row>
-    <row r="34" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C34" s="18"/>
     </row>
-    <row r="35" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C35" s="18"/>
     </row>
-    <row r="36" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C36" s="18"/>
       <c r="D36" s="74"/>
     </row>
-    <row r="37" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C37" s="18"/>
       <c r="D37" s="37"/>
     </row>
-    <row r="38" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C38" s="18"/>
     </row>
-    <row r="39" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C39" s="18"/>
     </row>
-    <row r="40" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C40" s="18"/>
     </row>
-    <row r="41" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C41" s="18"/>
     </row>
-    <row r="42" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C42" s="18"/>
       <c r="D42" s="24" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="43" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C43" s="18"/>
     </row>
-    <row r="44" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C44" s="18"/>
       <c r="E44" s="24" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="45" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C45" s="18"/>
       <c r="E45" s="24" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="46" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C46" s="18"/>
       <c r="E46" s="24" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="47" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C47" s="18"/>
     </row>
-    <row r="48" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C48" s="18"/>
       <c r="D48" s="24" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="49" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C49" s="18"/>
       <c r="D49" s="24" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="50" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C50" s="18"/>
     </row>
-    <row r="51" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C51" s="18"/>
       <c r="D51" s="75" t="s">
         <v>310</v>
@@ -16605,7 +16605,7 @@
       <c r="X51" s="78"/>
       <c r="Y51" s="77"/>
     </row>
-    <row r="52" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C52" s="18"/>
       <c r="D52" s="79" t="s">
         <v>313</v>
@@ -16636,7 +16636,7 @@
       <c r="X52" s="72"/>
       <c r="Y52" s="84"/>
     </row>
-    <row r="53" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C53" s="18"/>
       <c r="D53" s="85"/>
       <c r="E53" s="86"/>
@@ -16665,7 +16665,7 @@
       <c r="X53" s="72"/>
       <c r="Y53" s="84"/>
     </row>
-    <row r="54" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C54" s="18"/>
       <c r="D54" s="79" t="s">
         <v>316</v>
@@ -16696,7 +16696,7 @@
       <c r="X54" s="72"/>
       <c r="Y54" s="84"/>
     </row>
-    <row r="55" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C55" s="18"/>
       <c r="D55" s="85"/>
       <c r="E55" s="86"/>
@@ -16725,7 +16725,7 @@
       <c r="X55" s="72"/>
       <c r="Y55" s="84"/>
     </row>
-    <row r="56" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C56" s="18"/>
       <c r="D56" s="79" t="s">
         <v>318</v>
@@ -16756,7 +16756,7 @@
       <c r="X56" s="72"/>
       <c r="Y56" s="84"/>
     </row>
-    <row r="57" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C57" s="18"/>
       <c r="D57" s="88"/>
       <c r="E57" s="86"/>
@@ -16785,13 +16785,13 @@
       <c r="X57" s="72"/>
       <c r="Y57" s="84"/>
     </row>
-    <row r="58" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C58" s="18"/>
       <c r="D58" s="24"/>
       <c r="E58" s="24"/>
       <c r="I58" s="24"/>
     </row>
-    <row r="59" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C59" s="18"/>
       <c r="D59" s="24" t="s">
         <v>320</v>
@@ -16799,7 +16799,7 @@
       <c r="E59" s="24"/>
       <c r="I59" s="24"/>
     </row>
-    <row r="60" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C60" s="18"/>
       <c r="D60" s="24" t="s">
         <v>321</v>
@@ -16807,7 +16807,7 @@
       <c r="E60" s="24"/>
       <c r="I60" s="24"/>
     </row>
-    <row r="61" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C61" s="18"/>
       <c r="D61" s="24" t="s">
         <v>322</v>
@@ -16815,13 +16815,13 @@
       <c r="E61" s="24"/>
       <c r="I61" s="24"/>
     </row>
-    <row r="62" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C62" s="18"/>
       <c r="D62" s="24"/>
       <c r="E62" s="24"/>
       <c r="I62" s="24"/>
     </row>
-    <row r="63" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C63" s="18"/>
       <c r="D63" s="24" t="s">
         <v>323</v>
@@ -16829,7 +16829,7 @@
       <c r="E63" s="24"/>
       <c r="I63" s="24"/>
     </row>
-    <row r="64" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C64" s="18"/>
       <c r="D64" s="24" t="s">
         <v>324</v>
@@ -16837,13 +16837,13 @@
       <c r="E64" s="24"/>
       <c r="I64" s="24"/>
     </row>
-    <row r="65" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C65" s="18"/>
       <c r="D65" s="24"/>
       <c r="E65" s="24"/>
       <c r="I65" s="24"/>
     </row>
-    <row r="66" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C66" s="18"/>
       <c r="D66" s="24" t="s">
         <v>325</v>
@@ -16851,7 +16851,7 @@
       <c r="E66" s="24"/>
       <c r="I66" s="24"/>
     </row>
-    <row r="67" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C67" s="18"/>
       <c r="D67" s="24" t="s">
         <v>326</v>
@@ -16859,15 +16859,15 @@
       <c r="E67" s="24"/>
       <c r="I67" s="24"/>
     </row>
-    <row r="70" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C70" s="18" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="71" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C71" s="18"/>
     </row>
-    <row r="72" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C72" s="37"/>
       <c r="D72" s="37" t="s">
         <v>108</v>
@@ -16899,7 +16899,7 @@
       <c r="AC72" s="37"/>
       <c r="AD72" s="37"/>
     </row>
-    <row r="73" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C73" s="37"/>
       <c r="D73" s="37" t="s">
         <v>126</v>
@@ -16931,7 +16931,7 @@
       <c r="AC73" s="37"/>
       <c r="AD73" s="37"/>
     </row>
-    <row r="74" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
       <c r="E74" s="37"/>
@@ -16961,7 +16961,7 @@
       <c r="AC74" s="37"/>
       <c r="AD74" s="37"/>
     </row>
-    <row r="75" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C75" s="37"/>
       <c r="D75" s="37" t="s">
         <v>275</v>
@@ -16993,7 +16993,7 @@
       <c r="AC75" s="37"/>
       <c r="AD75" s="37"/>
     </row>
-    <row r="76" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C76" s="37"/>
       <c r="D76" s="37"/>
       <c r="E76" s="37"/>
@@ -17023,7 +17023,7 @@
       <c r="AC76" s="37"/>
       <c r="AD76" s="37"/>
     </row>
-    <row r="77" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C77" s="37"/>
       <c r="D77" s="37"/>
       <c r="E77" s="37" t="s">
@@ -17055,7 +17055,7 @@
       <c r="AC77" s="37"/>
       <c r="AD77" s="37"/>
     </row>
-    <row r="78" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C78" s="37"/>
       <c r="D78" s="37"/>
       <c r="E78" s="37"/>
@@ -17085,7 +17085,7 @@
       <c r="AC78" s="37"/>
       <c r="AD78" s="37"/>
     </row>
-    <row r="79" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C79" s="37"/>
       <c r="D79" s="37"/>
       <c r="E79" s="206" t="s">
@@ -17125,7 +17125,7 @@
       <c r="AG79" s="207"/>
       <c r="AH79" s="208"/>
     </row>
-    <row r="80" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C80" s="37"/>
       <c r="D80" s="37"/>
       <c r="E80" s="215" t="s">
@@ -17165,7 +17165,7 @@
       <c r="AG80" s="210"/>
       <c r="AH80" s="211"/>
     </row>
-    <row r="81" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C81" s="37"/>
       <c r="D81" s="37"/>
       <c r="E81" s="217"/>
@@ -17199,7 +17199,7 @@
       <c r="AG81" s="213"/>
       <c r="AH81" s="214"/>
     </row>
-    <row r="82" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C82" s="37"/>
       <c r="D82" s="37"/>
       <c r="E82" s="95" t="s">
@@ -17239,7 +17239,7 @@
       <c r="AG82" s="96"/>
       <c r="AH82" s="97"/>
     </row>
-    <row r="83" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C83" s="37"/>
       <c r="D83" s="37"/>
       <c r="E83" s="95" t="s">
@@ -17279,7 +17279,7 @@
       <c r="AG83" s="96"/>
       <c r="AH83" s="97"/>
     </row>
-    <row r="84" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
       <c r="E84" s="215" t="s">
@@ -17319,7 +17319,7 @@
       <c r="AG84" s="210"/>
       <c r="AH84" s="211"/>
     </row>
-    <row r="85" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C85" s="37"/>
       <c r="D85" s="37"/>
       <c r="E85" s="217"/>
@@ -17353,13 +17353,13 @@
       <c r="AG85" s="213"/>
       <c r="AH85" s="214"/>
     </row>
-    <row r="86" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C86" s="37"/>
       <c r="D86" s="37"/>
       <c r="AC86" s="37"/>
       <c r="AD86" s="37"/>
     </row>
-    <row r="87" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C87" s="37"/>
       <c r="D87" s="37" t="s">
         <v>276</v>
@@ -17367,27 +17367,27 @@
       <c r="AC87" s="37"/>
       <c r="AD87" s="37"/>
     </row>
-    <row r="88" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C88" s="37"/>
       <c r="D88" s="37"/>
       <c r="AC88" s="37"/>
       <c r="AD88" s="37"/>
     </row>
-    <row r="89" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="E89" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="90" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="91" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="91" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="E91" s="40" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="92" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="E92" s="40"/>
     </row>
-    <row r="93" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="E93" s="206" t="s">
         <v>116</v>
       </c>
@@ -17425,7 +17425,7 @@
       <c r="AG93" s="207"/>
       <c r="AH93" s="208"/>
     </row>
-    <row r="94" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="E94" s="215" t="s">
         <v>28</v>
       </c>
@@ -17463,7 +17463,7 @@
       <c r="AG94" s="210"/>
       <c r="AH94" s="211"/>
     </row>
-    <row r="95" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="E95" s="217"/>
       <c r="F95" s="220"/>
       <c r="G95" s="220"/>
@@ -17495,7 +17495,7 @@
       <c r="AG95" s="213"/>
       <c r="AH95" s="214"/>
     </row>
-    <row r="96" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="E96" s="95" t="s">
         <v>29</v>
       </c>
@@ -17533,7 +17533,7 @@
       <c r="AG96" s="96"/>
       <c r="AH96" s="97"/>
     </row>
-    <row r="97" spans="5:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="5:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="E97" s="95" t="s">
         <v>30</v>
       </c>
@@ -17571,7 +17571,7 @@
       <c r="AG97" s="96"/>
       <c r="AH97" s="97"/>
     </row>
-    <row r="98" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E98" s="215" t="s">
         <v>128</v>
       </c>
@@ -17609,7 +17609,7 @@
       <c r="AG98" s="210"/>
       <c r="AH98" s="211"/>
     </row>
-    <row r="99" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E99" s="217"/>
       <c r="F99" s="220"/>
       <c r="G99" s="220"/>
@@ -17641,33 +17641,33 @@
       <c r="AG99" s="213"/>
       <c r="AH99" s="214"/>
     </row>
-    <row r="100" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="101" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="102" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E102" s="40" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="103" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E103" s="40"/>
     </row>
-    <row r="104" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F104" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="105" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F105" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="106" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G106" s="24" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="107" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="108" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E108" s="206" t="s">
         <v>116</v>
       </c>
@@ -17705,7 +17705,7 @@
       <c r="AG108" s="207"/>
       <c r="AH108" s="208"/>
     </row>
-    <row r="109" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E109" s="215" t="s">
         <v>129</v>
       </c>
@@ -17743,7 +17743,7 @@
       <c r="AG109" s="210"/>
       <c r="AH109" s="211"/>
     </row>
-    <row r="110" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E110" s="217"/>
       <c r="F110" s="220"/>
       <c r="G110" s="220"/>
@@ -17775,7 +17775,7 @@
       <c r="AG110" s="213"/>
       <c r="AH110" s="214"/>
     </row>
-    <row r="111" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E111" s="215" t="s">
         <v>23</v>
       </c>
@@ -17813,7 +17813,7 @@
       <c r="AG111" s="210"/>
       <c r="AH111" s="211"/>
     </row>
-    <row r="112" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E112" s="221"/>
       <c r="F112" s="222"/>
       <c r="G112" s="222"/>
@@ -17845,7 +17845,7 @@
       <c r="AG112" s="229"/>
       <c r="AH112" s="230"/>
     </row>
-    <row r="113" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E113" s="221"/>
       <c r="F113" s="222"/>
       <c r="G113" s="222"/>
@@ -17877,7 +17877,7 @@
       <c r="AG113" s="229"/>
       <c r="AH113" s="230"/>
     </row>
-    <row r="114" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E114" s="221"/>
       <c r="F114" s="222"/>
       <c r="G114" s="222"/>
@@ -17909,7 +17909,7 @@
       <c r="AG114" s="229"/>
       <c r="AH114" s="230"/>
     </row>
-    <row r="115" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E115" s="217"/>
       <c r="F115" s="220"/>
       <c r="G115" s="220"/>
@@ -17941,52 +17941,52 @@
       <c r="AG115" s="213"/>
       <c r="AH115" s="214"/>
     </row>
-    <row r="116" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="117" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="118" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D118" s="37" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="119" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D119" s="37"/>
     </row>
-    <row r="120" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E120" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="121" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E121" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="122" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E122" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="123" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="124" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E124" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="125" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F125" s="24" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="126" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E127" s="40" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="128" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E128" s="40"/>
     </row>
-    <row r="129" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E129" s="206" t="s">
         <v>116</v>
       </c>
@@ -18024,7 +18024,7 @@
       <c r="AG129" s="207"/>
       <c r="AH129" s="208"/>
     </row>
-    <row r="130" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E130" s="215" t="s">
         <v>28</v>
       </c>
@@ -18062,7 +18062,7 @@
       <c r="AG130" s="210"/>
       <c r="AH130" s="211"/>
     </row>
-    <row r="131" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E131" s="217"/>
       <c r="F131" s="220"/>
       <c r="G131" s="220"/>
@@ -18094,7 +18094,7 @@
       <c r="AG131" s="213"/>
       <c r="AH131" s="214"/>
     </row>
-    <row r="132" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E132" s="215" t="s">
         <v>23</v>
       </c>
@@ -18132,7 +18132,7 @@
       <c r="AG132" s="210"/>
       <c r="AH132" s="211"/>
     </row>
-    <row r="133" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E133" s="221"/>
       <c r="F133" s="222"/>
       <c r="G133" s="222"/>
@@ -18164,7 +18164,7 @@
       <c r="AG133" s="229"/>
       <c r="AH133" s="230"/>
     </row>
-    <row r="134" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E134" s="217"/>
       <c r="F134" s="220"/>
       <c r="G134" s="220"/>
@@ -18196,17 +18196,17 @@
       <c r="AG134" s="213"/>
       <c r="AH134" s="214"/>
     </row>
-    <row r="135" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E137" s="40" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="138" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E138" s="40"/>
     </row>
-    <row r="139" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E139" s="206" t="s">
         <v>116</v>
       </c>
@@ -18244,7 +18244,7 @@
       <c r="AG139" s="207"/>
       <c r="AH139" s="208"/>
     </row>
-    <row r="140" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E140" s="215" t="s">
         <v>28</v>
       </c>
@@ -18282,7 +18282,7 @@
       <c r="AG140" s="210"/>
       <c r="AH140" s="211"/>
     </row>
-    <row r="141" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E141" s="217"/>
       <c r="F141" s="220"/>
       <c r="G141" s="220"/>
@@ -18314,7 +18314,7 @@
       <c r="AG141" s="213"/>
       <c r="AH141" s="214"/>
     </row>
-    <row r="142" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E142" s="215" t="s">
         <v>23</v>
       </c>
@@ -18352,7 +18352,7 @@
       <c r="AG142" s="210"/>
       <c r="AH142" s="211"/>
     </row>
-    <row r="143" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="143" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E143" s="221"/>
       <c r="F143" s="222"/>
       <c r="G143" s="222"/>
@@ -18384,7 +18384,7 @@
       <c r="AG143" s="229"/>
       <c r="AH143" s="230"/>
     </row>
-    <row r="144" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="144" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E144" s="221"/>
       <c r="F144" s="222"/>
       <c r="G144" s="222"/>
@@ -18416,7 +18416,7 @@
       <c r="AG144" s="229"/>
       <c r="AH144" s="230"/>
     </row>
-    <row r="145" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="145" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E145" s="217"/>
       <c r="F145" s="220"/>
       <c r="G145" s="220"/>
@@ -18448,7 +18448,7 @@
       <c r="AG145" s="213"/>
       <c r="AH145" s="214"/>
     </row>
-    <row r="146" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="146" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E146" s="215" t="s">
         <v>130</v>
       </c>
@@ -18486,7 +18486,7 @@
       <c r="AG146" s="210"/>
       <c r="AH146" s="211"/>
     </row>
-    <row r="147" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="147" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E147" s="221"/>
       <c r="F147" s="222"/>
       <c r="G147" s="222"/>
@@ -18518,7 +18518,7 @@
       <c r="AG147" s="229"/>
       <c r="AH147" s="230"/>
     </row>
-    <row r="148" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="148" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E148" s="217"/>
       <c r="F148" s="220"/>
       <c r="G148" s="220"/>
@@ -18550,7 +18550,7 @@
       <c r="AG148" s="213"/>
       <c r="AH148" s="214"/>
     </row>
-    <row r="149" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="149" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E149" s="215" t="s">
         <v>131</v>
       </c>
@@ -18571,7 +18571,7 @@
       <c r="AA149" s="37"/>
       <c r="AH149" s="44"/>
     </row>
-    <row r="150" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E150" s="221"/>
       <c r="F150" s="222"/>
       <c r="G150" s="222"/>
@@ -18588,7 +18588,7 @@
       <c r="AA150" s="37"/>
       <c r="AH150" s="44"/>
     </row>
-    <row r="151" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E151" s="221"/>
       <c r="F151" s="222"/>
       <c r="G151" s="222"/>
@@ -18605,7 +18605,7 @@
       <c r="AA151" s="37"/>
       <c r="AH151" s="44"/>
     </row>
-    <row r="152" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="152" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E152" s="221"/>
       <c r="F152" s="222"/>
       <c r="G152" s="222"/>
@@ -18621,7 +18621,7 @@
       <c r="AA152" s="37"/>
       <c r="AH152" s="44"/>
     </row>
-    <row r="153" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="153" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E153" s="221"/>
       <c r="F153" s="222"/>
       <c r="G153" s="222"/>
@@ -18638,7 +18638,7 @@
       <c r="AA153" s="37"/>
       <c r="AH153" s="44"/>
     </row>
-    <row r="154" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="154" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E154" s="221"/>
       <c r="F154" s="222"/>
       <c r="G154" s="222"/>
@@ -18656,7 +18656,7 @@
       <c r="AA154" s="37"/>
       <c r="AH154" s="44"/>
     </row>
-    <row r="155" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="155" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E155" s="221"/>
       <c r="F155" s="222"/>
       <c r="G155" s="222"/>
@@ -18674,7 +18674,7 @@
       <c r="AA155" s="37"/>
       <c r="AH155" s="44"/>
     </row>
-    <row r="156" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="156" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E156" s="221"/>
       <c r="F156" s="222"/>
       <c r="G156" s="222"/>
@@ -18692,7 +18692,7 @@
       <c r="AA156" s="37"/>
       <c r="AH156" s="44"/>
     </row>
-    <row r="157" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="157" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E157" s="221"/>
       <c r="F157" s="222"/>
       <c r="G157" s="222"/>
@@ -18710,7 +18710,7 @@
       <c r="AA157" s="37"/>
       <c r="AH157" s="44"/>
     </row>
-    <row r="158" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="158" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E158" s="221"/>
       <c r="F158" s="222"/>
       <c r="G158" s="222"/>
@@ -18728,7 +18728,7 @@
       <c r="AA158" s="37"/>
       <c r="AH158" s="44"/>
     </row>
-    <row r="159" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="159" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E159" s="221"/>
       <c r="F159" s="222"/>
       <c r="G159" s="222"/>
@@ -18746,7 +18746,7 @@
       <c r="AA159" s="37"/>
       <c r="AH159" s="44"/>
     </row>
-    <row r="160" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="160" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E160" s="221"/>
       <c r="F160" s="222"/>
       <c r="G160" s="222"/>
@@ -18764,7 +18764,7 @@
       <c r="AA160" s="37"/>
       <c r="AH160" s="44"/>
     </row>
-    <row r="161" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="161" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E161" s="221"/>
       <c r="F161" s="222"/>
       <c r="G161" s="222"/>
@@ -18782,7 +18782,7 @@
       <c r="AA161" s="37"/>
       <c r="AH161" s="44"/>
     </row>
-    <row r="162" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="162" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E162" s="217"/>
       <c r="F162" s="220"/>
       <c r="G162" s="220"/>
@@ -18800,7 +18800,7 @@
       <c r="AA162" s="37"/>
       <c r="AH162" s="44"/>
     </row>
-    <row r="163" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="163" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E163" s="215" t="s">
         <v>133</v>
       </c>
@@ -18838,7 +18838,7 @@
       <c r="AG163" s="210"/>
       <c r="AH163" s="211"/>
     </row>
-    <row r="164" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="164" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E164" s="217"/>
       <c r="F164" s="220"/>
       <c r="G164" s="220"/>
@@ -18870,7 +18870,7 @@
       <c r="AG164" s="213"/>
       <c r="AH164" s="214"/>
     </row>
-    <row r="165" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="165" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E165" s="209" t="s">
         <v>259</v>
       </c>
@@ -18908,7 +18908,7 @@
       <c r="AG165" s="219"/>
       <c r="AH165" s="216"/>
     </row>
-    <row r="166" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="166" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E166" s="212"/>
       <c r="F166" s="213"/>
       <c r="G166" s="213"/>
@@ -18940,31 +18940,31 @@
       <c r="AG166" s="220"/>
       <c r="AH166" s="218"/>
     </row>
-    <row r="167" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="167" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D169" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="170" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="170" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E171" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="172" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="172" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E172" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="173" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="173" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E173" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="174" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2"/>
-    <row r="175" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="174" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="E175" s="45" t="s">
         <v>134</v>
       </c>
@@ -18995,7 +18995,7 @@
       <c r="AD175" s="47"/>
       <c r="AE175" s="48"/>
     </row>
-    <row r="176" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="176" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E176" s="49"/>
       <c r="F176" s="37" t="s">
         <v>135</v>
@@ -19011,7 +19011,7 @@
       <c r="O176" s="37"/>
       <c r="AE176" s="50"/>
     </row>
-    <row r="177" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E177" s="49"/>
       <c r="F177" s="37"/>
       <c r="G177" s="37"/>
@@ -19027,7 +19027,7 @@
       <c r="O177" s="37"/>
       <c r="AE177" s="50"/>
     </row>
-    <row r="178" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E178" s="49"/>
       <c r="F178" s="37"/>
       <c r="G178" s="37"/>
@@ -19051,7 +19051,7 @@
       </c>
       <c r="AE178" s="50"/>
     </row>
-    <row r="179" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E179" s="49"/>
       <c r="F179" s="37"/>
       <c r="G179" s="37"/>
@@ -19070,7 +19070,7 @@
       </c>
       <c r="AE179" s="50"/>
     </row>
-    <row r="180" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E180" s="49"/>
       <c r="F180" s="37"/>
       <c r="G180" s="37"/>
@@ -19089,7 +19089,7 @@
       </c>
       <c r="AE180" s="50"/>
     </row>
-    <row r="181" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E181" s="49"/>
       <c r="F181" s="37"/>
       <c r="G181" s="37"/>
@@ -19108,7 +19108,7 @@
       </c>
       <c r="AE181" s="50"/>
     </row>
-    <row r="182" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E182" s="49"/>
       <c r="F182" s="37"/>
       <c r="G182" s="37"/>
@@ -19121,7 +19121,7 @@
       </c>
       <c r="AE182" s="50"/>
     </row>
-    <row r="183" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E183" s="49"/>
       <c r="F183" s="37"/>
       <c r="G183" s="37"/>
@@ -19137,7 +19137,7 @@
       <c r="O183" s="37"/>
       <c r="AE183" s="50"/>
     </row>
-    <row r="184" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E184" s="51"/>
       <c r="H184" s="37"/>
       <c r="I184" s="37"/>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="AE184" s="50"/>
     </row>
-    <row r="185" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E185" s="51"/>
       <c r="H185" s="37"/>
       <c r="I185" s="37"/>
@@ -19170,7 +19170,7 @@
       </c>
       <c r="AE185" s="50"/>
     </row>
-    <row r="186" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E186" s="51"/>
       <c r="H186" s="37"/>
       <c r="I186" s="37"/>
@@ -19184,7 +19184,7 @@
       </c>
       <c r="AE186" s="50"/>
     </row>
-    <row r="187" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E187" s="51"/>
       <c r="H187" s="37"/>
       <c r="I187" s="37"/>
@@ -19198,7 +19198,7 @@
       </c>
       <c r="AE187" s="50"/>
     </row>
-    <row r="188" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E188" s="51"/>
       <c r="H188" s="37"/>
       <c r="I188" s="37"/>
@@ -19212,7 +19212,7 @@
       </c>
       <c r="AE188" s="50"/>
     </row>
-    <row r="189" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E189" s="51"/>
       <c r="H189" s="37"/>
       <c r="I189" s="37"/>
@@ -19226,7 +19226,7 @@
       </c>
       <c r="AE189" s="50"/>
     </row>
-    <row r="190" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E190" s="52"/>
       <c r="F190" s="53"/>
       <c r="G190" s="53"/>
@@ -19255,8 +19255,8 @@
       <c r="AD190" s="53"/>
       <c r="AE190" s="54"/>
     </row>
-    <row r="191" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.15"/>
-    <row r="192" spans="1:31" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="192" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A192" s="27"/>
       <c r="B192" s="27"/>
       <c r="C192" s="27"/>
@@ -19283,7 +19283,7 @@
       <c r="X192" s="27"/>
       <c r="Y192" s="27"/>
     </row>
-    <row r="193" spans="1:25" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A193" s="27"/>
       <c r="B193" s="27"/>
       <c r="C193" s="27"/>
@@ -19310,7 +19310,7 @@
       <c r="X193" s="27"/>
       <c r="Y193" s="27"/>
     </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A194" s="27"/>
       <c r="B194" s="27"/>
       <c r="C194" s="27"/>
@@ -19451,13 +19451,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AJ162"/>
-  <sheetFormatPr defaultColWidth="4.83203125" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="4.81640625" defaultRowHeight="10.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="9" width="4.83203125" style="37" customWidth="1"/>
-    <col min="10" max="16384" width="4.83203125" style="37"/>
+    <col min="1" max="9" width="4.81640625" style="37" customWidth="1"/>
+    <col min="10" max="16384" width="4.81640625" style="37"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:35" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="107" t="s">
         <v>225</v>
       </c>
@@ -19507,12 +19507,12 @@
       <c r="AF1" s="148"/>
       <c r="AG1" s="149">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>45061</v>
+        <v>45565</v>
       </c>
       <c r="AH1" s="150"/>
       <c r="AI1" s="151"/>
     </row>
-    <row r="2" spans="1:35" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:35" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="107" t="s">
         <v>228</v>
       </c>
@@ -19562,7 +19562,7 @@
       <c r="AH2" s="150"/>
       <c r="AI2" s="151"/>
     </row>
-    <row r="3" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="107" t="s">
         <v>230</v>
       </c>
@@ -19610,40 +19610,40 @@
       <c r="AH3" s="150"/>
       <c r="AI3" s="151"/>
     </row>
-    <row r="4" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B5" s="24" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="6" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B6" s="24"/>
     </row>
-    <row r="7" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C7" s="24" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="8" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C8" s="18"/>
     </row>
-    <row r="9" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C9" s="18"/>
       <c r="D9" s="24" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="10" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C10" s="18"/>
       <c r="D10" s="24"/>
     </row>
-    <row r="11" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="D11" s="18"/>
       <c r="E11" s="24" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="E12" s="27"/>
       <c r="F12" s="27"/>
       <c r="G12" s="27"/>
@@ -19667,7 +19667,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="E13" s="63" t="s">
         <v>125</v>
       </c>
@@ -19718,7 +19718,7 @@
       <c r="AH13" s="260"/>
       <c r="AI13" s="261"/>
     </row>
-    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E14" s="62">
         <v>1</v>
       </c>
@@ -19767,7 +19767,7 @@
       <c r="AH14" s="263"/>
       <c r="AI14" s="274"/>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="E15" s="62">
         <v>2</v>
       </c>
@@ -19804,7 +19804,7 @@
       <c r="AH15" s="266"/>
       <c r="AI15" s="275"/>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="E16" s="62">
         <v>3</v>
       </c>
@@ -19841,7 +19841,7 @@
       <c r="AH16" s="266"/>
       <c r="AI16" s="275"/>
     </row>
-    <row r="17" spans="4:35" x14ac:dyDescent="0.15">
+    <row r="17" spans="4:35" x14ac:dyDescent="0.2">
       <c r="E17" s="62">
         <v>4</v>
       </c>
@@ -19878,7 +19878,7 @@
       <c r="AH17" s="266"/>
       <c r="AI17" s="275"/>
     </row>
-    <row r="18" spans="4:35" x14ac:dyDescent="0.15">
+    <row r="18" spans="4:35" x14ac:dyDescent="0.2">
       <c r="E18" s="62">
         <v>5</v>
       </c>
@@ -19917,7 +19917,7 @@
       <c r="AH18" s="266"/>
       <c r="AI18" s="275"/>
     </row>
-    <row r="19" spans="4:35" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="4:35" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E19" s="62">
         <v>6</v>
       </c>
@@ -19954,7 +19954,7 @@
       <c r="AH19" s="266"/>
       <c r="AI19" s="275"/>
     </row>
-    <row r="20" spans="4:35" x14ac:dyDescent="0.15">
+    <row r="20" spans="4:35" x14ac:dyDescent="0.2">
       <c r="E20" s="62">
         <v>7</v>
       </c>
@@ -19991,7 +19991,7 @@
       <c r="AH20" s="266"/>
       <c r="AI20" s="275"/>
     </row>
-    <row r="21" spans="4:35" x14ac:dyDescent="0.15">
+    <row r="21" spans="4:35" x14ac:dyDescent="0.2">
       <c r="E21" s="62">
         <v>8</v>
       </c>
@@ -20028,7 +20028,7 @@
       <c r="AH21" s="266"/>
       <c r="AI21" s="275"/>
     </row>
-    <row r="22" spans="4:35" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="4:35" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E22" s="62">
         <v>9</v>
       </c>
@@ -20067,7 +20067,7 @@
       <c r="AH22" s="266"/>
       <c r="AI22" s="275"/>
     </row>
-    <row r="23" spans="4:35" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="4:35" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E23" s="62">
         <v>10</v>
       </c>
@@ -20106,7 +20106,7 @@
       <c r="AH23" s="269"/>
       <c r="AI23" s="276"/>
     </row>
-    <row r="24" spans="4:35" x14ac:dyDescent="0.15">
+    <row r="24" spans="4:35" x14ac:dyDescent="0.2">
       <c r="E24" s="25"/>
       <c r="F24" s="29"/>
       <c r="G24" s="29"/>
@@ -20127,7 +20127,7 @@
       <c r="V24" s="30"/>
       <c r="W24" s="27"/>
     </row>
-    <row r="25" spans="4:35" x14ac:dyDescent="0.15">
+    <row r="25" spans="4:35" x14ac:dyDescent="0.2">
       <c r="E25" s="27" t="s">
         <v>262</v>
       </c>
@@ -20150,7 +20150,7 @@
       <c r="V25" s="27"/>
       <c r="W25" s="27"/>
     </row>
-    <row r="26" spans="4:35" x14ac:dyDescent="0.15">
+    <row r="26" spans="4:35" x14ac:dyDescent="0.2">
       <c r="E26" s="27"/>
       <c r="F26" s="27" t="s">
         <v>209</v>
@@ -20173,7 +20173,7 @@
       <c r="V26" s="27"/>
       <c r="W26" s="27"/>
     </row>
-    <row r="27" spans="4:35" x14ac:dyDescent="0.15">
+    <row r="27" spans="4:35" x14ac:dyDescent="0.2">
       <c r="E27" s="27"/>
       <c r="F27" s="27" t="s">
         <v>345</v>
@@ -20196,65 +20196,65 @@
       <c r="V27" s="27"/>
       <c r="W27" s="27"/>
     </row>
-    <row r="28" spans="4:35" x14ac:dyDescent="0.15">
+    <row r="28" spans="4:35" x14ac:dyDescent="0.2">
       <c r="F28" s="37" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="31" spans="4:35" x14ac:dyDescent="0.15">
+    <row r="31" spans="4:35" x14ac:dyDescent="0.2">
       <c r="D31" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="33" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="E33" s="59" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="34" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="F34" s="1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="35" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="36" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="36" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="F36" s="24" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="37" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="G37" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="38" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="G38" s="1" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="39" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="G39" s="1" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="40" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="41" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="G41" s="24" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="42" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H42" s="1" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="43" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="44" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H44" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="45" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H45" s="248" t="s">
         <v>77</v>
       </c>
@@ -20283,7 +20283,7 @@
       <c r="AC45" s="249"/>
       <c r="AD45" s="250"/>
     </row>
-    <row r="46" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H46" s="245" t="s">
         <v>139</v>
       </c>
@@ -20320,7 +20320,7 @@
       <c r="AC46" s="244"/>
       <c r="AD46" s="233"/>
     </row>
-    <row r="47" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H47" s="245" t="s">
         <v>143</v>
       </c>
@@ -20361,7 +20361,7 @@
       <c r="AC47" s="244"/>
       <c r="AD47" s="233"/>
     </row>
-    <row r="48" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H48" s="245" t="s">
         <v>145</v>
       </c>
@@ -20402,7 +20402,7 @@
       <c r="AC48" s="244"/>
       <c r="AD48" s="233"/>
     </row>
-    <row r="49" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H49" s="245" t="s">
         <v>147</v>
       </c>
@@ -20439,24 +20439,24 @@
       <c r="AC49" s="244"/>
       <c r="AD49" s="233"/>
     </row>
-    <row r="50" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="51" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="51" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="G51" s="24" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="52" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H52" s="1" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="53" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="54" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="54" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H54" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="55" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H55" s="248" t="s">
         <v>77</v>
       </c>
@@ -20490,7 +20490,7 @@
       <c r="AH55" s="249"/>
       <c r="AI55" s="250"/>
     </row>
-    <row r="56" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H56" s="245" t="s">
         <v>139</v>
       </c>
@@ -20536,7 +20536,7 @@
       <c r="AH56" s="244"/>
       <c r="AI56" s="233"/>
     </row>
-    <row r="57" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H57" s="245" t="s">
         <v>143</v>
       </c>
@@ -20578,7 +20578,7 @@
       <c r="AH57" s="244"/>
       <c r="AI57" s="233"/>
     </row>
-    <row r="58" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H58" s="245" t="s">
         <v>145</v>
       </c>
@@ -20628,7 +20628,7 @@
       <c r="AH58" s="244"/>
       <c r="AI58" s="233"/>
     </row>
-    <row r="59" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H59" s="245" t="s">
         <v>147</v>
       </c>
@@ -20666,51 +20666,51 @@
       <c r="AH59" s="244"/>
       <c r="AI59" s="233"/>
     </row>
-    <row r="60" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="61" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="62" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="61" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="62" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="G62" s="24" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="63" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H63" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="64" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="65" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="65" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="G65" s="24" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="66" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H66" s="1" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="67" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H67" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="68" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H68" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="69" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="70" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="70" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="G70" s="24" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="71" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H71" s="1" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="72" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H72" s="15" t="s">
         <v>11</v>
       </c>
@@ -20718,7 +20718,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="73" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H73" s="15" t="s">
         <v>11</v>
       </c>
@@ -20726,7 +20726,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="74" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H74" s="15" t="s">
         <v>11</v>
       </c>
@@ -20734,20 +20734,20 @@
         <v>200</v>
       </c>
     </row>
-    <row r="75" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H75" s="41" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="76" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H76" s="41"/>
     </row>
-    <row r="77" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H77" s="41" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="78" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H78" s="68" t="s">
         <v>77</v>
       </c>
@@ -20776,7 +20776,7 @@
       <c r="AC78" s="69"/>
       <c r="AD78" s="70"/>
     </row>
-    <row r="79" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H79" s="71" t="s">
         <v>139</v>
       </c>
@@ -20817,7 +20817,7 @@
       <c r="AC79" s="244"/>
       <c r="AD79" s="233"/>
     </row>
-    <row r="80" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H80" s="71" t="s">
         <v>143</v>
       </c>
@@ -20858,7 +20858,7 @@
       <c r="AC80" s="244"/>
       <c r="AD80" s="233"/>
     </row>
-    <row r="81" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H81" s="71" t="s">
         <v>145</v>
       </c>
@@ -20899,63 +20899,63 @@
       <c r="AC81" s="244"/>
       <c r="AD81" s="233"/>
     </row>
-    <row r="82" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H82" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="84" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="84" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="G84" s="24" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="85" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H85" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="86" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="87" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="87" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="G87" s="24" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="88" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H88" s="1" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="91" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C91" s="24" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="92" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C92" s="18"/>
     </row>
-    <row r="93" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C93" s="18"/>
       <c r="D93" s="24" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="94" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C94" s="18"/>
     </row>
-    <row r="95" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="D95" s="18"/>
       <c r="E95" s="24" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="96" spans="3:35" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="3:35" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="V96" s="38"/>
       <c r="AI96" s="38" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="97" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E97" s="64" t="s">
         <v>250</v>
       </c>
@@ -21004,7 +21004,7 @@
       <c r="AH97" s="173"/>
       <c r="AI97" s="174"/>
     </row>
-    <row r="98" spans="1:36" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:36" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E98" s="62">
         <v>1</v>
       </c>
@@ -21053,7 +21053,7 @@
       <c r="AH98" s="238"/>
       <c r="AI98" s="239"/>
     </row>
-    <row r="99" spans="1:36" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:36" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E99" s="62">
         <v>2</v>
       </c>
@@ -21098,7 +21098,7 @@
       <c r="AH99" s="238"/>
       <c r="AI99" s="239"/>
     </row>
-    <row r="100" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:36" x14ac:dyDescent="0.2">
       <c r="E100" s="25"/>
       <c r="F100" s="29"/>
       <c r="G100" s="29"/>
@@ -21119,7 +21119,7 @@
       <c r="V100" s="30"/>
       <c r="W100" s="27"/>
     </row>
-    <row r="101" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D101" t="s">
         <v>358</v>
       </c>
@@ -21143,7 +21143,7 @@
       <c r="V101" s="30"/>
       <c r="W101" s="27"/>
     </row>
-    <row r="102" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:36" x14ac:dyDescent="0.2">
       <c r="E102" s="25"/>
       <c r="F102" s="29"/>
       <c r="G102" s="29"/>
@@ -21164,7 +21164,7 @@
       <c r="V102" s="30"/>
       <c r="W102" s="27"/>
     </row>
-    <row r="103" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -21203,7 +21203,7 @@
       <c r="AI103" s="1"/>
       <c r="AJ103" s="1"/>
     </row>
-    <row r="104" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -21241,7 +21241,7 @@
       <c r="AI104" s="1"/>
       <c r="AJ104" s="1"/>
     </row>
-    <row r="105" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -21277,7 +21277,7 @@
       <c r="AI105" s="1"/>
       <c r="AJ105" s="1"/>
     </row>
-    <row r="106" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -21316,7 +21316,7 @@
       <c r="AI106" s="1"/>
       <c r="AJ106" s="1"/>
     </row>
-    <row r="107" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -21355,7 +21355,7 @@
       <c r="AI107" s="1"/>
       <c r="AJ107" s="1"/>
     </row>
-    <row r="108" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -21392,7 +21392,7 @@
       <c r="AI108" s="1"/>
       <c r="AJ108" s="1"/>
     </row>
-    <row r="109" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -21431,7 +21431,7 @@
       <c r="AI109" s="1"/>
       <c r="AJ109" s="1"/>
     </row>
-    <row r="110" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -21470,7 +21470,7 @@
       <c r="AI110" s="1"/>
       <c r="AJ110" s="1"/>
     </row>
-    <row r="111" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -21509,7 +21509,7 @@
       <c r="AI111" s="1"/>
       <c r="AJ111" s="1"/>
     </row>
-    <row r="112" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -21547,7 +21547,7 @@
       <c r="AI112" s="1"/>
       <c r="AJ112" s="1"/>
     </row>
-    <row r="113" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -21584,36 +21584,36 @@
       <c r="AH113" s="1"/>
       <c r="AI113" s="1"/>
     </row>
-    <row r="114" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C114" s="24" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="115" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C115" s="18"/>
     </row>
-    <row r="116" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C116" s="18"/>
       <c r="D116" s="24" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="117" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C117" s="18"/>
     </row>
-    <row r="118" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="D118" s="18"/>
       <c r="E118" s="24" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="119" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="V119" s="38"/>
       <c r="AI119" s="38" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="120" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E120" s="64" t="s">
         <v>250</v>
       </c>
@@ -21662,7 +21662,7 @@
       <c r="AH120" s="173"/>
       <c r="AI120" s="174"/>
     </row>
-    <row r="121" spans="1:36" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:36" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E121" s="62">
         <v>1</v>
       </c>
@@ -21711,7 +21711,7 @@
       <c r="AH121" s="238"/>
       <c r="AI121" s="239"/>
     </row>
-    <row r="122" spans="1:36" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:36" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E122" s="62">
         <v>2</v>
       </c>
@@ -21756,7 +21756,7 @@
       <c r="AH122" s="238"/>
       <c r="AI122" s="239"/>
     </row>
-    <row r="123" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:36" x14ac:dyDescent="0.2">
       <c r="E123" s="25"/>
       <c r="F123" s="29"/>
       <c r="G123" s="29"/>
@@ -21777,7 +21777,7 @@
       <c r="V123" s="30"/>
       <c r="W123" s="27"/>
     </row>
-    <row r="124" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D124" t="s">
         <v>363</v>
       </c>
@@ -21801,7 +21801,7 @@
       <c r="V124" s="30"/>
       <c r="W124" s="27"/>
     </row>
-    <row r="125" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:36" x14ac:dyDescent="0.2">
       <c r="E125" s="25"/>
       <c r="F125" s="29"/>
       <c r="G125" s="29"/>
@@ -21822,7 +21822,7 @@
       <c r="V125" s="30"/>
       <c r="W125" s="27"/>
     </row>
-    <row r="126" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -21861,7 +21861,7 @@
       <c r="AI126" s="1"/>
       <c r="AJ126" s="1"/>
     </row>
-    <row r="127" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -21899,7 +21899,7 @@
       <c r="AI127" s="1"/>
       <c r="AJ127" s="1"/>
     </row>
-    <row r="128" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -21935,7 +21935,7 @@
       <c r="AI128" s="1"/>
       <c r="AJ128" s="1"/>
     </row>
-    <row r="129" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -21974,7 +21974,7 @@
       <c r="AI129" s="1"/>
       <c r="AJ129" s="1"/>
     </row>
-    <row r="130" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -22013,7 +22013,7 @@
       <c r="AI130" s="1"/>
       <c r="AJ130" s="1"/>
     </row>
-    <row r="131" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -22050,7 +22050,7 @@
       <c r="AI131" s="1"/>
       <c r="AJ131" s="1"/>
     </row>
-    <row r="132" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -22089,7 +22089,7 @@
       <c r="AI132" s="1"/>
       <c r="AJ132" s="1"/>
     </row>
-    <row r="133" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -22128,7 +22128,7 @@
       <c r="AI133" s="1"/>
       <c r="AJ133" s="1"/>
     </row>
-    <row r="134" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -22167,7 +22167,7 @@
       <c r="AI134" s="1"/>
       <c r="AJ134" s="1"/>
     </row>
-    <row r="135" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -22205,35 +22205,35 @@
       <c r="AI135" s="1"/>
       <c r="AJ135" s="1"/>
     </row>
-    <row r="137" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C137" s="24" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="138" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="D138" s="18"/>
     </row>
-    <row r="139" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="D139" s="58" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="140" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="D140" s="18"/>
     </row>
-    <row r="141" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="D141" s="18"/>
       <c r="E141" s="24" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="142" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="V142" s="38"/>
       <c r="AI142" s="38" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="143" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E143" s="64" t="s">
         <v>250</v>
       </c>
@@ -22282,7 +22282,7 @@
       <c r="AH143" s="173"/>
       <c r="AI143" s="174"/>
     </row>
-    <row r="144" spans="1:36" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:36" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E144" s="62">
         <v>1</v>
       </c>
@@ -22331,7 +22331,7 @@
       <c r="AH144" s="238"/>
       <c r="AI144" s="239"/>
     </row>
-    <row r="145" spans="1:36" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:36" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E145" s="62">
         <v>2</v>
       </c>
@@ -22376,7 +22376,7 @@
       <c r="AH145" s="238"/>
       <c r="AI145" s="239"/>
     </row>
-    <row r="146" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:36" x14ac:dyDescent="0.2">
       <c r="E146" s="25"/>
       <c r="F146" s="29"/>
       <c r="G146" s="29"/>
@@ -22397,7 +22397,7 @@
       <c r="V146" s="30"/>
       <c r="W146" s="27"/>
     </row>
-    <row r="147" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D147" t="s">
         <v>365</v>
       </c>
@@ -22421,7 +22421,7 @@
       <c r="V147" s="30"/>
       <c r="W147" s="27"/>
     </row>
-    <row r="148" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:36" x14ac:dyDescent="0.2">
       <c r="E148" s="25"/>
       <c r="F148" s="29"/>
       <c r="G148" s="29"/>
@@ -22442,7 +22442,7 @@
       <c r="V148" s="30"/>
       <c r="W148" s="27"/>
     </row>
-    <row r="149" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -22481,7 +22481,7 @@
       <c r="AI149" s="1"/>
       <c r="AJ149" s="1"/>
     </row>
-    <row r="150" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -22519,7 +22519,7 @@
       <c r="AI150" s="1"/>
       <c r="AJ150" s="1"/>
     </row>
-    <row r="151" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -22555,7 +22555,7 @@
       <c r="AI151" s="1"/>
       <c r="AJ151" s="1"/>
     </row>
-    <row r="152" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -22594,7 +22594,7 @@
       <c r="AI152" s="1"/>
       <c r="AJ152" s="1"/>
     </row>
-    <row r="153" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -22633,7 +22633,7 @@
       <c r="AI153" s="1"/>
       <c r="AJ153" s="1"/>
     </row>
-    <row r="154" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -22670,7 +22670,7 @@
       <c r="AI154" s="1"/>
       <c r="AJ154" s="1"/>
     </row>
-    <row r="155" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -22709,7 +22709,7 @@
       <c r="AI155" s="1"/>
       <c r="AJ155" s="1"/>
     </row>
-    <row r="156" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -22748,7 +22748,7 @@
       <c r="AI156" s="1"/>
       <c r="AJ156" s="1"/>
     </row>
-    <row r="157" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -22787,7 +22787,7 @@
       <c r="AI157" s="1"/>
       <c r="AJ157" s="1"/>
     </row>
-    <row r="158" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -22825,7 +22825,7 @@
       <c r="AI158" s="1"/>
       <c r="AJ158" s="1"/>
     </row>
-    <row r="160" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A160" s="27"/>
       <c r="B160" s="27"/>
       <c r="C160" s="27"/>
@@ -22852,7 +22852,7 @@
       <c r="X160" s="27"/>
       <c r="Y160" s="27"/>
     </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A161" s="27"/>
       <c r="B161" s="27"/>
       <c r="C161" s="27"/>
@@ -22879,7 +22879,7 @@
       <c r="X161" s="27"/>
       <c r="Y161" s="27"/>
     </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A162" s="27"/>
       <c r="B162" s="27"/>
       <c r="C162" s="27"/>

--- a/020_アプリケーション開発標準/020_テスト標準/単体テスト標準.xlsx
+++ b/020_アプリケーション開発標準/020_テスト標準/単体テスト標準.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD594ABF-9C60-45F3-A03F-1E1E3836C12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D0F957-52F8-4FD8-AC8F-6190719590AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="1860" windowWidth="25800" windowHeight="13710" tabRatio="641" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="754" yWindow="754" windowWidth="24686" windowHeight="13260" tabRatio="641" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="33" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="368">
   <si>
     <t>更新</t>
     <rPh sb="0" eb="2">
@@ -4186,6 +4186,13 @@
       <t>ハン</t>
     </rPh>
     <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1.2. 参照ドキュメント</t>
+    <rPh sb="5" eb="7">
+      <t>サンショウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
@@ -5703,8 +5710,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7753350" y="390525"/>
-          <a:ext cx="1390650" cy="581025"/>
+          <a:off x="8100332" y="387804"/>
+          <a:ext cx="1460047" cy="570139"/>
           <a:chOff x="809" y="41"/>
           <a:chExt cx="143" cy="61"/>
         </a:xfrm>
@@ -8375,39 +8382,39 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:S512"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="13.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="8.83203125" style="7"/>
+    <col min="1" max="16384" width="8.81640625" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B1" s="8"/>
       <c r="C1" s="9"/>
     </row>
-    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
     </row>
-    <row r="3" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="4" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="6" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="7" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="8" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="9" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="10" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="11" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="12" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="13" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="14" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="15" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="16" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="17" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="18" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="19" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="20" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="21" spans="6:12" ht="9" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="22" spans="6:12" ht="9" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="23" spans="6:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="6:12" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="6:12" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="6:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
@@ -8418,7 +8425,7 @@
       <c r="K23" s="33"/>
       <c r="L23" s="33"/>
     </row>
-    <row r="24" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F24" s="10"/>
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
@@ -8427,19 +8434,19 @@
       <c r="K24" s="33"/>
       <c r="L24" s="33"/>
     </row>
-    <row r="25" spans="6:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="6:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
       <c r="I25" s="94">
         <f ca="1">IF(INDIRECT("変更履歴!D8")="","",MAX(INDIRECT("変更履歴!D8"):INDIRECT("変更履歴!F33")))</f>
-        <v>43336</v>
+        <v>45565</v>
       </c>
       <c r="J25" s="94"/>
       <c r="K25" s="94"/>
       <c r="L25" s="33"/>
     </row>
-    <row r="26" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
       <c r="H26" s="10"/>
@@ -8448,7 +8455,7 @@
       <c r="K26" s="33"/>
       <c r="L26" s="33"/>
     </row>
-    <row r="27" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
       <c r="H27" s="10"/>
@@ -8457,7 +8464,7 @@
       <c r="K27" s="33"/>
       <c r="L27" s="33"/>
     </row>
-    <row r="28" spans="6:12" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="6:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F28" s="10"/>
       <c r="H28" s="10"/>
       <c r="I28" s="33"/>
@@ -8465,7 +8472,7 @@
       <c r="K28" s="33"/>
       <c r="L28" s="33"/>
     </row>
-    <row r="29" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F29" s="10"/>
       <c r="G29" s="11"/>
       <c r="H29" s="10"/>
@@ -8474,7 +8481,7 @@
       <c r="K29" s="33"/>
       <c r="L29" s="33"/>
     </row>
-    <row r="30" spans="6:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="6:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F30" s="10"/>
       <c r="G30" s="11"/>
       <c r="H30" s="10"/>
@@ -8483,7 +8490,7 @@
       <c r="K30" s="33"/>
       <c r="L30" s="33"/>
     </row>
-    <row r="31" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="6:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F31" s="10"/>
       <c r="G31" s="11"/>
       <c r="H31" s="10"/>
@@ -8492,7 +8499,7 @@
       <c r="K31" s="33"/>
       <c r="L31" s="33"/>
     </row>
-    <row r="32" spans="6:12" ht="18.75" x14ac:dyDescent="0.2">
+    <row r="32" spans="6:12" ht="18.45" x14ac:dyDescent="0.3">
       <c r="F32" s="10"/>
       <c r="G32" s="11"/>
       <c r="H32" s="10"/>
@@ -8503,7 +8510,7 @@
       <c r="K32" s="33"/>
       <c r="L32" s="33"/>
     </row>
-    <row r="33" spans="6:19" ht="18.75" x14ac:dyDescent="0.2">
+    <row r="33" spans="6:19" ht="18.45" x14ac:dyDescent="0.3">
       <c r="F33" s="10"/>
       <c r="H33" s="10"/>
       <c r="I33" s="33"/>
@@ -8515,7 +8522,7 @@
       <c r="O33" s="12"/>
       <c r="P33" s="12"/>
     </row>
-    <row r="34" spans="6:19" ht="18.75" x14ac:dyDescent="0.2">
+    <row r="34" spans="6:19" ht="18.45" x14ac:dyDescent="0.3">
       <c r="F34" s="10"/>
       <c r="H34" s="10"/>
       <c r="I34" s="33"/>
@@ -8532,504 +8539,504 @@
       <c r="R34" s="92"/>
       <c r="S34" s="92"/>
     </row>
-    <row r="35" spans="6:19" x14ac:dyDescent="0.15">
+    <row r="35" spans="6:19" x14ac:dyDescent="0.25">
       <c r="Q35" s="92"/>
       <c r="R35" s="92"/>
       <c r="S35" s="92"/>
     </row>
-    <row r="36" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Q36" s="93"/>
       <c r="R36" s="92"/>
       <c r="S36" s="32"/>
     </row>
-    <row r="37" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Q37" s="89"/>
       <c r="R37" s="90"/>
       <c r="S37" s="89"/>
     </row>
-    <row r="38" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Q38" s="90"/>
       <c r="R38" s="90"/>
       <c r="S38" s="90"/>
     </row>
-    <row r="39" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="Q39" s="90"/>
       <c r="R39" s="90"/>
       <c r="S39" s="90"/>
     </row>
-    <row r="40" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="41" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="42" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="43" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="44" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="45" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="46" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="47" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="48" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="49" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="50" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="51" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="52" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="53" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="54" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="55" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="56" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="57" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="58" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="59" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="60" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="61" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="62" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="63" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="64" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="65" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="66" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="67" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="68" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="69" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="70" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="71" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="72" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="73" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="74" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="75" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="76" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="77" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="78" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="79" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="80" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="81" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="82" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="83" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="84" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="85" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="86" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="87" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="88" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="89" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="90" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="91" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="92" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="93" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="94" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="95" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="96" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="97" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="98" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="99" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="100" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="101" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="102" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="103" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="104" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="105" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="106" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="107" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="108" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="109" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="110" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="111" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="112" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="113" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="114" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="115" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="116" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="117" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="118" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="119" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="120" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="121" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="122" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="123" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="124" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="125" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="126" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="40" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="6:19" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="116" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="117" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="118" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="119" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="120" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="121" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="122" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="123" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="124" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="125" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="126" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="127" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="128" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="129" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="130" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="131" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="132" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="133" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="134" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="135" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="136" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="137" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="138" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="139" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="140" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="141" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="142" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="143" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="144" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="145" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="146" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="147" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="148" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="149" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="150" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="151" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="152" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="153" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="154" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="155" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="156" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="157" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="158" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="159" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="160" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="161" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="162" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="163" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="164" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="165" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="166" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="167" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="168" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="169" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="170" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="171" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="172" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="173" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="174" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="175" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="176" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="177" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="178" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="179" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="180" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="181" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="182" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="183" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="184" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="185" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="186" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="187" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="188" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="189" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="190" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="191" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="192" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="193" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="194" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="195" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="196" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="197" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="198" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="199" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="200" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="201" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="202" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="203" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="204" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="205" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="206" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="207" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="208" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="209" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="210" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="211" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="212" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="213" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="214" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="215" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="216" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="217" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="218" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="219" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="220" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="221" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="222" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="223" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="224" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="225" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="226" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="227" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="228" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="229" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="230" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="231" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="232" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="233" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="234" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="235" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="236" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="237" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="238" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="239" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="240" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="241" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="242" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="243" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="244" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="245" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="246" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="247" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="248" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="249" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="250" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="251" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="252" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="253" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="254" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="255" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="256" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="257" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="258" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="259" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="260" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="261" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="262" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="263" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="264" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="265" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="266" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="267" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="268" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="269" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="270" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="271" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="272" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="273" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="274" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="275" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="276" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="277" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="278" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="279" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="280" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="281" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="282" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="283" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="284" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="285" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="286" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="287" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="288" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="289" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="290" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="291" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="292" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="293" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="294" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="295" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="296" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="297" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="298" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="299" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="300" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="301" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="302" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="303" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="304" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="305" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="306" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="307" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="308" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="309" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="310" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="311" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="312" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="313" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="314" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="315" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="316" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="317" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="318" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="319" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="320" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="321" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="322" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="323" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="324" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="325" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="326" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="327" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="328" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="329" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="330" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="331" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="332" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="333" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="334" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="335" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="336" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="337" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="338" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="339" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="340" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="341" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="342" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="343" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="344" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="345" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="346" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="347" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="348" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="349" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="350" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="351" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="352" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="353" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="354" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="355" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="356" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="357" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="358" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="359" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="360" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="361" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="362" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="363" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="364" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="365" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="366" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="367" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="368" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="369" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="370" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="371" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="372" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="373" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="374" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="375" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="376" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="377" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="378" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="379" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="380" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="381" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="382" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="383" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="384" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="385" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="386" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="387" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="388" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="389" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="390" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="391" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="392" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="393" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="394" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="395" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="396" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="397" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="398" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="399" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="400" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="401" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="402" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="403" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="404" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="405" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="406" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="407" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="408" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="409" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="410" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="411" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="412" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="413" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="414" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="415" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="416" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="417" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="418" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="419" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="420" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="421" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="422" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="423" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="424" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="425" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="426" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="427" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="428" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="429" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="430" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="431" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="432" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="433" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="434" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="435" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="436" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="437" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="438" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="439" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="440" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="441" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="442" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="443" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="444" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="445" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="446" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="447" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="448" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="449" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="450" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="451" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="452" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="453" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="454" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="455" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="456" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="457" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="458" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="459" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="460" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="461" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="462" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="463" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="464" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="465" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="466" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="467" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="468" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="469" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="470" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="471" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="472" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="473" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="474" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="475" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="476" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="477" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="478" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="479" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="480" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="481" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="482" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="483" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="484" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="485" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="486" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="487" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="488" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="489" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="490" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="491" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="492" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="493" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="494" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="500" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="501" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="502" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="503" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="504" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="505" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="506" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="507" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="508" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="509" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="510" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="511" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="512" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="Q37:R39"/>
@@ -9053,16 +9060,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AN33"/>
-  <sheetFormatPr defaultColWidth="4.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="4.81640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16" width="4.83203125" style="19" customWidth="1"/>
-    <col min="17" max="17" width="4.83203125" style="21" customWidth="1"/>
-    <col min="18" max="34" width="4.83203125" style="19" customWidth="1"/>
-    <col min="35" max="35" width="4.83203125" style="21" customWidth="1"/>
-    <col min="36" max="16384" width="4.83203125" style="19"/>
+    <col min="1" max="16" width="4.81640625" style="19" customWidth="1"/>
+    <col min="17" max="17" width="4.81640625" style="21" customWidth="1"/>
+    <col min="18" max="34" width="4.81640625" style="19" customWidth="1"/>
+    <col min="35" max="35" width="4.81640625" style="21" customWidth="1"/>
+    <col min="36" max="16384" width="4.81640625" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="107" t="s">
         <v>225</v>
       </c>
@@ -9110,7 +9117,7 @@
       <c r="AF1" s="148"/>
       <c r="AG1" s="149">
         <f>IF(D8="","",D8)</f>
-        <v>43336</v>
+        <v>45565</v>
       </c>
       <c r="AH1" s="150"/>
       <c r="AI1" s="151"/>
@@ -9120,7 +9127,7 @@
       <c r="AM1" s="37"/>
       <c r="AN1" s="38"/>
     </row>
-    <row r="2" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="107" t="s">
         <v>228</v>
       </c>
@@ -9174,7 +9181,7 @@
       <c r="AM2" s="37"/>
       <c r="AN2" s="37"/>
     </row>
-    <row r="3" spans="1:40" s="13" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:40" s="13" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A3" s="107" t="s">
         <v>230</v>
       </c>
@@ -9218,7 +9225,7 @@
       <c r="AM3" s="36"/>
       <c r="AN3" s="36"/>
     </row>
-    <row r="4" spans="1:40" s="13" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:40" s="13" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="36"/>
       <c r="B4" s="36"/>
       <c r="C4" s="36"/>
@@ -9260,7 +9267,7 @@
       <c r="AM4" s="36"/>
       <c r="AN4" s="36"/>
     </row>
-    <row r="5" spans="1:40" s="13" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" s="13" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="36"/>
       <c r="B5" s="36"/>
       <c r="C5" s="36"/>
@@ -9304,7 +9311,7 @@
       <c r="AM5" s="36"/>
       <c r="AN5" s="36"/>
     </row>
-    <row r="6" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="36"/>
       <c r="B6" s="36"/>
       <c r="C6" s="36"/>
@@ -9346,7 +9353,7 @@
       <c r="AM6" s="36"/>
       <c r="AN6" s="36"/>
     </row>
-    <row r="7" spans="1:40" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:40" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="55" t="s">
         <v>234</v>
       </c>
@@ -9397,7 +9404,7 @@
       <c r="AH7" s="159"/>
       <c r="AI7" s="158"/>
     </row>
-    <row r="8" spans="1:40" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:40" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A8" s="65">
         <v>1</v>
       </c>
@@ -9406,7 +9413,7 @@
       </c>
       <c r="C8" s="132"/>
       <c r="D8" s="133">
-        <v>43336</v>
+        <v>45565</v>
       </c>
       <c r="E8" s="134"/>
       <c r="F8" s="135"/>
@@ -9448,7 +9455,7 @@
       <c r="AH8" s="140"/>
       <c r="AI8" s="141"/>
     </row>
-    <row r="9" spans="1:40" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:40" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A9" s="66"/>
       <c r="B9" s="156"/>
       <c r="C9" s="102"/>
@@ -9485,7 +9492,7 @@
       <c r="AH9" s="96"/>
       <c r="AI9" s="97"/>
     </row>
-    <row r="10" spans="1:40" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:40" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A10" s="56"/>
       <c r="B10" s="156"/>
       <c r="C10" s="102"/>
@@ -9522,7 +9529,7 @@
       <c r="AH10" s="96"/>
       <c r="AI10" s="97"/>
     </row>
-    <row r="11" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="56"/>
       <c r="B11" s="101"/>
       <c r="C11" s="102"/>
@@ -9559,7 +9566,7 @@
       <c r="AH11" s="96"/>
       <c r="AI11" s="97"/>
     </row>
-    <row r="12" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="56"/>
       <c r="B12" s="101"/>
       <c r="C12" s="102"/>
@@ -9596,7 +9603,7 @@
       <c r="AH12" s="96"/>
       <c r="AI12" s="97"/>
     </row>
-    <row r="13" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="56"/>
       <c r="B13" s="101"/>
       <c r="C13" s="102"/>
@@ -9633,7 +9640,7 @@
       <c r="AH13" s="96"/>
       <c r="AI13" s="97"/>
     </row>
-    <row r="14" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="56"/>
       <c r="B14" s="101"/>
       <c r="C14" s="102"/>
@@ -9670,7 +9677,7 @@
       <c r="AH14" s="96"/>
       <c r="AI14" s="97"/>
     </row>
-    <row r="15" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="56"/>
       <c r="B15" s="101"/>
       <c r="C15" s="102"/>
@@ -9707,7 +9714,7 @@
       <c r="AH15" s="96"/>
       <c r="AI15" s="97"/>
     </row>
-    <row r="16" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="56"/>
       <c r="B16" s="101"/>
       <c r="C16" s="102"/>
@@ -9744,7 +9751,7 @@
       <c r="AH16" s="96"/>
       <c r="AI16" s="97"/>
     </row>
-    <row r="17" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="56"/>
       <c r="B17" s="101"/>
       <c r="C17" s="102"/>
@@ -9781,7 +9788,7 @@
       <c r="AH17" s="96"/>
       <c r="AI17" s="97"/>
     </row>
-    <row r="18" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="56"/>
       <c r="B18" s="101"/>
       <c r="C18" s="102"/>
@@ -9818,7 +9825,7 @@
       <c r="AH18" s="96"/>
       <c r="AI18" s="97"/>
     </row>
-    <row r="19" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="56"/>
       <c r="B19" s="101"/>
       <c r="C19" s="102"/>
@@ -9855,7 +9862,7 @@
       <c r="AH19" s="96"/>
       <c r="AI19" s="97"/>
     </row>
-    <row r="20" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="56"/>
       <c r="B20" s="101"/>
       <c r="C20" s="102"/>
@@ -9892,7 +9899,7 @@
       <c r="AH20" s="96"/>
       <c r="AI20" s="97"/>
     </row>
-    <row r="21" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="56"/>
       <c r="B21" s="101"/>
       <c r="C21" s="102"/>
@@ -9929,7 +9936,7 @@
       <c r="AH21" s="96"/>
       <c r="AI21" s="97"/>
     </row>
-    <row r="22" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="56"/>
       <c r="B22" s="101"/>
       <c r="C22" s="102"/>
@@ -9966,7 +9973,7 @@
       <c r="AH22" s="96"/>
       <c r="AI22" s="97"/>
     </row>
-    <row r="23" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="56"/>
       <c r="B23" s="101"/>
       <c r="C23" s="102"/>
@@ -10003,7 +10010,7 @@
       <c r="AH23" s="96"/>
       <c r="AI23" s="97"/>
     </row>
-    <row r="24" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="56"/>
       <c r="B24" s="101"/>
       <c r="C24" s="102"/>
@@ -10040,7 +10047,7 @@
       <c r="AH24" s="96"/>
       <c r="AI24" s="97"/>
     </row>
-    <row r="25" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="56"/>
       <c r="B25" s="101"/>
       <c r="C25" s="102"/>
@@ -10077,7 +10084,7 @@
       <c r="AH25" s="96"/>
       <c r="AI25" s="97"/>
     </row>
-    <row r="26" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="56"/>
       <c r="B26" s="101"/>
       <c r="C26" s="102"/>
@@ -10114,7 +10121,7 @@
       <c r="AH26" s="96"/>
       <c r="AI26" s="97"/>
     </row>
-    <row r="27" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="56"/>
       <c r="B27" s="101"/>
       <c r="C27" s="102"/>
@@ -10151,7 +10158,7 @@
       <c r="AH27" s="96"/>
       <c r="AI27" s="97"/>
     </row>
-    <row r="28" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="56"/>
       <c r="B28" s="101"/>
       <c r="C28" s="102"/>
@@ -10188,7 +10195,7 @@
       <c r="AH28" s="96"/>
       <c r="AI28" s="97"/>
     </row>
-    <row r="29" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="56"/>
       <c r="B29" s="101"/>
       <c r="C29" s="102"/>
@@ -10225,7 +10232,7 @@
       <c r="AH29" s="96"/>
       <c r="AI29" s="97"/>
     </row>
-    <row r="30" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="56"/>
       <c r="B30" s="101"/>
       <c r="C30" s="102"/>
@@ -10262,7 +10269,7 @@
       <c r="AH30" s="96"/>
       <c r="AI30" s="97"/>
     </row>
-    <row r="31" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="56"/>
       <c r="B31" s="101"/>
       <c r="C31" s="102"/>
@@ -10299,7 +10306,7 @@
       <c r="AH31" s="96"/>
       <c r="AI31" s="97"/>
     </row>
-    <row r="32" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="56"/>
       <c r="B32" s="101"/>
       <c r="C32" s="102"/>
@@ -10336,7 +10343,7 @@
       <c r="AH32" s="96"/>
       <c r="AI32" s="97"/>
     </row>
-    <row r="33" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="56"/>
       <c r="B33" s="101"/>
       <c r="C33" s="102"/>
@@ -10573,17 +10580,17 @@
   <sheetPr codeName="Sheet44">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AW109"/>
-  <sheetFormatPr defaultColWidth="4.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:AW110"/>
+  <sheetFormatPr defaultColWidth="4.81640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16" width="4.83203125" style="3" customWidth="1"/>
-    <col min="17" max="17" width="4.83203125" style="2" customWidth="1"/>
-    <col min="18" max="33" width="4.83203125" style="3" customWidth="1"/>
-    <col min="34" max="34" width="4.83203125" style="2" customWidth="1"/>
-    <col min="35" max="16384" width="4.83203125" style="3"/>
+    <col min="1" max="16" width="4.81640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="4.81640625" style="2" customWidth="1"/>
+    <col min="18" max="33" width="4.81640625" style="3" customWidth="1"/>
+    <col min="34" max="34" width="4.81640625" style="2" customWidth="1"/>
+    <col min="35" max="16384" width="4.81640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:49" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="107" t="s">
         <v>225</v>
       </c>
@@ -10633,7 +10640,7 @@
       <c r="AF1" s="148"/>
       <c r="AG1" s="149">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>43336</v>
+        <v>45565</v>
       </c>
       <c r="AH1" s="150"/>
       <c r="AI1" s="151"/>
@@ -10652,7 +10659,7 @@
       <c r="AV1" s="36"/>
       <c r="AW1" s="36"/>
     </row>
-    <row r="2" spans="1:49" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:49" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="107" t="s">
         <v>228</v>
       </c>
@@ -10716,7 +10723,7 @@
       <c r="AV2" s="36"/>
       <c r="AW2" s="36"/>
     </row>
-    <row r="3" spans="1:49" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:49" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="107" t="s">
         <v>230</v>
       </c>
@@ -10778,7 +10785,7 @@
       <c r="AV3" s="36"/>
       <c r="AW3" s="36"/>
     </row>
-    <row r="4" spans="1:49" s="13" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:49" s="13" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A4" s="36"/>
       <c r="B4" s="36"/>
       <c r="C4" s="36"/>
@@ -10829,7 +10836,7 @@
       <c r="AV4" s="36"/>
       <c r="AW4" s="36"/>
     </row>
-    <row r="5" spans="1:49" s="13" customFormat="1" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:49" s="13" customFormat="1" ht="16.75" x14ac:dyDescent="0.3">
       <c r="A5" s="36"/>
       <c r="B5" s="36"/>
       <c r="C5" s="36"/>
@@ -10880,7 +10887,7 @@
       <c r="AV5" s="36"/>
       <c r="AW5" s="36"/>
     </row>
-    <row r="6" spans="1:49" s="13" customFormat="1" ht="17.25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:49" s="13" customFormat="1" ht="16.75" x14ac:dyDescent="0.3">
       <c r="A6" s="36"/>
       <c r="B6" s="36"/>
       <c r="C6" s="36"/>
@@ -10931,7 +10938,7 @@
       <c r="AV6" s="36"/>
       <c r="AW6" s="36"/>
     </row>
-    <row r="7" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="24" t="s">
         <v>237</v>
@@ -10985,7 +10992,7 @@
       <c r="AV7" s="41"/>
       <c r="AW7" s="41"/>
     </row>
-    <row r="8" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="C8" s="58" t="s">
         <v>239</v>
@@ -11038,10 +11045,11 @@
       <c r="AV8" s="41"/>
       <c r="AW8" s="41"/>
     </row>
-    <row r="9" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="1"/>
+      <c r="C9" s="58" t="s">
+        <v>367</v>
+      </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="1"/>
@@ -11091,11 +11099,9 @@
       <c r="AV9" s="41"/>
       <c r="AW9" s="41"/>
     </row>
-    <row r="10" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
-      <c r="B10" s="24" t="s">
-        <v>238</v>
-      </c>
+      <c r="B10" s="18"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -11146,11 +11152,12 @@
       <c r="AV10" s="41"/>
       <c r="AW10" s="41"/>
     </row>
-    <row r="11" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
-      <c r="C11" s="58" t="s">
-        <v>341</v>
-      </c>
+      <c r="B11" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -11200,10 +11207,10 @@
       <c r="AV11" s="41"/>
       <c r="AW11" s="41"/>
     </row>
-    <row r="12" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="C12" s="58" t="s">
-        <v>240</v>
+        <v>341</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -11251,10 +11258,10 @@
       <c r="AV12" s="41"/>
       <c r="AW12" s="41"/>
     </row>
-    <row r="13" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="C13" s="58" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -11303,10 +11310,10 @@
       <c r="AV13" s="41"/>
       <c r="AW13" s="41"/>
     </row>
-    <row r="14" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="C14" s="58" t="s">
-        <v>340</v>
+        <v>241</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -11355,10 +11362,11 @@
       <c r="AV14" s="41"/>
       <c r="AW14" s="41"/>
     </row>
-    <row r="15" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
-      <c r="B15" s="41"/>
-      <c r="C15" s="1"/>
+      <c r="C15" s="58" t="s">
+        <v>340</v>
+      </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -11405,19 +11413,18 @@
       <c r="AV15" s="41"/>
       <c r="AW15" s="41"/>
     </row>
-    <row r="16" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="A16" s="41"/>
-      <c r="B16" s="24" t="s">
-        <v>342</v>
-      </c>
+    <row r="16" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
+      <c r="A16" s="1"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="41"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
       <c r="L16" s="41"/>
       <c r="M16" s="41"/>
       <c r="N16" s="41"/>
@@ -11456,19 +11463,19 @@
       <c r="AV16" s="41"/>
       <c r="AW16" s="41"/>
     </row>
-    <row r="17" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="A17" s="1"/>
-      <c r="C17" s="58" t="s">
-        <v>242</v>
-      </c>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
+    <row r="17" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
+      <c r="A17" s="41"/>
+      <c r="B17" s="24" t="s">
+        <v>342</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
       <c r="N17" s="41"/>
@@ -11507,19 +11514,19 @@
       <c r="AV17" s="41"/>
       <c r="AW17" s="41"/>
     </row>
-    <row r="18" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="C18" s="58" t="s">
-        <v>243</v>
-      </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
+        <v>242</v>
+      </c>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
-      <c r="K18" s="41"/>
+      <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
@@ -11558,19 +11565,18 @@
       <c r="AV18" s="41"/>
       <c r="AW18" s="41"/>
     </row>
-    <row r="19" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
-      <c r="A19" s="41"/>
-      <c r="B19" s="1"/>
+    <row r="19" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
+      <c r="A19" s="1"/>
       <c r="C19" s="58" t="s">
-        <v>244</v>
-      </c>
-      <c r="D19" s="24"/>
+        <v>243</v>
+      </c>
+      <c r="D19" s="1"/>
       <c r="E19" s="1"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="41"/>
-      <c r="I19" s="41"/>
-      <c r="J19" s="41"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
       <c r="K19" s="41"/>
       <c r="L19" s="41"/>
       <c r="M19" s="41"/>
@@ -11609,8 +11615,20 @@
       <c r="AV19" s="41"/>
       <c r="AW19" s="41"/>
     </row>
-    <row r="20" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A20" s="41"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="58" t="s">
+        <v>244</v>
+      </c>
+      <c r="D20" s="24"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="41"/>
       <c r="O20" s="41"/>
       <c r="P20" s="41"/>
       <c r="Q20" s="57"/>
@@ -11646,7 +11664,7 @@
       <c r="AV20" s="41"/>
       <c r="AW20" s="41"/>
     </row>
-    <row r="21" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A21" s="41"/>
       <c r="O21" s="41"/>
       <c r="P21" s="41"/>
@@ -11684,7 +11702,7 @@
       <c r="AV21" s="41"/>
       <c r="AW21" s="41"/>
     </row>
-    <row r="22" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A22" s="41"/>
       <c r="O22" s="41"/>
       <c r="P22" s="41"/>
@@ -11711,7 +11729,7 @@
       <c r="AV22" s="41"/>
       <c r="AW22" s="41"/>
     </row>
-    <row r="23" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A23" s="41"/>
       <c r="O23" s="41"/>
       <c r="P23" s="41"/>
@@ -11738,7 +11756,7 @@
       <c r="AV23" s="41"/>
       <c r="AW23" s="41"/>
     </row>
-    <row r="24" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A24" s="41"/>
       <c r="O24" s="41"/>
       <c r="P24" s="41"/>
@@ -11763,17 +11781,8 @@
       <c r="AV24" s="41"/>
       <c r="AW24" s="41"/>
     </row>
-    <row r="25" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A25" s="41"/>
-      <c r="B25" s="41"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="41"/>
-      <c r="J25" s="41"/>
-      <c r="K25" s="41"/>
       <c r="L25" s="41"/>
       <c r="M25" s="41"/>
       <c r="N25" s="41"/>
@@ -11813,7 +11822,7 @@
       <c r="AV25" s="41"/>
       <c r="AW25" s="41"/>
     </row>
-    <row r="26" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A26" s="41"/>
       <c r="B26" s="41"/>
       <c r="D26" s="59"/>
@@ -11863,7 +11872,7 @@
       <c r="AV26" s="41"/>
       <c r="AW26" s="41"/>
     </row>
-    <row r="27" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A27" s="41"/>
       <c r="B27" s="41"/>
       <c r="D27" s="59"/>
@@ -11913,9 +11922,10 @@
       <c r="AV27" s="41"/>
       <c r="AW27" s="41"/>
     </row>
-    <row r="28" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A28" s="41"/>
       <c r="B28" s="41"/>
+      <c r="D28" s="59"/>
       <c r="E28" s="41"/>
       <c r="F28" s="41"/>
       <c r="G28" s="41"/>
@@ -11962,9 +11972,16 @@
       <c r="AV28" s="36"/>
       <c r="AW28" s="36"/>
     </row>
-    <row r="29" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A29" s="41"/>
       <c r="B29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="41"/>
       <c r="N29" s="41"/>
       <c r="O29" s="41"/>
       <c r="P29" s="41"/>
@@ -12001,16 +12018,9 @@
       <c r="AV29" s="36"/>
       <c r="AW29" s="36"/>
     </row>
-    <row r="30" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A30" s="41"/>
       <c r="B30" s="41"/>
-      <c r="D30" s="41"/>
-      <c r="F30" s="41"/>
-      <c r="G30" s="41"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="41"/>
-      <c r="J30" s="41"/>
-      <c r="K30" s="41"/>
       <c r="L30" s="41"/>
       <c r="M30" s="41"/>
       <c r="N30" s="41"/>
@@ -12049,11 +12059,10 @@
       <c r="AV30" s="36"/>
       <c r="AW30" s="36"/>
     </row>
-    <row r="31" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A31" s="41"/>
       <c r="B31" s="41"/>
       <c r="D31" s="41"/>
-      <c r="E31" s="59"/>
       <c r="F31" s="41"/>
       <c r="G31" s="41"/>
       <c r="H31" s="41"/>
@@ -12098,7 +12107,7 @@
       <c r="AV31" s="36"/>
       <c r="AW31" s="36"/>
     </row>
-    <row r="32" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A32" s="41"/>
       <c r="B32" s="41"/>
       <c r="D32" s="41"/>
@@ -12147,11 +12156,11 @@
       <c r="AV32" s="36"/>
       <c r="AW32" s="36"/>
     </row>
-    <row r="33" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A33" s="41"/>
-      <c r="B33" s="18"/>
+      <c r="B33" s="41"/>
       <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
+      <c r="E33" s="59"/>
       <c r="F33" s="41"/>
       <c r="G33" s="41"/>
       <c r="H33" s="41"/>
@@ -12196,10 +12205,16 @@
       <c r="AV33" s="36"/>
       <c r="AW33" s="36"/>
     </row>
-    <row r="34" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A34" s="41"/>
-      <c r="B34" s="41"/>
-      <c r="C34" s="41"/>
+      <c r="B34" s="18"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="41"/>
+      <c r="H34" s="41"/>
+      <c r="I34" s="41"/>
+      <c r="J34" s="41"/>
       <c r="K34" s="41"/>
       <c r="L34" s="41"/>
       <c r="M34" s="41"/>
@@ -12239,7 +12254,7 @@
       <c r="AV34" s="36"/>
       <c r="AW34" s="36"/>
     </row>
-    <row r="35" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A35" s="41"/>
       <c r="B35" s="41"/>
       <c r="C35" s="41"/>
@@ -12282,17 +12297,11 @@
       <c r="AV35" s="36"/>
       <c r="AW35" s="36"/>
     </row>
-    <row r="36" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A36" s="41"/>
       <c r="B36" s="41"/>
       <c r="C36" s="41"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="40"/>
+      <c r="K36" s="41"/>
       <c r="L36" s="41"/>
       <c r="M36" s="41"/>
       <c r="N36" s="41"/>
@@ -12308,15 +12317,15 @@
       <c r="X36" s="41"/>
       <c r="Y36" s="41"/>
     </row>
-    <row r="37" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A37" s="41"/>
       <c r="B37" s="41"/>
       <c r="C37" s="41"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
-      <c r="H37" s="41"/>
-      <c r="I37" s="41"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
       <c r="J37" s="15"/>
       <c r="K37" s="40"/>
       <c r="L37" s="41"/>
@@ -12334,11 +12343,10 @@
       <c r="X37" s="41"/>
       <c r="Y37" s="41"/>
     </row>
-    <row r="38" spans="1:49" s="19" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:49" s="19" customFormat="1" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A38" s="41"/>
       <c r="B38" s="41"/>
       <c r="C38" s="41"/>
-      <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -12361,18 +12369,18 @@
       <c r="X38" s="41"/>
       <c r="Y38" s="41"/>
     </row>
-    <row r="39" spans="1:49" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:49" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A39" s="41"/>
       <c r="B39" s="41"/>
-      <c r="C39" s="1"/>
+      <c r="C39" s="41"/>
       <c r="D39" s="1"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
       <c r="H39" s="41"/>
       <c r="I39" s="41"/>
       <c r="J39" s="15"/>
-      <c r="K39" s="15"/>
+      <c r="K39" s="40"/>
       <c r="L39" s="41"/>
       <c r="M39" s="41"/>
       <c r="N39" s="41"/>
@@ -12389,18 +12397,18 @@
       <c r="Y39" s="41"/>
       <c r="AH39" s="3"/>
     </row>
-    <row r="40" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="41"/>
       <c r="B40" s="41"/>
-      <c r="C40" s="41"/>
-      <c r="D40" s="41"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
       <c r="E40" s="41"/>
       <c r="F40" s="41"/>
       <c r="G40" s="41"/>
       <c r="H40" s="41"/>
       <c r="I40" s="41"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="41"/>
+      <c r="J40" s="15"/>
+      <c r="K40" s="15"/>
       <c r="L40" s="41"/>
       <c r="M40" s="41"/>
       <c r="N40" s="41"/>
@@ -12417,7 +12425,7 @@
       <c r="Y40" s="41"/>
       <c r="AH40" s="3"/>
     </row>
-    <row r="41" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="41"/>
       <c r="B41" s="41"/>
       <c r="C41" s="41"/>
@@ -12445,10 +12453,11 @@
       <c r="Y41" s="41"/>
       <c r="AH41" s="3"/>
     </row>
-    <row r="42" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="41"/>
       <c r="B42" s="41"/>
       <c r="C42" s="41"/>
+      <c r="D42" s="41"/>
       <c r="E42" s="41"/>
       <c r="F42" s="41"/>
       <c r="G42" s="41"/>
@@ -12472,7 +12481,7 @@
       <c r="Y42" s="41"/>
       <c r="AH42" s="3"/>
     </row>
-    <row r="43" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="41"/>
       <c r="B43" s="41"/>
       <c r="C43" s="41"/>
@@ -12481,7 +12490,7 @@
       <c r="G43" s="41"/>
       <c r="H43" s="41"/>
       <c r="I43" s="41"/>
-      <c r="J43" s="1"/>
+      <c r="J43" s="2"/>
       <c r="K43" s="41"/>
       <c r="L43" s="41"/>
       <c r="M43" s="41"/>
@@ -12499,7 +12508,7 @@
       <c r="Y43" s="41"/>
       <c r="AH43" s="3"/>
     </row>
-    <row r="44" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="41"/>
       <c r="B44" s="41"/>
       <c r="C44" s="41"/>
@@ -12526,7 +12535,7 @@
       <c r="Y44" s="41"/>
       <c r="AH44" s="3"/>
     </row>
-    <row r="45" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="41"/>
       <c r="B45" s="41"/>
       <c r="C45" s="41"/>
@@ -12553,7 +12562,7 @@
       <c r="Y45" s="41"/>
       <c r="AH45" s="3"/>
     </row>
-    <row r="46" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="41"/>
       <c r="B46" s="41"/>
       <c r="C46" s="41"/>
@@ -12580,7 +12589,7 @@
       <c r="Y46" s="41"/>
       <c r="AH46" s="3"/>
     </row>
-    <row r="47" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="41"/>
       <c r="B47" s="41"/>
       <c r="C47" s="41"/>
@@ -12607,7 +12616,7 @@
       <c r="Y47" s="41"/>
       <c r="AH47" s="3"/>
     </row>
-    <row r="48" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="41"/>
       <c r="B48" s="41"/>
       <c r="C48" s="41"/>
@@ -12634,7 +12643,7 @@
       <c r="Y48" s="41"/>
       <c r="AH48" s="3"/>
     </row>
-    <row r="49" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="41"/>
       <c r="B49" s="41"/>
       <c r="C49" s="41"/>
@@ -12661,10 +12670,15 @@
       <c r="Y49" s="41"/>
       <c r="AH49" s="3"/>
     </row>
-    <row r="50" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="41"/>
       <c r="B50" s="41"/>
       <c r="C50" s="41"/>
+      <c r="E50" s="41"/>
+      <c r="F50" s="41"/>
+      <c r="G50" s="41"/>
+      <c r="H50" s="41"/>
+      <c r="I50" s="41"/>
       <c r="J50" s="1"/>
       <c r="K50" s="41"/>
       <c r="L50" s="41"/>
@@ -12683,10 +12697,16 @@
       <c r="Y50" s="41"/>
       <c r="AH50" s="3"/>
     </row>
-    <row r="51" spans="1:34" s="22" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:34" s="22" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="41"/>
       <c r="B51" s="41"/>
       <c r="C51" s="41"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
       <c r="J51" s="1"/>
       <c r="K51" s="41"/>
       <c r="L51" s="36"/>
@@ -12704,10 +12724,16 @@
       <c r="X51" s="36"/>
       <c r="Y51" s="36"/>
     </row>
-    <row r="52" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="41"/>
       <c r="B52" s="41"/>
       <c r="C52" s="41"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="22"/>
+      <c r="H52" s="22"/>
+      <c r="I52" s="22"/>
       <c r="J52" s="1"/>
       <c r="K52" s="41"/>
       <c r="L52" s="41"/>
@@ -12726,12 +12752,12 @@
       <c r="Y52" s="41"/>
       <c r="AH52" s="3"/>
     </row>
-    <row r="53" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="41"/>
       <c r="B53" s="41"/>
       <c r="C53" s="41"/>
       <c r="J53" s="1"/>
-      <c r="K53" s="36"/>
+      <c r="K53" s="41"/>
       <c r="L53" s="41"/>
       <c r="M53" s="41"/>
       <c r="N53" s="41"/>
@@ -12748,12 +12774,12 @@
       <c r="Y53" s="41"/>
       <c r="AH53" s="3"/>
     </row>
-    <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="41"/>
       <c r="B54" s="41"/>
       <c r="C54" s="41"/>
       <c r="J54" s="1"/>
-      <c r="K54" s="41"/>
+      <c r="K54" s="36"/>
       <c r="L54" s="41"/>
       <c r="M54" s="41"/>
       <c r="N54" s="41"/>
@@ -12770,7 +12796,7 @@
       <c r="Y54" s="41"/>
       <c r="AH54" s="3"/>
     </row>
-    <row r="55" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="41"/>
       <c r="B55" s="41"/>
       <c r="C55" s="41"/>
@@ -12792,7 +12818,7 @@
       <c r="Y55" s="41"/>
       <c r="AH55" s="3"/>
     </row>
-    <row r="56" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="41"/>
       <c r="B56" s="41"/>
       <c r="C56" s="41"/>
@@ -12814,11 +12840,10 @@
       <c r="Y56" s="41"/>
       <c r="AH56" s="3"/>
     </row>
-    <row r="57" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="41"/>
       <c r="B57" s="41"/>
       <c r="C57" s="41"/>
-      <c r="D57" s="41"/>
       <c r="J57" s="1"/>
       <c r="K57" s="41"/>
       <c r="L57" s="41"/>
@@ -12837,9 +12862,11 @@
       <c r="Y57" s="41"/>
       <c r="AH57" s="3"/>
     </row>
-    <row r="58" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="41"/>
       <c r="B58" s="41"/>
+      <c r="C58" s="41"/>
+      <c r="D58" s="41"/>
       <c r="J58" s="1"/>
       <c r="K58" s="41"/>
       <c r="L58" s="41"/>
@@ -12858,10 +12885,9 @@
       <c r="Y58" s="41"/>
       <c r="AH58" s="3"/>
     </row>
-    <row r="59" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="41"/>
       <c r="B59" s="41"/>
-      <c r="D59" s="41"/>
       <c r="J59" s="1"/>
       <c r="K59" s="41"/>
       <c r="L59" s="41"/>
@@ -12880,7 +12906,7 @@
       <c r="Y59" s="41"/>
       <c r="AH59" s="3"/>
     </row>
-    <row r="60" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="41"/>
       <c r="B60" s="41"/>
       <c r="D60" s="41"/>
@@ -12902,7 +12928,7 @@
       <c r="Y60" s="41"/>
       <c r="AH60" s="3"/>
     </row>
-    <row r="61" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="41"/>
       <c r="B61" s="41"/>
       <c r="D61" s="41"/>
@@ -12924,7 +12950,7 @@
       <c r="Y61" s="41"/>
       <c r="AH61" s="3"/>
     </row>
-    <row r="62" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="41"/>
       <c r="B62" s="41"/>
       <c r="D62" s="41"/>
@@ -12946,7 +12972,7 @@
       <c r="Y62" s="41"/>
       <c r="AH62" s="3"/>
     </row>
-    <row r="63" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="41"/>
       <c r="B63" s="41"/>
       <c r="D63" s="41"/>
@@ -12968,7 +12994,7 @@
       <c r="Y63" s="41"/>
       <c r="AH63" s="3"/>
     </row>
-    <row r="64" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="41"/>
       <c r="B64" s="41"/>
       <c r="D64" s="41"/>
@@ -12990,7 +13016,7 @@
       <c r="Y64" s="41"/>
       <c r="AH64" s="3"/>
     </row>
-    <row r="65" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="41"/>
       <c r="B65" s="41"/>
       <c r="D65" s="41"/>
@@ -13012,15 +13038,10 @@
       <c r="Y65" s="41"/>
       <c r="AH65" s="3"/>
     </row>
-    <row r="66" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="41"/>
       <c r="B66" s="41"/>
       <c r="D66" s="41"/>
-      <c r="E66" s="41"/>
-      <c r="F66" s="41"/>
-      <c r="G66" s="41"/>
-      <c r="H66" s="41"/>
-      <c r="I66" s="41"/>
       <c r="J66" s="1"/>
       <c r="K66" s="41"/>
       <c r="L66" s="41"/>
@@ -13039,7 +13060,7 @@
       <c r="Y66" s="41"/>
       <c r="AH66" s="3"/>
     </row>
-    <row r="67" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="41"/>
       <c r="B67" s="41"/>
       <c r="D67" s="41"/>
@@ -13066,7 +13087,7 @@
       <c r="Y67" s="41"/>
       <c r="AH67" s="3"/>
     </row>
-    <row r="68" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="41"/>
       <c r="B68" s="41"/>
       <c r="D68" s="41"/>
@@ -13093,7 +13114,7 @@
       <c r="Y68" s="41"/>
       <c r="AH68" s="3"/>
     </row>
-    <row r="69" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="41"/>
       <c r="B69" s="41"/>
       <c r="D69" s="41"/>
@@ -13101,7 +13122,7 @@
       <c r="F69" s="41"/>
       <c r="G69" s="41"/>
       <c r="H69" s="41"/>
-      <c r="I69" s="15"/>
+      <c r="I69" s="41"/>
       <c r="J69" s="1"/>
       <c r="K69" s="41"/>
       <c r="L69" s="41"/>
@@ -13120,7 +13141,7 @@
       <c r="Y69" s="41"/>
       <c r="AH69" s="3"/>
     </row>
-    <row r="70" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="41"/>
       <c r="B70" s="41"/>
       <c r="D70" s="41"/>
@@ -13147,7 +13168,7 @@
       <c r="Y70" s="41"/>
       <c r="AH70" s="3"/>
     </row>
-    <row r="71" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="41"/>
       <c r="B71" s="41"/>
       <c r="D71" s="41"/>
@@ -13174,7 +13195,7 @@
       <c r="Y71" s="41"/>
       <c r="AH71" s="3"/>
     </row>
-    <row r="72" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="41"/>
       <c r="B72" s="41"/>
       <c r="D72" s="41"/>
@@ -13182,8 +13203,8 @@
       <c r="F72" s="41"/>
       <c r="G72" s="41"/>
       <c r="H72" s="41"/>
-      <c r="I72" s="41"/>
-      <c r="J72" s="2"/>
+      <c r="I72" s="15"/>
+      <c r="J72" s="1"/>
       <c r="K72" s="41"/>
       <c r="L72" s="41"/>
       <c r="M72" s="41"/>
@@ -13201,17 +13222,16 @@
       <c r="Y72" s="41"/>
       <c r="AH72" s="3"/>
     </row>
-    <row r="73" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A73" s="15"/>
-      <c r="B73" s="1"/>
-      <c r="C73" s="41"/>
+    <row r="73" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="41"/>
+      <c r="B73" s="41"/>
       <c r="D73" s="41"/>
       <c r="E73" s="41"/>
       <c r="F73" s="41"/>
       <c r="G73" s="41"/>
       <c r="H73" s="41"/>
       <c r="I73" s="41"/>
-      <c r="J73" s="41"/>
+      <c r="J73" s="2"/>
       <c r="K73" s="41"/>
       <c r="L73" s="41"/>
       <c r="M73" s="41"/>
@@ -13221,9 +13241,9 @@
       <c r="Q73" s="41"/>
       <c r="AH73" s="3"/>
     </row>
-    <row r="74" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A74" s="41"/>
-      <c r="B74" s="2"/>
+    <row r="74" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="15"/>
+      <c r="B74" s="1"/>
       <c r="C74" s="41"/>
       <c r="D74" s="41"/>
       <c r="E74" s="41"/>
@@ -13241,7 +13261,7 @@
       <c r="Q74" s="41"/>
       <c r="AH74" s="3"/>
     </row>
-    <row r="75" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="41"/>
       <c r="B75" s="2"/>
       <c r="C75" s="41"/>
@@ -13261,7 +13281,7 @@
       <c r="Q75" s="41"/>
       <c r="AH75" s="3"/>
     </row>
-    <row r="76" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="41"/>
       <c r="B76" s="2"/>
       <c r="C76" s="41"/>
@@ -13281,7 +13301,7 @@
       <c r="Q76" s="41"/>
       <c r="AH76" s="3"/>
     </row>
-    <row r="77" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="41"/>
       <c r="B77" s="2"/>
       <c r="C77" s="41"/>
@@ -13301,9 +13321,9 @@
       <c r="Q77" s="41"/>
       <c r="AH77" s="3"/>
     </row>
-    <row r="78" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A78" s="15"/>
-      <c r="B78" s="15"/>
+    <row r="78" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="41"/>
+      <c r="B78" s="2"/>
       <c r="C78" s="41"/>
       <c r="D78" s="41"/>
       <c r="E78" s="41"/>
@@ -13321,7 +13341,7 @@
       <c r="Q78" s="41"/>
       <c r="AH78" s="3"/>
     </row>
-    <row r="79" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="15"/>
       <c r="B79" s="15"/>
       <c r="C79" s="41"/>
@@ -13341,7 +13361,7 @@
       <c r="Q79" s="41"/>
       <c r="AH79" s="3"/>
     </row>
-    <row r="80" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="15"/>
       <c r="B80" s="15"/>
       <c r="C80" s="41"/>
@@ -13361,7 +13381,7 @@
       <c r="Q80" s="41"/>
       <c r="AH80" s="3"/>
     </row>
-    <row r="81" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="15"/>
       <c r="B81" s="15"/>
       <c r="C81" s="41"/>
@@ -13381,7 +13401,7 @@
       <c r="Q81" s="41"/>
       <c r="AH81" s="3"/>
     </row>
-    <row r="82" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="15"/>
       <c r="B82" s="15"/>
       <c r="C82" s="41"/>
@@ -13401,7 +13421,7 @@
       <c r="Q82" s="41"/>
       <c r="AH82" s="3"/>
     </row>
-    <row r="83" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="15"/>
       <c r="B83" s="15"/>
       <c r="C83" s="41"/>
@@ -13421,7 +13441,7 @@
       <c r="Q83" s="41"/>
       <c r="AH83" s="3"/>
     </row>
-    <row r="84" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="15"/>
       <c r="B84" s="15"/>
       <c r="C84" s="41"/>
@@ -13441,7 +13461,7 @@
       <c r="Q84" s="41"/>
       <c r="AH84" s="3"/>
     </row>
-    <row r="85" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="15"/>
       <c r="B85" s="15"/>
       <c r="C85" s="41"/>
@@ -13461,18 +13481,18 @@
       <c r="Q85" s="41"/>
       <c r="AH85" s="3"/>
     </row>
-    <row r="86" spans="1:34" s="22" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:34" s="22" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="15"/>
-      <c r="B86" s="1"/>
+      <c r="B86" s="15"/>
       <c r="C86" s="41"/>
-      <c r="D86" s="36"/>
-      <c r="E86" s="36"/>
-      <c r="F86" s="36"/>
-      <c r="G86" s="36"/>
-      <c r="H86" s="36"/>
-      <c r="I86" s="36"/>
-      <c r="J86" s="36"/>
-      <c r="K86" s="36"/>
+      <c r="D86" s="41"/>
+      <c r="E86" s="41"/>
+      <c r="F86" s="41"/>
+      <c r="G86" s="41"/>
+      <c r="H86" s="41"/>
+      <c r="I86" s="41"/>
+      <c r="J86" s="41"/>
+      <c r="K86" s="41"/>
       <c r="L86" s="36"/>
       <c r="M86" s="36"/>
       <c r="N86" s="36"/>
@@ -13480,18 +13500,18 @@
       <c r="P86" s="36"/>
       <c r="Q86" s="36"/>
     </row>
-    <row r="87" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="15"/>
       <c r="B87" s="1"/>
       <c r="C87" s="41"/>
-      <c r="D87" s="41"/>
-      <c r="E87" s="41"/>
-      <c r="F87" s="41"/>
-      <c r="G87" s="41"/>
-      <c r="H87" s="41"/>
-      <c r="I87" s="41"/>
-      <c r="J87" s="41"/>
-      <c r="K87" s="41"/>
+      <c r="D87" s="36"/>
+      <c r="E87" s="36"/>
+      <c r="F87" s="36"/>
+      <c r="G87" s="36"/>
+      <c r="H87" s="36"/>
+      <c r="I87" s="36"/>
+      <c r="J87" s="36"/>
+      <c r="K87" s="36"/>
       <c r="L87" s="41"/>
       <c r="M87" s="41"/>
       <c r="N87" s="41"/>
@@ -13500,10 +13520,10 @@
       <c r="Q87" s="41"/>
       <c r="AH87" s="3"/>
     </row>
-    <row r="88" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="15"/>
       <c r="B88" s="1"/>
-      <c r="C88" s="36"/>
+      <c r="C88" s="41"/>
       <c r="D88" s="41"/>
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
@@ -13520,10 +13540,10 @@
       <c r="Q88" s="41"/>
       <c r="AH88" s="3"/>
     </row>
-    <row r="89" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="15"/>
       <c r="B89" s="1"/>
-      <c r="C89" s="41"/>
+      <c r="C89" s="36"/>
       <c r="D89" s="41"/>
       <c r="E89" s="41"/>
       <c r="F89" s="41"/>
@@ -13540,7 +13560,7 @@
       <c r="Q89" s="41"/>
       <c r="AH89" s="3"/>
     </row>
-    <row r="90" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="15"/>
       <c r="B90" s="1"/>
       <c r="C90" s="41"/>
@@ -13560,7 +13580,7 @@
       <c r="Q90" s="41"/>
       <c r="AH90" s="3"/>
     </row>
-    <row r="91" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="15"/>
       <c r="B91" s="1"/>
       <c r="C91" s="41"/>
@@ -13580,7 +13600,7 @@
       <c r="Q91" s="41"/>
       <c r="AH91" s="3"/>
     </row>
-    <row r="92" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="15"/>
       <c r="B92" s="1"/>
       <c r="C92" s="41"/>
@@ -13600,7 +13620,7 @@
       <c r="Q92" s="41"/>
       <c r="AH92" s="3"/>
     </row>
-    <row r="93" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="15"/>
       <c r="B93" s="1"/>
       <c r="C93" s="41"/>
@@ -13620,7 +13640,7 @@
       <c r="Q93" s="41"/>
       <c r="AH93" s="3"/>
     </row>
-    <row r="94" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="15"/>
       <c r="B94" s="1"/>
       <c r="C94" s="41"/>
@@ -13640,9 +13660,9 @@
       <c r="Q94" s="41"/>
       <c r="AH94" s="3"/>
     </row>
-    <row r="95" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A95" s="41"/>
-      <c r="B95" s="2"/>
+    <row r="95" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="15"/>
+      <c r="B95" s="1"/>
       <c r="C95" s="41"/>
       <c r="D95" s="41"/>
       <c r="E95" s="41"/>
@@ -13660,7 +13680,7 @@
       <c r="Q95" s="41"/>
       <c r="AH95" s="3"/>
     </row>
-    <row r="96" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:34" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="41"/>
       <c r="B96" s="2"/>
       <c r="C96" s="41"/>
@@ -13680,7 +13700,7 @@
       <c r="Q96" s="41"/>
       <c r="AH96" s="3"/>
     </row>
-    <row r="97" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="41"/>
       <c r="B97" s="2"/>
       <c r="C97" s="41"/>
@@ -13700,7 +13720,7 @@
       <c r="Q97" s="41"/>
       <c r="AH97" s="3"/>
     </row>
-    <row r="98" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="41"/>
       <c r="B98" s="2"/>
       <c r="C98" s="41"/>
@@ -13720,9 +13740,9 @@
       <c r="Q98" s="41"/>
       <c r="AH98" s="3"/>
     </row>
-    <row r="99" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A99" s="15"/>
-      <c r="B99" s="1"/>
+    <row r="99" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="41"/>
+      <c r="B99" s="2"/>
       <c r="C99" s="41"/>
       <c r="D99" s="41"/>
       <c r="E99" s="41"/>
@@ -13740,7 +13760,7 @@
       <c r="Q99" s="41"/>
       <c r="AH99" s="3"/>
     </row>
-    <row r="100" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="15"/>
       <c r="B100" s="1"/>
       <c r="C100" s="41"/>
@@ -13760,7 +13780,7 @@
       <c r="Q100" s="41"/>
       <c r="AH100" s="3"/>
     </row>
-    <row r="101" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="15"/>
       <c r="B101" s="1"/>
       <c r="C101" s="41"/>
@@ -13780,7 +13800,7 @@
       <c r="Q101" s="41"/>
       <c r="AH101" s="3"/>
     </row>
-    <row r="102" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="15"/>
       <c r="B102" s="1"/>
       <c r="C102" s="41"/>
@@ -13800,7 +13820,7 @@
       <c r="Q102" s="41"/>
       <c r="AH102" s="3"/>
     </row>
-    <row r="103" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="15"/>
       <c r="B103" s="1"/>
       <c r="C103" s="41"/>
@@ -13820,7 +13840,7 @@
       <c r="Q103" s="41"/>
       <c r="AH103" s="3"/>
     </row>
-    <row r="104" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="15"/>
       <c r="B104" s="1"/>
       <c r="C104" s="41"/>
@@ -13840,9 +13860,9 @@
       <c r="Q104" s="41"/>
       <c r="AH104" s="3"/>
     </row>
-    <row r="105" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A105" s="41"/>
-      <c r="B105" s="2"/>
+    <row r="105" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="15"/>
+      <c r="B105" s="1"/>
       <c r="C105" s="41"/>
       <c r="D105" s="41"/>
       <c r="E105" s="41"/>
@@ -13860,7 +13880,7 @@
       <c r="Q105" s="41"/>
       <c r="AH105" s="3"/>
     </row>
-    <row r="106" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="41"/>
       <c r="B106" s="2"/>
       <c r="C106" s="41"/>
@@ -13880,7 +13900,7 @@
       <c r="Q106" s="41"/>
       <c r="AH106" s="3"/>
     </row>
-    <row r="107" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="41"/>
       <c r="B107" s="2"/>
       <c r="C107" s="41"/>
@@ -13900,7 +13920,7 @@
       <c r="Q107" s="41"/>
       <c r="AH107" s="3"/>
     </row>
-    <row r="108" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="41"/>
       <c r="B108" s="2"/>
       <c r="C108" s="41"/>
@@ -13920,9 +13940,9 @@
       <c r="Q108" s="41"/>
       <c r="AH108" s="3"/>
     </row>
-    <row r="109" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="41"/>
-      <c r="B109" s="41"/>
+      <c r="B109" s="2"/>
       <c r="C109" s="41"/>
       <c r="D109" s="41"/>
       <c r="E109" s="41"/>
@@ -13969,6 +13989,19 @@
       <c r="AV109" s="41"/>
       <c r="AW109" s="41"/>
     </row>
+    <row r="110" spans="1:49" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="41"/>
+      <c r="B110" s="41"/>
+      <c r="C110" s="41"/>
+      <c r="D110" s="41"/>
+      <c r="E110" s="41"/>
+      <c r="F110" s="41"/>
+      <c r="G110" s="41"/>
+      <c r="H110" s="41"/>
+      <c r="I110" s="41"/>
+      <c r="J110" s="41"/>
+      <c r="K110" s="41"/>
+    </row>
   </sheetData>
   <mergeCells count="17">
     <mergeCell ref="AC3:AF3"/>
@@ -14006,12 +14039,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AI25"/>
-  <sheetFormatPr defaultColWidth="4.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="4.81640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="4.83203125" style="14"/>
+    <col min="1" max="16384" width="4.81640625" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:35" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="107" t="s">
         <v>225</v>
       </c>
@@ -14061,12 +14094,12 @@
       <c r="AF1" s="148"/>
       <c r="AG1" s="149">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>43336</v>
+        <v>45565</v>
       </c>
       <c r="AH1" s="150"/>
       <c r="AI1" s="151"/>
     </row>
-    <row r="2" spans="1:35" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:35" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="107" t="s">
         <v>228</v>
       </c>
@@ -14116,7 +14149,7 @@
       <c r="AH2" s="150"/>
       <c r="AI2" s="151"/>
     </row>
-    <row r="3" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A3" s="107" t="s">
         <v>230</v>
       </c>
@@ -14164,7 +14197,7 @@
       <c r="AH3" s="150"/>
       <c r="AI3" s="151"/>
     </row>
-    <row r="4" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -14201,7 +14234,7 @@
       <c r="AH4" s="1"/>
       <c r="AI4" s="1"/>
     </row>
-    <row r="5" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="B5" s="24" t="s">
         <v>245</v>
       </c>
@@ -14239,7 +14272,7 @@
       <c r="AH5" s="1"/>
       <c r="AI5" s="1"/>
     </row>
-    <row r="6" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="C6" s="24" t="s">
         <v>246</v>
@@ -14276,7 +14309,7 @@
       <c r="AH6" s="1"/>
       <c r="AI6" s="1"/>
     </row>
-    <row r="7" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="C7" s="24"/>
       <c r="E7" s="1"/>
@@ -14311,7 +14344,7 @@
       <c r="AH7" s="1"/>
       <c r="AI7" s="1"/>
     </row>
-    <row r="8" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
@@ -14349,7 +14382,7 @@
       <c r="AH8" s="1"/>
       <c r="AI8" s="1"/>
     </row>
-    <row r="9" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
@@ -14387,7 +14420,7 @@
       <c r="AH9" s="1"/>
       <c r="AI9" s="1"/>
     </row>
-    <row r="10" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -14423,7 +14456,7 @@
       <c r="AH10" s="1"/>
       <c r="AI10" s="1"/>
     </row>
-    <row r="11" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1" t="s">
@@ -14461,7 +14494,7 @@
       <c r="AH11" s="1"/>
       <c r="AI11" s="1"/>
     </row>
-    <row r="12" spans="1:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1" t="s">
@@ -14499,8 +14532,8 @@
       <c r="AH12" s="1"/>
       <c r="AI12" s="1"/>
     </row>
-    <row r="13" spans="1:35" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="14" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:35" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="24" t="s">
@@ -14541,7 +14574,7 @@
       <c r="AH14" s="1"/>
       <c r="AI14" s="1"/>
     </row>
-    <row r="15" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -14578,7 +14611,7 @@
       <c r="AH15" s="1"/>
       <c r="AI15" s="1"/>
     </row>
-    <row r="16" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -14617,7 +14650,7 @@
       <c r="AH16" s="1"/>
       <c r="AI16" s="1"/>
     </row>
-    <row r="17" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -14654,7 +14687,7 @@
       <c r="AH17" s="1"/>
       <c r="AI17" s="1"/>
     </row>
-    <row r="18" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -14693,7 +14726,7 @@
       <c r="AH18" s="1"/>
       <c r="AI18" s="1"/>
     </row>
-    <row r="19" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -14732,7 +14765,7 @@
       <c r="AH19" s="1"/>
       <c r="AI19" s="1"/>
     </row>
-    <row r="20" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -14769,7 +14802,7 @@
       <c r="AH20" s="1"/>
       <c r="AI20" s="1"/>
     </row>
-    <row r="21" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -14808,7 +14841,7 @@
       <c r="AH21" s="1"/>
       <c r="AI21" s="1"/>
     </row>
-    <row r="22" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -14847,7 +14880,7 @@
       <c r="AH22" s="1"/>
       <c r="AI22" s="1"/>
     </row>
-    <row r="23" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -14884,7 +14917,7 @@
       <c r="AH23" s="1"/>
       <c r="AI23" s="1"/>
     </row>
-    <row r="24" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -14921,7 +14954,7 @@
       <c r="AH24" s="1"/>
       <c r="AI24" s="1"/>
     </row>
-    <row r="25" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -15000,12 +15033,12 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AK73"/>
-  <sheetFormatPr defaultColWidth="4.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="4.81640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="4.83203125" style="1"/>
+    <col min="1" max="16384" width="4.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:37" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="107" t="s">
         <v>225</v>
       </c>
@@ -15055,12 +15088,12 @@
       <c r="AF1" s="148"/>
       <c r="AG1" s="149">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>43336</v>
+        <v>45565</v>
       </c>
       <c r="AH1" s="150"/>
       <c r="AI1" s="151"/>
     </row>
-    <row r="2" spans="1:37" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:37" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="107" t="s">
         <v>228</v>
       </c>
@@ -15110,7 +15143,7 @@
       <c r="AH2" s="150"/>
       <c r="AI2" s="151"/>
     </row>
-    <row r="3" spans="1:37" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:37" ht="10.75" x14ac:dyDescent="0.2">
       <c r="A3" s="107" t="s">
         <v>230</v>
       </c>
@@ -15158,16 +15191,16 @@
       <c r="AH3" s="150"/>
       <c r="AI3" s="151"/>
     </row>
-    <row r="4" spans="1:37" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:37" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:37" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:37" ht="10.75" x14ac:dyDescent="0.2">
       <c r="B5" s="24" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="6" spans="1:37" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:37" ht="10.75" x14ac:dyDescent="0.2">
       <c r="B6" s="24"/>
     </row>
-    <row r="7" spans="1:37" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:37" ht="10.75" x14ac:dyDescent="0.2">
       <c r="C7" s="58" t="s">
         <v>120</v>
       </c>
@@ -15178,35 +15211,35 @@
       <c r="F7" s="37"/>
       <c r="G7" s="37"/>
     </row>
-    <row r="8" spans="1:37" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:37" ht="10.75" x14ac:dyDescent="0.2">
       <c r="C8" s="58"/>
       <c r="D8" s="24"/>
       <c r="E8" s="37"/>
       <c r="F8" s="37"/>
       <c r="G8" s="37"/>
     </row>
-    <row r="9" spans="1:37" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:37" ht="10.75" x14ac:dyDescent="0.2">
       <c r="C9" s="18"/>
       <c r="D9" s="24" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="10" spans="1:37" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:37" ht="10.75" x14ac:dyDescent="0.2">
       <c r="C10" s="18"/>
       <c r="D10" s="24" t="s">
         <v>307</v>
       </c>
       <c r="AK10" s="24"/>
     </row>
-    <row r="11" spans="1:37" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:37" ht="10.75" x14ac:dyDescent="0.2">
       <c r="C11" s="18"/>
       <c r="D11" s="73" t="s">
         <v>297</v>
       </c>
       <c r="AK11" s="24"/>
     </row>
-    <row r="12" spans="1:37" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="13" spans="1:37" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:37" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:37" ht="10.75" x14ac:dyDescent="0.2">
       <c r="C13" s="58" t="s">
         <v>295</v>
       </c>
@@ -15214,35 +15247,35 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:37" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:37" ht="10.75" x14ac:dyDescent="0.2">
       <c r="C14" s="18"/>
     </row>
-    <row r="15" spans="1:37" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:37" ht="10.75" x14ac:dyDescent="0.2">
       <c r="C15" s="18"/>
       <c r="D15" s="24" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="16" spans="1:37" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="17" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="18" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="19" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="20" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="21" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="22" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="23" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="24" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="25" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="26" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="27" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="28" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="29" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:37" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="17" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D29" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="31" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="30" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D31" s="169" t="s">
         <v>60</v>
       </c>
@@ -15279,7 +15312,7 @@
       <c r="AG31" s="170"/>
       <c r="AH31" s="171"/>
     </row>
-    <row r="32" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="32" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D32" s="175" t="s">
         <v>62</v>
       </c>
@@ -15316,7 +15349,7 @@
       <c r="AG32" s="185"/>
       <c r="AH32" s="186"/>
     </row>
-    <row r="33" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="33" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D33" s="178"/>
       <c r="E33" s="179"/>
       <c r="F33" s="179"/>
@@ -15349,7 +15382,7 @@
       <c r="AG33" s="188"/>
       <c r="AH33" s="189"/>
     </row>
-    <row r="34" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="34" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D34" s="178"/>
       <c r="E34" s="179"/>
       <c r="F34" s="179"/>
@@ -15382,7 +15415,7 @@
       <c r="AG34" s="188"/>
       <c r="AH34" s="189"/>
     </row>
-    <row r="35" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="35" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D35" s="181"/>
       <c r="E35" s="182"/>
       <c r="F35" s="182"/>
@@ -15415,7 +15448,7 @@
       <c r="AG35" s="191"/>
       <c r="AH35" s="192"/>
     </row>
-    <row r="36" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="36" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D36" s="175" t="s">
         <v>63</v>
       </c>
@@ -15452,7 +15485,7 @@
       <c r="AG36" s="194"/>
       <c r="AH36" s="195"/>
     </row>
-    <row r="37" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="37" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D37" s="178"/>
       <c r="E37" s="179"/>
       <c r="F37" s="179"/>
@@ -15485,7 +15518,7 @@
       <c r="AG37" s="197"/>
       <c r="AH37" s="198"/>
     </row>
-    <row r="38" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="38" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D38" s="178"/>
       <c r="E38" s="179"/>
       <c r="F38" s="179"/>
@@ -15518,7 +15551,7 @@
       <c r="AG38" s="197"/>
       <c r="AH38" s="198"/>
     </row>
-    <row r="39" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="39" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D39" s="181"/>
       <c r="E39" s="182"/>
       <c r="F39" s="182"/>
@@ -15551,7 +15584,7 @@
       <c r="AG39" s="200"/>
       <c r="AH39" s="201"/>
     </row>
-    <row r="40" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="40" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D40" s="175" t="s">
         <v>64</v>
       </c>
@@ -15588,7 +15621,7 @@
       <c r="AG40" s="194"/>
       <c r="AH40" s="195"/>
     </row>
-    <row r="41" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="41" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D41" s="178"/>
       <c r="E41" s="179"/>
       <c r="F41" s="179"/>
@@ -15621,7 +15654,7 @@
       <c r="AG41" s="197"/>
       <c r="AH41" s="198"/>
     </row>
-    <row r="42" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="42" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D42" s="178"/>
       <c r="E42" s="179"/>
       <c r="F42" s="179"/>
@@ -15654,7 +15687,7 @@
       <c r="AG42" s="197"/>
       <c r="AH42" s="198"/>
     </row>
-    <row r="43" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="43" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D43" s="181"/>
       <c r="E43" s="182"/>
       <c r="F43" s="182"/>
@@ -15687,7 +15720,7 @@
       <c r="AG43" s="200"/>
       <c r="AH43" s="201"/>
     </row>
-    <row r="44" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="44" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D44" s="25" t="s">
         <v>186</v>
       </c>
@@ -15695,19 +15728,19 @@
         <v>95</v>
       </c>
     </row>
-    <row r="45" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="46" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="45" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D46" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="47" spans="4:34" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="47" spans="4:34" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D47" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="48" spans="4:34" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="49" spans="3:35" ht="48.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="4:34" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="49" spans="3:35" ht="48.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D49" s="203" t="s">
         <v>248</v>
       </c>
@@ -15755,7 +15788,7 @@
       <c r="AD49" s="173"/>
       <c r="AE49" s="174"/>
     </row>
-    <row r="50" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="50" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D50" s="95" t="s">
         <v>97</v>
       </c>
@@ -15803,7 +15836,7 @@
       <c r="AD50" s="96"/>
       <c r="AE50" s="97"/>
     </row>
-    <row r="51" spans="3:35" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="3:35" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D51" s="145" t="s">
         <v>52</v>
       </c>
@@ -15851,7 +15884,7 @@
       <c r="AD51" s="99"/>
       <c r="AE51" s="100"/>
     </row>
-    <row r="52" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="52" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D52" s="95" t="s">
         <v>98</v>
       </c>
@@ -15899,7 +15932,7 @@
       <c r="AD52" s="96"/>
       <c r="AE52" s="97"/>
     </row>
-    <row r="53" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="53" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D53" s="1" t="s">
         <v>121</v>
       </c>
@@ -15907,7 +15940,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="54" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="54" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D54" s="1" t="s">
         <v>15</v>
       </c>
@@ -15915,7 +15948,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="55" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="55" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D55" s="1" t="s">
         <v>16</v>
       </c>
@@ -15923,12 +15956,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="56" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="56" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="E56" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="57" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="57" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D57" s="1" t="s">
         <v>122</v>
       </c>
@@ -15961,7 +15994,7 @@
       <c r="AH57" s="23"/>
       <c r="AI57" s="23"/>
     </row>
-    <row r="58" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="58" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="J58" s="23"/>
       <c r="K58" s="23"/>
       <c r="L58" s="23"/>
@@ -15988,38 +16021,38 @@
       <c r="AG58" s="23"/>
       <c r="AH58" s="23"/>
     </row>
-    <row r="59" spans="3:35" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="60" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="59" spans="3:35" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="60" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="C60" s="58" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="61" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="61" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="C61" s="58"/>
     </row>
-    <row r="62" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="62" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D62" s="24" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="63" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="63" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D63" s="24"/>
     </row>
-    <row r="64" spans="3:35" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="64" spans="3:35" ht="10.75" x14ac:dyDescent="0.2">
       <c r="C64" s="58" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="65" spans="3:23" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="65" spans="3:23" ht="10.75" x14ac:dyDescent="0.2">
       <c r="C65" s="58"/>
     </row>
-    <row r="66" spans="3:23" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="66" spans="3:23" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D66" s="1" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="67" spans="3:23" ht="11.25" x14ac:dyDescent="0.15"/>
-    <row r="68" spans="3:23" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="67" spans="3:23" ht="10.75" x14ac:dyDescent="0.2"/>
+    <row r="68" spans="3:23" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D68" s="15" t="s">
         <v>11</v>
       </c>
@@ -16027,13 +16060,13 @@
         <v>93</v>
       </c>
     </row>
-    <row r="69" spans="3:23" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="69" spans="3:23" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D69" s="15"/>
       <c r="E69" s="1" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="70" spans="3:23" s="17" customFormat="1" ht="12" x14ac:dyDescent="0.15">
+    <row r="70" spans="3:23" s="17" customFormat="1" ht="11.6" x14ac:dyDescent="0.2">
       <c r="E70" s="42" t="s">
         <v>221</v>
       </c>
@@ -16056,7 +16089,7 @@
       <c r="V70" s="16"/>
       <c r="W70" s="16"/>
     </row>
-    <row r="71" spans="3:23" s="17" customFormat="1" ht="12" x14ac:dyDescent="0.15">
+    <row r="71" spans="3:23" s="17" customFormat="1" ht="11.6" x14ac:dyDescent="0.2">
       <c r="E71" s="42" t="s">
         <v>222</v>
       </c>
@@ -16079,7 +16112,7 @@
       <c r="V71" s="16"/>
       <c r="W71" s="16"/>
     </row>
-    <row r="72" spans="3:23" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="72" spans="3:23" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D72" s="15" t="s">
         <v>12</v>
       </c>
@@ -16087,7 +16120,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="73" spans="3:23" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="73" spans="3:23" ht="10.75" x14ac:dyDescent="0.2">
       <c r="D73" s="15" t="s">
         <v>94</v>
       </c>
@@ -16184,13 +16217,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AK194"/>
-  <sheetFormatPr defaultColWidth="4.83203125" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="4.81640625" defaultRowHeight="10.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="9" width="4.83203125" style="37" customWidth="1"/>
-    <col min="10" max="16384" width="4.83203125" style="37"/>
+    <col min="1" max="9" width="4.81640625" style="37" customWidth="1"/>
+    <col min="10" max="16384" width="4.81640625" style="37"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:35" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="107" t="s">
         <v>225</v>
       </c>
@@ -16240,12 +16273,12 @@
       <c r="AF1" s="148"/>
       <c r="AG1" s="149">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>43336</v>
+        <v>45565</v>
       </c>
       <c r="AH1" s="150"/>
       <c r="AI1" s="151"/>
     </row>
-    <row r="2" spans="1:35" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:35" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="107" t="s">
         <v>228</v>
       </c>
@@ -16295,7 +16328,7 @@
       <c r="AH2" s="150"/>
       <c r="AI2" s="151"/>
     </row>
-    <row r="3" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="107" t="s">
         <v>230</v>
       </c>
@@ -16343,14 +16376,14 @@
       <c r="AH3" s="150"/>
       <c r="AI3" s="151"/>
     </row>
-    <row r="4" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="6" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="7" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C7" s="18" t="s">
         <v>124</v>
       </c>
@@ -16358,52 +16391,52 @@
         <v>106</v>
       </c>
     </row>
-    <row r="8" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C8" s="18"/>
     </row>
-    <row r="9" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C9" s="18"/>
       <c r="D9" s="25" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="10" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C10" s="18"/>
       <c r="D10" s="24" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="11" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C11" s="18"/>
       <c r="D11" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="12" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C12" s="18"/>
     </row>
-    <row r="13" spans="1:35" s="25" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:35" s="25" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C13" s="26"/>
       <c r="D13" s="25" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="14" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C14" s="18"/>
       <c r="D14" s="25" t="s">
         <v>204</v>
       </c>
       <c r="E14" s="25"/>
     </row>
-    <row r="15" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C15" s="18"/>
       <c r="D15" s="25"/>
       <c r="E15" s="25"/>
     </row>
-    <row r="16" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C16" s="18"/>
     </row>
-    <row r="17" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C17" s="18" t="s">
         <v>17</v>
       </c>
@@ -16411,137 +16444,137 @@
         <v>162</v>
       </c>
     </row>
-    <row r="18" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C18" s="18"/>
     </row>
-    <row r="19" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C19" s="18"/>
       <c r="D19" s="24" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="20" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C20" s="18"/>
       <c r="D20" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="21" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C21" s="18"/>
     </row>
-    <row r="22" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C22" s="18"/>
     </row>
-    <row r="23" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C23" s="18"/>
     </row>
-    <row r="24" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C24" s="18"/>
     </row>
-    <row r="25" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C25" s="18"/>
     </row>
-    <row r="26" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C26" s="18"/>
     </row>
-    <row r="27" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C27" s="18"/>
       <c r="AK27" s="24"/>
     </row>
-    <row r="28" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C28" s="18"/>
       <c r="AK28" s="24"/>
     </row>
-    <row r="29" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C29" s="18"/>
       <c r="Z29" s="1" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="30" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C30" s="18"/>
     </row>
-    <row r="31" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C31" s="18"/>
     </row>
-    <row r="32" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="3:37" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C32" s="18"/>
     </row>
-    <row r="33" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C33" s="18"/>
     </row>
-    <row r="34" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C34" s="18"/>
     </row>
-    <row r="35" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C35" s="18"/>
     </row>
-    <row r="36" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C36" s="18"/>
       <c r="D36" s="74"/>
     </row>
-    <row r="37" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C37" s="18"/>
       <c r="D37" s="37"/>
     </row>
-    <row r="38" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C38" s="18"/>
     </row>
-    <row r="39" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C39" s="18"/>
     </row>
-    <row r="40" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C40" s="18"/>
     </row>
-    <row r="41" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C41" s="18"/>
     </row>
-    <row r="42" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C42" s="18"/>
       <c r="D42" s="24" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="43" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C43" s="18"/>
     </row>
-    <row r="44" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C44" s="18"/>
       <c r="E44" s="24" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="45" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C45" s="18"/>
       <c r="E45" s="24" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="46" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C46" s="18"/>
       <c r="E46" s="24" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="47" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C47" s="18"/>
     </row>
-    <row r="48" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="3:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C48" s="18"/>
       <c r="D48" s="24" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="49" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C49" s="18"/>
       <c r="D49" s="24" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="50" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C50" s="18"/>
     </row>
-    <row r="51" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C51" s="18"/>
       <c r="D51" s="75" t="s">
         <v>310</v>
@@ -16572,7 +16605,7 @@
       <c r="X51" s="78"/>
       <c r="Y51" s="77"/>
     </row>
-    <row r="52" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C52" s="18"/>
       <c r="D52" s="79" t="s">
         <v>313</v>
@@ -16603,7 +16636,7 @@
       <c r="X52" s="72"/>
       <c r="Y52" s="84"/>
     </row>
-    <row r="53" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C53" s="18"/>
       <c r="D53" s="85"/>
       <c r="E53" s="86"/>
@@ -16632,7 +16665,7 @@
       <c r="X53" s="72"/>
       <c r="Y53" s="84"/>
     </row>
-    <row r="54" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C54" s="18"/>
       <c r="D54" s="79" t="s">
         <v>316</v>
@@ -16663,7 +16696,7 @@
       <c r="X54" s="72"/>
       <c r="Y54" s="84"/>
     </row>
-    <row r="55" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C55" s="18"/>
       <c r="D55" s="85"/>
       <c r="E55" s="86"/>
@@ -16692,7 +16725,7 @@
       <c r="X55" s="72"/>
       <c r="Y55" s="84"/>
     </row>
-    <row r="56" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C56" s="18"/>
       <c r="D56" s="79" t="s">
         <v>318</v>
@@ -16723,7 +16756,7 @@
       <c r="X56" s="72"/>
       <c r="Y56" s="84"/>
     </row>
-    <row r="57" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C57" s="18"/>
       <c r="D57" s="88"/>
       <c r="E57" s="86"/>
@@ -16752,13 +16785,13 @@
       <c r="X57" s="72"/>
       <c r="Y57" s="84"/>
     </row>
-    <row r="58" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C58" s="18"/>
       <c r="D58" s="24"/>
       <c r="E58" s="24"/>
       <c r="I58" s="24"/>
     </row>
-    <row r="59" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C59" s="18"/>
       <c r="D59" s="24" t="s">
         <v>320</v>
@@ -16766,7 +16799,7 @@
       <c r="E59" s="24"/>
       <c r="I59" s="24"/>
     </row>
-    <row r="60" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C60" s="18"/>
       <c r="D60" s="24" t="s">
         <v>321</v>
@@ -16774,7 +16807,7 @@
       <c r="E60" s="24"/>
       <c r="I60" s="24"/>
     </row>
-    <row r="61" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C61" s="18"/>
       <c r="D61" s="24" t="s">
         <v>322</v>
@@ -16782,13 +16815,13 @@
       <c r="E61" s="24"/>
       <c r="I61" s="24"/>
     </row>
-    <row r="62" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C62" s="18"/>
       <c r="D62" s="24"/>
       <c r="E62" s="24"/>
       <c r="I62" s="24"/>
     </row>
-    <row r="63" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C63" s="18"/>
       <c r="D63" s="24" t="s">
         <v>323</v>
@@ -16796,7 +16829,7 @@
       <c r="E63" s="24"/>
       <c r="I63" s="24"/>
     </row>
-    <row r="64" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="3:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C64" s="18"/>
       <c r="D64" s="24" t="s">
         <v>324</v>
@@ -16804,13 +16837,13 @@
       <c r="E64" s="24"/>
       <c r="I64" s="24"/>
     </row>
-    <row r="65" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C65" s="18"/>
       <c r="D65" s="24"/>
       <c r="E65" s="24"/>
       <c r="I65" s="24"/>
     </row>
-    <row r="66" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C66" s="18"/>
       <c r="D66" s="24" t="s">
         <v>325</v>
@@ -16818,7 +16851,7 @@
       <c r="E66" s="24"/>
       <c r="I66" s="24"/>
     </row>
-    <row r="67" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C67" s="18"/>
       <c r="D67" s="24" t="s">
         <v>326</v>
@@ -16826,15 +16859,15 @@
       <c r="E67" s="24"/>
       <c r="I67" s="24"/>
     </row>
-    <row r="70" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C70" s="18" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="71" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C71" s="18"/>
     </row>
-    <row r="72" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C72" s="37"/>
       <c r="D72" s="37" t="s">
         <v>108</v>
@@ -16866,7 +16899,7 @@
       <c r="AC72" s="37"/>
       <c r="AD72" s="37"/>
     </row>
-    <row r="73" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C73" s="37"/>
       <c r="D73" s="37" t="s">
         <v>126</v>
@@ -16898,7 +16931,7 @@
       <c r="AC73" s="37"/>
       <c r="AD73" s="37"/>
     </row>
-    <row r="74" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
       <c r="E74" s="37"/>
@@ -16928,7 +16961,7 @@
       <c r="AC74" s="37"/>
       <c r="AD74" s="37"/>
     </row>
-    <row r="75" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C75" s="37"/>
       <c r="D75" s="37" t="s">
         <v>275</v>
@@ -16960,7 +16993,7 @@
       <c r="AC75" s="37"/>
       <c r="AD75" s="37"/>
     </row>
-    <row r="76" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C76" s="37"/>
       <c r="D76" s="37"/>
       <c r="E76" s="37"/>
@@ -16990,7 +17023,7 @@
       <c r="AC76" s="37"/>
       <c r="AD76" s="37"/>
     </row>
-    <row r="77" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C77" s="37"/>
       <c r="D77" s="37"/>
       <c r="E77" s="37" t="s">
@@ -17022,7 +17055,7 @@
       <c r="AC77" s="37"/>
       <c r="AD77" s="37"/>
     </row>
-    <row r="78" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C78" s="37"/>
       <c r="D78" s="37"/>
       <c r="E78" s="37"/>
@@ -17052,7 +17085,7 @@
       <c r="AC78" s="37"/>
       <c r="AD78" s="37"/>
     </row>
-    <row r="79" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C79" s="37"/>
       <c r="D79" s="37"/>
       <c r="E79" s="206" t="s">
@@ -17092,7 +17125,7 @@
       <c r="AG79" s="207"/>
       <c r="AH79" s="208"/>
     </row>
-    <row r="80" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C80" s="37"/>
       <c r="D80" s="37"/>
       <c r="E80" s="215" t="s">
@@ -17132,7 +17165,7 @@
       <c r="AG80" s="210"/>
       <c r="AH80" s="211"/>
     </row>
-    <row r="81" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C81" s="37"/>
       <c r="D81" s="37"/>
       <c r="E81" s="217"/>
@@ -17166,7 +17199,7 @@
       <c r="AG81" s="213"/>
       <c r="AH81" s="214"/>
     </row>
-    <row r="82" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C82" s="37"/>
       <c r="D82" s="37"/>
       <c r="E82" s="95" t="s">
@@ -17206,7 +17239,7 @@
       <c r="AG82" s="96"/>
       <c r="AH82" s="97"/>
     </row>
-    <row r="83" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C83" s="37"/>
       <c r="D83" s="37"/>
       <c r="E83" s="95" t="s">
@@ -17246,7 +17279,7 @@
       <c r="AG83" s="96"/>
       <c r="AH83" s="97"/>
     </row>
-    <row r="84" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
       <c r="E84" s="215" t="s">
@@ -17286,7 +17319,7 @@
       <c r="AG84" s="210"/>
       <c r="AH84" s="211"/>
     </row>
-    <row r="85" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C85" s="37"/>
       <c r="D85" s="37"/>
       <c r="E85" s="217"/>
@@ -17320,13 +17353,13 @@
       <c r="AG85" s="213"/>
       <c r="AH85" s="214"/>
     </row>
-    <row r="86" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C86" s="37"/>
       <c r="D86" s="37"/>
       <c r="AC86" s="37"/>
       <c r="AD86" s="37"/>
     </row>
-    <row r="87" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C87" s="37"/>
       <c r="D87" s="37" t="s">
         <v>276</v>
@@ -17334,27 +17367,27 @@
       <c r="AC87" s="37"/>
       <c r="AD87" s="37"/>
     </row>
-    <row r="88" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C88" s="37"/>
       <c r="D88" s="37"/>
       <c r="AC88" s="37"/>
       <c r="AD88" s="37"/>
     </row>
-    <row r="89" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="E89" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="90" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="91" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="91" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="E91" s="40" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="92" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="E92" s="40"/>
     </row>
-    <row r="93" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="E93" s="206" t="s">
         <v>116</v>
       </c>
@@ -17392,7 +17425,7 @@
       <c r="AG93" s="207"/>
       <c r="AH93" s="208"/>
     </row>
-    <row r="94" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="E94" s="215" t="s">
         <v>28</v>
       </c>
@@ -17430,7 +17463,7 @@
       <c r="AG94" s="210"/>
       <c r="AH94" s="211"/>
     </row>
-    <row r="95" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="E95" s="217"/>
       <c r="F95" s="220"/>
       <c r="G95" s="220"/>
@@ -17462,7 +17495,7 @@
       <c r="AG95" s="213"/>
       <c r="AH95" s="214"/>
     </row>
-    <row r="96" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="3:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="E96" s="95" t="s">
         <v>29</v>
       </c>
@@ -17500,7 +17533,7 @@
       <c r="AG96" s="96"/>
       <c r="AH96" s="97"/>
     </row>
-    <row r="97" spans="5:34" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="5:34" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="E97" s="95" t="s">
         <v>30</v>
       </c>
@@ -17538,7 +17571,7 @@
       <c r="AG97" s="96"/>
       <c r="AH97" s="97"/>
     </row>
-    <row r="98" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E98" s="215" t="s">
         <v>128</v>
       </c>
@@ -17576,7 +17609,7 @@
       <c r="AG98" s="210"/>
       <c r="AH98" s="211"/>
     </row>
-    <row r="99" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E99" s="217"/>
       <c r="F99" s="220"/>
       <c r="G99" s="220"/>
@@ -17608,33 +17641,33 @@
       <c r="AG99" s="213"/>
       <c r="AH99" s="214"/>
     </row>
-    <row r="100" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="101" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="102" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E102" s="40" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="103" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E103" s="40"/>
     </row>
-    <row r="104" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F104" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="105" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F105" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="106" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G106" s="24" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="107" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="108" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E108" s="206" t="s">
         <v>116</v>
       </c>
@@ -17672,7 +17705,7 @@
       <c r="AG108" s="207"/>
       <c r="AH108" s="208"/>
     </row>
-    <row r="109" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E109" s="215" t="s">
         <v>129</v>
       </c>
@@ -17710,7 +17743,7 @@
       <c r="AG109" s="210"/>
       <c r="AH109" s="211"/>
     </row>
-    <row r="110" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E110" s="217"/>
       <c r="F110" s="220"/>
       <c r="G110" s="220"/>
@@ -17742,7 +17775,7 @@
       <c r="AG110" s="213"/>
       <c r="AH110" s="214"/>
     </row>
-    <row r="111" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E111" s="215" t="s">
         <v>23</v>
       </c>
@@ -17780,7 +17813,7 @@
       <c r="AG111" s="210"/>
       <c r="AH111" s="211"/>
     </row>
-    <row r="112" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E112" s="221"/>
       <c r="F112" s="222"/>
       <c r="G112" s="222"/>
@@ -17812,7 +17845,7 @@
       <c r="AG112" s="229"/>
       <c r="AH112" s="230"/>
     </row>
-    <row r="113" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E113" s="221"/>
       <c r="F113" s="222"/>
       <c r="G113" s="222"/>
@@ -17844,7 +17877,7 @@
       <c r="AG113" s="229"/>
       <c r="AH113" s="230"/>
     </row>
-    <row r="114" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E114" s="221"/>
       <c r="F114" s="222"/>
       <c r="G114" s="222"/>
@@ -17876,7 +17909,7 @@
       <c r="AG114" s="229"/>
       <c r="AH114" s="230"/>
     </row>
-    <row r="115" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E115" s="217"/>
       <c r="F115" s="220"/>
       <c r="G115" s="220"/>
@@ -17908,52 +17941,52 @@
       <c r="AG115" s="213"/>
       <c r="AH115" s="214"/>
     </row>
-    <row r="116" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="117" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="118" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D118" s="37" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="119" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D119" s="37"/>
     </row>
-    <row r="120" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E120" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="121" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E121" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="122" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E122" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="123" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="124" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E124" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="125" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F125" s="24" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="126" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E127" s="40" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="128" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E128" s="40"/>
     </row>
-    <row r="129" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E129" s="206" t="s">
         <v>116</v>
       </c>
@@ -17991,7 +18024,7 @@
       <c r="AG129" s="207"/>
       <c r="AH129" s="208"/>
     </row>
-    <row r="130" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E130" s="215" t="s">
         <v>28</v>
       </c>
@@ -18029,7 +18062,7 @@
       <c r="AG130" s="210"/>
       <c r="AH130" s="211"/>
     </row>
-    <row r="131" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E131" s="217"/>
       <c r="F131" s="220"/>
       <c r="G131" s="220"/>
@@ -18061,7 +18094,7 @@
       <c r="AG131" s="213"/>
       <c r="AH131" s="214"/>
     </row>
-    <row r="132" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E132" s="215" t="s">
         <v>23</v>
       </c>
@@ -18099,7 +18132,7 @@
       <c r="AG132" s="210"/>
       <c r="AH132" s="211"/>
     </row>
-    <row r="133" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E133" s="221"/>
       <c r="F133" s="222"/>
       <c r="G133" s="222"/>
@@ -18131,7 +18164,7 @@
       <c r="AG133" s="229"/>
       <c r="AH133" s="230"/>
     </row>
-    <row r="134" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E134" s="217"/>
       <c r="F134" s="220"/>
       <c r="G134" s="220"/>
@@ -18163,17 +18196,17 @@
       <c r="AG134" s="213"/>
       <c r="AH134" s="214"/>
     </row>
-    <row r="135" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E137" s="40" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="138" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E138" s="40"/>
     </row>
-    <row r="139" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E139" s="206" t="s">
         <v>116</v>
       </c>
@@ -18211,7 +18244,7 @@
       <c r="AG139" s="207"/>
       <c r="AH139" s="208"/>
     </row>
-    <row r="140" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E140" s="215" t="s">
         <v>28</v>
       </c>
@@ -18249,7 +18282,7 @@
       <c r="AG140" s="210"/>
       <c r="AH140" s="211"/>
     </row>
-    <row r="141" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E141" s="217"/>
       <c r="F141" s="220"/>
       <c r="G141" s="220"/>
@@ -18281,7 +18314,7 @@
       <c r="AG141" s="213"/>
       <c r="AH141" s="214"/>
     </row>
-    <row r="142" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E142" s="215" t="s">
         <v>23</v>
       </c>
@@ -18319,7 +18352,7 @@
       <c r="AG142" s="210"/>
       <c r="AH142" s="211"/>
     </row>
-    <row r="143" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="143" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E143" s="221"/>
       <c r="F143" s="222"/>
       <c r="G143" s="222"/>
@@ -18351,7 +18384,7 @@
       <c r="AG143" s="229"/>
       <c r="AH143" s="230"/>
     </row>
-    <row r="144" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="144" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E144" s="221"/>
       <c r="F144" s="222"/>
       <c r="G144" s="222"/>
@@ -18383,7 +18416,7 @@
       <c r="AG144" s="229"/>
       <c r="AH144" s="230"/>
     </row>
-    <row r="145" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="145" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E145" s="217"/>
       <c r="F145" s="220"/>
       <c r="G145" s="220"/>
@@ -18415,7 +18448,7 @@
       <c r="AG145" s="213"/>
       <c r="AH145" s="214"/>
     </row>
-    <row r="146" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="146" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E146" s="215" t="s">
         <v>130</v>
       </c>
@@ -18453,7 +18486,7 @@
       <c r="AG146" s="210"/>
       <c r="AH146" s="211"/>
     </row>
-    <row r="147" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="147" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E147" s="221"/>
       <c r="F147" s="222"/>
       <c r="G147" s="222"/>
@@ -18485,7 +18518,7 @@
       <c r="AG147" s="229"/>
       <c r="AH147" s="230"/>
     </row>
-    <row r="148" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="148" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E148" s="217"/>
       <c r="F148" s="220"/>
       <c r="G148" s="220"/>
@@ -18517,7 +18550,7 @@
       <c r="AG148" s="213"/>
       <c r="AH148" s="214"/>
     </row>
-    <row r="149" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="149" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E149" s="215" t="s">
         <v>131</v>
       </c>
@@ -18538,7 +18571,7 @@
       <c r="AA149" s="37"/>
       <c r="AH149" s="44"/>
     </row>
-    <row r="150" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E150" s="221"/>
       <c r="F150" s="222"/>
       <c r="G150" s="222"/>
@@ -18555,7 +18588,7 @@
       <c r="AA150" s="37"/>
       <c r="AH150" s="44"/>
     </row>
-    <row r="151" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E151" s="221"/>
       <c r="F151" s="222"/>
       <c r="G151" s="222"/>
@@ -18572,7 +18605,7 @@
       <c r="AA151" s="37"/>
       <c r="AH151" s="44"/>
     </row>
-    <row r="152" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="152" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E152" s="221"/>
       <c r="F152" s="222"/>
       <c r="G152" s="222"/>
@@ -18588,7 +18621,7 @@
       <c r="AA152" s="37"/>
       <c r="AH152" s="44"/>
     </row>
-    <row r="153" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="153" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E153" s="221"/>
       <c r="F153" s="222"/>
       <c r="G153" s="222"/>
@@ -18605,7 +18638,7 @@
       <c r="AA153" s="37"/>
       <c r="AH153" s="44"/>
     </row>
-    <row r="154" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="154" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E154" s="221"/>
       <c r="F154" s="222"/>
       <c r="G154" s="222"/>
@@ -18623,7 +18656,7 @@
       <c r="AA154" s="37"/>
       <c r="AH154" s="44"/>
     </row>
-    <row r="155" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="155" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E155" s="221"/>
       <c r="F155" s="222"/>
       <c r="G155" s="222"/>
@@ -18641,7 +18674,7 @@
       <c r="AA155" s="37"/>
       <c r="AH155" s="44"/>
     </row>
-    <row r="156" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="156" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E156" s="221"/>
       <c r="F156" s="222"/>
       <c r="G156" s="222"/>
@@ -18659,7 +18692,7 @@
       <c r="AA156" s="37"/>
       <c r="AH156" s="44"/>
     </row>
-    <row r="157" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="157" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E157" s="221"/>
       <c r="F157" s="222"/>
       <c r="G157" s="222"/>
@@ -18677,7 +18710,7 @@
       <c r="AA157" s="37"/>
       <c r="AH157" s="44"/>
     </row>
-    <row r="158" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="158" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E158" s="221"/>
       <c r="F158" s="222"/>
       <c r="G158" s="222"/>
@@ -18695,7 +18728,7 @@
       <c r="AA158" s="37"/>
       <c r="AH158" s="44"/>
     </row>
-    <row r="159" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="159" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E159" s="221"/>
       <c r="F159" s="222"/>
       <c r="G159" s="222"/>
@@ -18713,7 +18746,7 @@
       <c r="AA159" s="37"/>
       <c r="AH159" s="44"/>
     </row>
-    <row r="160" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="160" spans="5:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E160" s="221"/>
       <c r="F160" s="222"/>
       <c r="G160" s="222"/>
@@ -18731,7 +18764,7 @@
       <c r="AA160" s="37"/>
       <c r="AH160" s="44"/>
     </row>
-    <row r="161" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="161" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E161" s="221"/>
       <c r="F161" s="222"/>
       <c r="G161" s="222"/>
@@ -18749,7 +18782,7 @@
       <c r="AA161" s="37"/>
       <c r="AH161" s="44"/>
     </row>
-    <row r="162" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="162" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E162" s="217"/>
       <c r="F162" s="220"/>
       <c r="G162" s="220"/>
@@ -18767,7 +18800,7 @@
       <c r="AA162" s="37"/>
       <c r="AH162" s="44"/>
     </row>
-    <row r="163" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="163" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E163" s="215" t="s">
         <v>133</v>
       </c>
@@ -18805,7 +18838,7 @@
       <c r="AG163" s="210"/>
       <c r="AH163" s="211"/>
     </row>
-    <row r="164" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="164" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E164" s="217"/>
       <c r="F164" s="220"/>
       <c r="G164" s="220"/>
@@ -18837,7 +18870,7 @@
       <c r="AG164" s="213"/>
       <c r="AH164" s="214"/>
     </row>
-    <row r="165" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="165" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E165" s="209" t="s">
         <v>259</v>
       </c>
@@ -18875,7 +18908,7 @@
       <c r="AG165" s="219"/>
       <c r="AH165" s="216"/>
     </row>
-    <row r="166" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="166" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E166" s="212"/>
       <c r="F166" s="213"/>
       <c r="G166" s="213"/>
@@ -18907,31 +18940,31 @@
       <c r="AG166" s="220"/>
       <c r="AH166" s="218"/>
     </row>
-    <row r="167" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="167" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D169" s="1" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="170" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="170" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E171" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="172" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="172" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E172" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="173" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="173" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E173" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="174" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2"/>
-    <row r="175" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="174" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="175" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="E175" s="45" t="s">
         <v>134</v>
       </c>
@@ -18962,7 +18995,7 @@
       <c r="AD175" s="47"/>
       <c r="AE175" s="48"/>
     </row>
-    <row r="176" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="176" spans="4:34" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E176" s="49"/>
       <c r="F176" s="37" t="s">
         <v>135</v>
@@ -18978,7 +19011,7 @@
       <c r="O176" s="37"/>
       <c r="AE176" s="50"/>
     </row>
-    <row r="177" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E177" s="49"/>
       <c r="F177" s="37"/>
       <c r="G177" s="37"/>
@@ -18994,7 +19027,7 @@
       <c r="O177" s="37"/>
       <c r="AE177" s="50"/>
     </row>
-    <row r="178" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E178" s="49"/>
       <c r="F178" s="37"/>
       <c r="G178" s="37"/>
@@ -19018,7 +19051,7 @@
       </c>
       <c r="AE178" s="50"/>
     </row>
-    <row r="179" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E179" s="49"/>
       <c r="F179" s="37"/>
       <c r="G179" s="37"/>
@@ -19037,7 +19070,7 @@
       </c>
       <c r="AE179" s="50"/>
     </row>
-    <row r="180" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E180" s="49"/>
       <c r="F180" s="37"/>
       <c r="G180" s="37"/>
@@ -19056,7 +19089,7 @@
       </c>
       <c r="AE180" s="50"/>
     </row>
-    <row r="181" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E181" s="49"/>
       <c r="F181" s="37"/>
       <c r="G181" s="37"/>
@@ -19075,7 +19108,7 @@
       </c>
       <c r="AE181" s="50"/>
     </row>
-    <row r="182" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E182" s="49"/>
       <c r="F182" s="37"/>
       <c r="G182" s="37"/>
@@ -19088,7 +19121,7 @@
       </c>
       <c r="AE182" s="50"/>
     </row>
-    <row r="183" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E183" s="49"/>
       <c r="F183" s="37"/>
       <c r="G183" s="37"/>
@@ -19104,7 +19137,7 @@
       <c r="O183" s="37"/>
       <c r="AE183" s="50"/>
     </row>
-    <row r="184" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E184" s="51"/>
       <c r="H184" s="37"/>
       <c r="I184" s="37"/>
@@ -19123,7 +19156,7 @@
       </c>
       <c r="AE184" s="50"/>
     </row>
-    <row r="185" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E185" s="51"/>
       <c r="H185" s="37"/>
       <c r="I185" s="37"/>
@@ -19137,7 +19170,7 @@
       </c>
       <c r="AE185" s="50"/>
     </row>
-    <row r="186" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E186" s="51"/>
       <c r="H186" s="37"/>
       <c r="I186" s="37"/>
@@ -19151,7 +19184,7 @@
       </c>
       <c r="AE186" s="50"/>
     </row>
-    <row r="187" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E187" s="51"/>
       <c r="H187" s="37"/>
       <c r="I187" s="37"/>
@@ -19165,7 +19198,7 @@
       </c>
       <c r="AE187" s="50"/>
     </row>
-    <row r="188" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E188" s="51"/>
       <c r="H188" s="37"/>
       <c r="I188" s="37"/>
@@ -19179,7 +19212,7 @@
       </c>
       <c r="AE188" s="50"/>
     </row>
-    <row r="189" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E189" s="51"/>
       <c r="H189" s="37"/>
       <c r="I189" s="37"/>
@@ -19193,7 +19226,7 @@
       </c>
       <c r="AE189" s="50"/>
     </row>
-    <row r="190" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E190" s="52"/>
       <c r="F190" s="53"/>
       <c r="G190" s="53"/>
@@ -19222,8 +19255,8 @@
       <c r="AD190" s="53"/>
       <c r="AE190" s="54"/>
     </row>
-    <row r="191" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.15"/>
-    <row r="192" spans="1:31" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:31" s="1" customFormat="1" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.2"/>
+    <row r="192" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A192" s="27"/>
       <c r="B192" s="27"/>
       <c r="C192" s="27"/>
@@ -19250,7 +19283,7 @@
       <c r="X192" s="27"/>
       <c r="Y192" s="27"/>
     </row>
-    <row r="193" spans="1:25" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A193" s="27"/>
       <c r="B193" s="27"/>
       <c r="C193" s="27"/>
@@ -19277,7 +19310,7 @@
       <c r="X193" s="27"/>
       <c r="Y193" s="27"/>
     </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A194" s="27"/>
       <c r="B194" s="27"/>
       <c r="C194" s="27"/>
@@ -19418,13 +19451,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AJ162"/>
-  <sheetFormatPr defaultColWidth="4.83203125" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="4.81640625" defaultRowHeight="10.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="9" width="4.83203125" style="37" customWidth="1"/>
-    <col min="10" max="16384" width="4.83203125" style="37"/>
+    <col min="1" max="9" width="4.81640625" style="37" customWidth="1"/>
+    <col min="10" max="16384" width="4.81640625" style="37"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:35" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="107" t="s">
         <v>225</v>
       </c>
@@ -19474,12 +19507,12 @@
       <c r="AF1" s="148"/>
       <c r="AG1" s="149">
         <f ca="1">IF(INDIRECT("変更履歴!AG1")&lt;&gt;"",INDIRECT("変更履歴!AG1"),"")</f>
-        <v>43336</v>
+        <v>45565</v>
       </c>
       <c r="AH1" s="150"/>
       <c r="AI1" s="151"/>
     </row>
-    <row r="2" spans="1:35" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:35" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="107" t="s">
         <v>228</v>
       </c>
@@ -19529,7 +19562,7 @@
       <c r="AH2" s="150"/>
       <c r="AI2" s="151"/>
     </row>
-    <row r="3" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="107" t="s">
         <v>230</v>
       </c>
@@ -19577,40 +19610,40 @@
       <c r="AH3" s="150"/>
       <c r="AI3" s="151"/>
     </row>
-    <row r="4" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B5" s="24" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="6" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B6" s="24"/>
     </row>
-    <row r="7" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C7" s="24" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="8" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C8" s="18"/>
     </row>
-    <row r="9" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C9" s="18"/>
       <c r="D9" s="24" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="10" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C10" s="18"/>
       <c r="D10" s="24"/>
     </row>
-    <row r="11" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="D11" s="18"/>
       <c r="E11" s="24" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="E12" s="27"/>
       <c r="F12" s="27"/>
       <c r="G12" s="27"/>
@@ -19634,7 +19667,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="E13" s="63" t="s">
         <v>125</v>
       </c>
@@ -19685,7 +19718,7 @@
       <c r="AH13" s="260"/>
       <c r="AI13" s="261"/>
     </row>
-    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E14" s="62">
         <v>1</v>
       </c>
@@ -19734,7 +19767,7 @@
       <c r="AH14" s="263"/>
       <c r="AI14" s="274"/>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="E15" s="62">
         <v>2</v>
       </c>
@@ -19771,7 +19804,7 @@
       <c r="AH15" s="266"/>
       <c r="AI15" s="275"/>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="E16" s="62">
         <v>3</v>
       </c>
@@ -19808,7 +19841,7 @@
       <c r="AH16" s="266"/>
       <c r="AI16" s="275"/>
     </row>
-    <row r="17" spans="4:35" x14ac:dyDescent="0.15">
+    <row r="17" spans="4:35" x14ac:dyDescent="0.2">
       <c r="E17" s="62">
         <v>4</v>
       </c>
@@ -19845,7 +19878,7 @@
       <c r="AH17" s="266"/>
       <c r="AI17" s="275"/>
     </row>
-    <row r="18" spans="4:35" x14ac:dyDescent="0.15">
+    <row r="18" spans="4:35" x14ac:dyDescent="0.2">
       <c r="E18" s="62">
         <v>5</v>
       </c>
@@ -19884,7 +19917,7 @@
       <c r="AH18" s="266"/>
       <c r="AI18" s="275"/>
     </row>
-    <row r="19" spans="4:35" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="4:35" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E19" s="62">
         <v>6</v>
       </c>
@@ -19921,7 +19954,7 @@
       <c r="AH19" s="266"/>
       <c r="AI19" s="275"/>
     </row>
-    <row r="20" spans="4:35" x14ac:dyDescent="0.15">
+    <row r="20" spans="4:35" x14ac:dyDescent="0.2">
       <c r="E20" s="62">
         <v>7</v>
       </c>
@@ -19958,7 +19991,7 @@
       <c r="AH20" s="266"/>
       <c r="AI20" s="275"/>
     </row>
-    <row r="21" spans="4:35" x14ac:dyDescent="0.15">
+    <row r="21" spans="4:35" x14ac:dyDescent="0.2">
       <c r="E21" s="62">
         <v>8</v>
       </c>
@@ -19995,7 +20028,7 @@
       <c r="AH21" s="266"/>
       <c r="AI21" s="275"/>
     </row>
-    <row r="22" spans="4:35" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="4:35" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E22" s="62">
         <v>9</v>
       </c>
@@ -20034,7 +20067,7 @@
       <c r="AH22" s="266"/>
       <c r="AI22" s="275"/>
     </row>
-    <row r="23" spans="4:35" ht="36" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="4:35" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E23" s="62">
         <v>10</v>
       </c>
@@ -20073,7 +20106,7 @@
       <c r="AH23" s="269"/>
       <c r="AI23" s="276"/>
     </row>
-    <row r="24" spans="4:35" x14ac:dyDescent="0.15">
+    <row r="24" spans="4:35" x14ac:dyDescent="0.2">
       <c r="E24" s="25"/>
       <c r="F24" s="29"/>
       <c r="G24" s="29"/>
@@ -20094,7 +20127,7 @@
       <c r="V24" s="30"/>
       <c r="W24" s="27"/>
     </row>
-    <row r="25" spans="4:35" x14ac:dyDescent="0.15">
+    <row r="25" spans="4:35" x14ac:dyDescent="0.2">
       <c r="E25" s="27" t="s">
         <v>262</v>
       </c>
@@ -20117,7 +20150,7 @@
       <c r="V25" s="27"/>
       <c r="W25" s="27"/>
     </row>
-    <row r="26" spans="4:35" x14ac:dyDescent="0.15">
+    <row r="26" spans="4:35" x14ac:dyDescent="0.2">
       <c r="E26" s="27"/>
       <c r="F26" s="27" t="s">
         <v>209</v>
@@ -20140,7 +20173,7 @@
       <c r="V26" s="27"/>
       <c r="W26" s="27"/>
     </row>
-    <row r="27" spans="4:35" x14ac:dyDescent="0.15">
+    <row r="27" spans="4:35" x14ac:dyDescent="0.2">
       <c r="E27" s="27"/>
       <c r="F27" s="27" t="s">
         <v>345</v>
@@ -20163,65 +20196,65 @@
       <c r="V27" s="27"/>
       <c r="W27" s="27"/>
     </row>
-    <row r="28" spans="4:35" x14ac:dyDescent="0.15">
+    <row r="28" spans="4:35" x14ac:dyDescent="0.2">
       <c r="F28" s="37" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="31" spans="4:35" x14ac:dyDescent="0.15">
+    <row r="31" spans="4:35" x14ac:dyDescent="0.2">
       <c r="D31" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="33" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="E33" s="59" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="34" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="F34" s="1" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="35" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="36" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="36" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="F36" s="24" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="37" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="G37" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="38" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="G38" s="1" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="39" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="G39" s="1" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="40" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="41" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="G41" s="24" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="42" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H42" s="1" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="43" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="44" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H44" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="45" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H45" s="248" t="s">
         <v>77</v>
       </c>
@@ -20250,7 +20283,7 @@
       <c r="AC45" s="249"/>
       <c r="AD45" s="250"/>
     </row>
-    <row r="46" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H46" s="245" t="s">
         <v>139</v>
       </c>
@@ -20287,7 +20320,7 @@
       <c r="AC46" s="244"/>
       <c r="AD46" s="233"/>
     </row>
-    <row r="47" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H47" s="245" t="s">
         <v>143</v>
       </c>
@@ -20328,7 +20361,7 @@
       <c r="AC47" s="244"/>
       <c r="AD47" s="233"/>
     </row>
-    <row r="48" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="5:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H48" s="245" t="s">
         <v>145</v>
       </c>
@@ -20369,7 +20402,7 @@
       <c r="AC48" s="244"/>
       <c r="AD48" s="233"/>
     </row>
-    <row r="49" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H49" s="245" t="s">
         <v>147</v>
       </c>
@@ -20406,24 +20439,24 @@
       <c r="AC49" s="244"/>
       <c r="AD49" s="233"/>
     </row>
-    <row r="50" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="51" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="51" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="G51" s="24" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="52" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H52" s="1" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="53" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="54" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="54" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H54" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="55" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H55" s="248" t="s">
         <v>77</v>
       </c>
@@ -20457,7 +20490,7 @@
       <c r="AH55" s="249"/>
       <c r="AI55" s="250"/>
     </row>
-    <row r="56" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H56" s="245" t="s">
         <v>139</v>
       </c>
@@ -20503,7 +20536,7 @@
       <c r="AH56" s="244"/>
       <c r="AI56" s="233"/>
     </row>
-    <row r="57" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H57" s="245" t="s">
         <v>143</v>
       </c>
@@ -20545,7 +20578,7 @@
       <c r="AH57" s="244"/>
       <c r="AI57" s="233"/>
     </row>
-    <row r="58" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H58" s="245" t="s">
         <v>145</v>
       </c>
@@ -20595,7 +20628,7 @@
       <c r="AH58" s="244"/>
       <c r="AI58" s="233"/>
     </row>
-    <row r="59" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H59" s="245" t="s">
         <v>147</v>
       </c>
@@ -20633,51 +20666,51 @@
       <c r="AH59" s="244"/>
       <c r="AI59" s="233"/>
     </row>
-    <row r="60" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="61" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="62" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="61" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="62" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="G62" s="24" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="63" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H63" s="1" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="64" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="65" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="7:35" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="65" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="G65" s="24" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="66" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H66" s="1" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="67" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H67" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="68" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H68" s="1" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="69" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="70" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="70" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="G70" s="24" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="71" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H71" s="1" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="72" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H72" s="15" t="s">
         <v>11</v>
       </c>
@@ -20685,7 +20718,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="73" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H73" s="15" t="s">
         <v>11</v>
       </c>
@@ -20693,7 +20726,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="74" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H74" s="15" t="s">
         <v>11</v>
       </c>
@@ -20701,20 +20734,20 @@
         <v>200</v>
       </c>
     </row>
-    <row r="75" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H75" s="41" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="76" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H76" s="41"/>
     </row>
-    <row r="77" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H77" s="41" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="78" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H78" s="68" t="s">
         <v>77</v>
       </c>
@@ -20743,7 +20776,7 @@
       <c r="AC78" s="69"/>
       <c r="AD78" s="70"/>
     </row>
-    <row r="79" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H79" s="71" t="s">
         <v>139</v>
       </c>
@@ -20784,7 +20817,7 @@
       <c r="AC79" s="244"/>
       <c r="AD79" s="233"/>
     </row>
-    <row r="80" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="7:30" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H80" s="71" t="s">
         <v>143</v>
       </c>
@@ -20825,7 +20858,7 @@
       <c r="AC80" s="244"/>
       <c r="AD80" s="233"/>
     </row>
-    <row r="81" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H81" s="71" t="s">
         <v>145</v>
       </c>
@@ -20866,63 +20899,63 @@
       <c r="AC81" s="244"/>
       <c r="AD81" s="233"/>
     </row>
-    <row r="82" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H82" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="84" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="84" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="G84" s="24" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="85" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H85" s="1" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="86" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="87" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="87" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="G87" s="24" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="88" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="H88" s="1" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="91" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C91" s="24" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="92" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C92" s="18"/>
     </row>
-    <row r="93" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C93" s="18"/>
       <c r="D93" s="24" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="94" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C94" s="18"/>
     </row>
-    <row r="95" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="3:35" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="D95" s="18"/>
       <c r="E95" s="24" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="96" spans="3:35" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="3:35" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="V96" s="38"/>
       <c r="AI96" s="38" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="97" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E97" s="64" t="s">
         <v>250</v>
       </c>
@@ -20971,7 +21004,7 @@
       <c r="AH97" s="173"/>
       <c r="AI97" s="174"/>
     </row>
-    <row r="98" spans="1:36" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:36" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E98" s="62">
         <v>1</v>
       </c>
@@ -21020,7 +21053,7 @@
       <c r="AH98" s="238"/>
       <c r="AI98" s="239"/>
     </row>
-    <row r="99" spans="1:36" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:36" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E99" s="62">
         <v>2</v>
       </c>
@@ -21065,7 +21098,7 @@
       <c r="AH99" s="238"/>
       <c r="AI99" s="239"/>
     </row>
-    <row r="100" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:36" x14ac:dyDescent="0.2">
       <c r="E100" s="25"/>
       <c r="F100" s="29"/>
       <c r="G100" s="29"/>
@@ -21086,7 +21119,7 @@
       <c r="V100" s="30"/>
       <c r="W100" s="27"/>
     </row>
-    <row r="101" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D101" t="s">
         <v>358</v>
       </c>
@@ -21110,7 +21143,7 @@
       <c r="V101" s="30"/>
       <c r="W101" s="27"/>
     </row>
-    <row r="102" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:36" x14ac:dyDescent="0.2">
       <c r="E102" s="25"/>
       <c r="F102" s="29"/>
       <c r="G102" s="29"/>
@@ -21131,7 +21164,7 @@
       <c r="V102" s="30"/>
       <c r="W102" s="27"/>
     </row>
-    <row r="103" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -21170,7 +21203,7 @@
       <c r="AI103" s="1"/>
       <c r="AJ103" s="1"/>
     </row>
-    <row r="104" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -21208,7 +21241,7 @@
       <c r="AI104" s="1"/>
       <c r="AJ104" s="1"/>
     </row>
-    <row r="105" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -21244,7 +21277,7 @@
       <c r="AI105" s="1"/>
       <c r="AJ105" s="1"/>
     </row>
-    <row r="106" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -21283,7 +21316,7 @@
       <c r="AI106" s="1"/>
       <c r="AJ106" s="1"/>
     </row>
-    <row r="107" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -21322,7 +21355,7 @@
       <c r="AI107" s="1"/>
       <c r="AJ107" s="1"/>
     </row>
-    <row r="108" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -21359,7 +21392,7 @@
       <c r="AI108" s="1"/>
       <c r="AJ108" s="1"/>
     </row>
-    <row r="109" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -21398,7 +21431,7 @@
       <c r="AI109" s="1"/>
       <c r="AJ109" s="1"/>
     </row>
-    <row r="110" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -21437,7 +21470,7 @@
       <c r="AI110" s="1"/>
       <c r="AJ110" s="1"/>
     </row>
-    <row r="111" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -21476,7 +21509,7 @@
       <c r="AI111" s="1"/>
       <c r="AJ111" s="1"/>
     </row>
-    <row r="112" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -21514,7 +21547,7 @@
       <c r="AI112" s="1"/>
       <c r="AJ112" s="1"/>
     </row>
-    <row r="113" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -21551,36 +21584,36 @@
       <c r="AH113" s="1"/>
       <c r="AI113" s="1"/>
     </row>
-    <row r="114" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C114" s="24" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="115" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C115" s="18"/>
     </row>
-    <row r="116" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C116" s="18"/>
       <c r="D116" s="24" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="117" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C117" s="18"/>
     </row>
-    <row r="118" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="D118" s="18"/>
       <c r="E118" s="24" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="119" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="V119" s="38"/>
       <c r="AI119" s="38" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="120" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E120" s="64" t="s">
         <v>250</v>
       </c>
@@ -21629,7 +21662,7 @@
       <c r="AH120" s="173"/>
       <c r="AI120" s="174"/>
     </row>
-    <row r="121" spans="1:36" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:36" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E121" s="62">
         <v>1</v>
       </c>
@@ -21678,7 +21711,7 @@
       <c r="AH121" s="238"/>
       <c r="AI121" s="239"/>
     </row>
-    <row r="122" spans="1:36" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:36" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E122" s="62">
         <v>2</v>
       </c>
@@ -21723,7 +21756,7 @@
       <c r="AH122" s="238"/>
       <c r="AI122" s="239"/>
     </row>
-    <row r="123" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:36" x14ac:dyDescent="0.2">
       <c r="E123" s="25"/>
       <c r="F123" s="29"/>
       <c r="G123" s="29"/>
@@ -21744,7 +21777,7 @@
       <c r="V123" s="30"/>
       <c r="W123" s="27"/>
     </row>
-    <row r="124" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D124" t="s">
         <v>363</v>
       </c>
@@ -21768,7 +21801,7 @@
       <c r="V124" s="30"/>
       <c r="W124" s="27"/>
     </row>
-    <row r="125" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:36" x14ac:dyDescent="0.2">
       <c r="E125" s="25"/>
       <c r="F125" s="29"/>
       <c r="G125" s="29"/>
@@ -21789,7 +21822,7 @@
       <c r="V125" s="30"/>
       <c r="W125" s="27"/>
     </row>
-    <row r="126" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -21828,7 +21861,7 @@
       <c r="AI126" s="1"/>
       <c r="AJ126" s="1"/>
     </row>
-    <row r="127" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -21866,7 +21899,7 @@
       <c r="AI127" s="1"/>
       <c r="AJ127" s="1"/>
     </row>
-    <row r="128" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -21902,7 +21935,7 @@
       <c r="AI128" s="1"/>
       <c r="AJ128" s="1"/>
     </row>
-    <row r="129" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -21941,7 +21974,7 @@
       <c r="AI129" s="1"/>
       <c r="AJ129" s="1"/>
     </row>
-    <row r="130" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -21980,7 +22013,7 @@
       <c r="AI130" s="1"/>
       <c r="AJ130" s="1"/>
     </row>
-    <row r="131" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -22017,7 +22050,7 @@
       <c r="AI131" s="1"/>
       <c r="AJ131" s="1"/>
     </row>
-    <row r="132" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -22056,7 +22089,7 @@
       <c r="AI132" s="1"/>
       <c r="AJ132" s="1"/>
     </row>
-    <row r="133" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -22095,7 +22128,7 @@
       <c r="AI133" s="1"/>
       <c r="AJ133" s="1"/>
     </row>
-    <row r="134" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -22134,7 +22167,7 @@
       <c r="AI134" s="1"/>
       <c r="AJ134" s="1"/>
     </row>
-    <row r="135" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -22172,35 +22205,35 @@
       <c r="AI135" s="1"/>
       <c r="AJ135" s="1"/>
     </row>
-    <row r="137" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C137" s="24" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="138" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="D138" s="18"/>
     </row>
-    <row r="139" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="D139" s="58" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="140" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="D140" s="18"/>
     </row>
-    <row r="141" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="D141" s="18"/>
       <c r="E141" s="24" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="142" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="V142" s="38"/>
       <c r="AI142" s="38" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="143" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:36" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E143" s="64" t="s">
         <v>250</v>
       </c>
@@ -22249,7 +22282,7 @@
       <c r="AH143" s="173"/>
       <c r="AI143" s="174"/>
     </row>
-    <row r="144" spans="1:36" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:36" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E144" s="62">
         <v>1</v>
       </c>
@@ -22298,7 +22331,7 @@
       <c r="AH144" s="238"/>
       <c r="AI144" s="239"/>
     </row>
-    <row r="145" spans="1:36" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:36" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E145" s="62">
         <v>2</v>
       </c>
@@ -22343,7 +22376,7 @@
       <c r="AH145" s="238"/>
       <c r="AI145" s="239"/>
     </row>
-    <row r="146" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:36" x14ac:dyDescent="0.2">
       <c r="E146" s="25"/>
       <c r="F146" s="29"/>
       <c r="G146" s="29"/>
@@ -22364,7 +22397,7 @@
       <c r="V146" s="30"/>
       <c r="W146" s="27"/>
     </row>
-    <row r="147" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D147" t="s">
         <v>365</v>
       </c>
@@ -22388,7 +22421,7 @@
       <c r="V147" s="30"/>
       <c r="W147" s="27"/>
     </row>
-    <row r="148" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:36" x14ac:dyDescent="0.2">
       <c r="E148" s="25"/>
       <c r="F148" s="29"/>
       <c r="G148" s="29"/>
@@ -22409,7 +22442,7 @@
       <c r="V148" s="30"/>
       <c r="W148" s="27"/>
     </row>
-    <row r="149" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -22448,7 +22481,7 @@
       <c r="AI149" s="1"/>
       <c r="AJ149" s="1"/>
     </row>
-    <row r="150" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -22486,7 +22519,7 @@
       <c r="AI150" s="1"/>
       <c r="AJ150" s="1"/>
     </row>
-    <row r="151" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -22522,7 +22555,7 @@
       <c r="AI151" s="1"/>
       <c r="AJ151" s="1"/>
     </row>
-    <row r="152" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -22561,7 +22594,7 @@
       <c r="AI152" s="1"/>
       <c r="AJ152" s="1"/>
     </row>
-    <row r="153" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -22600,7 +22633,7 @@
       <c r="AI153" s="1"/>
       <c r="AJ153" s="1"/>
     </row>
-    <row r="154" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -22637,7 +22670,7 @@
       <c r="AI154" s="1"/>
       <c r="AJ154" s="1"/>
     </row>
-    <row r="155" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -22676,7 +22709,7 @@
       <c r="AI155" s="1"/>
       <c r="AJ155" s="1"/>
     </row>
-    <row r="156" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -22715,7 +22748,7 @@
       <c r="AI156" s="1"/>
       <c r="AJ156" s="1"/>
     </row>
-    <row r="157" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -22754,7 +22787,7 @@
       <c r="AI157" s="1"/>
       <c r="AJ157" s="1"/>
     </row>
-    <row r="158" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:36" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -22792,7 +22825,7 @@
       <c r="AI158" s="1"/>
       <c r="AJ158" s="1"/>
     </row>
-    <row r="160" spans="1:36" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A160" s="27"/>
       <c r="B160" s="27"/>
       <c r="C160" s="27"/>
@@ -22819,7 +22852,7 @@
       <c r="X160" s="27"/>
       <c r="Y160" s="27"/>
     </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A161" s="27"/>
       <c r="B161" s="27"/>
       <c r="C161" s="27"/>
@@ -22846,7 +22879,7 @@
       <c r="X161" s="27"/>
       <c r="Y161" s="27"/>
     </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A162" s="27"/>
       <c r="B162" s="27"/>
       <c r="C162" s="27"/>
